--- a/Literature/Languages/Ranûdan.xlsx
+++ b/Literature/Languages/Ranûdan.xlsx
@@ -5967,27 +5967,27 @@
     <t>ere</t>
   </si>
   <si>
+    <t>gwen</t>
+  </si>
+  <si>
+    <t>bir/lae</t>
+  </si>
+  <si>
+    <t>eŋya</t>
+  </si>
+  <si>
+    <t>gwenya</t>
+  </si>
+  <si>
+    <t>bere</t>
+  </si>
+  <si>
+    <t>ena</t>
+  </si>
+  <si>
     <t>gwin</t>
   </si>
   <si>
-    <t>bir/lae</t>
-  </si>
-  <si>
-    <t>eŋya</t>
-  </si>
-  <si>
-    <t>gwinya</t>
-  </si>
-  <si>
-    <t>bere</t>
-  </si>
-  <si>
-    <t>ena</t>
-  </si>
-  <si>
-    <t>gwaen</t>
-  </si>
-  <si>
     <t>baen/laen</t>
   </si>
   <si>
@@ -5997,7 +5997,7 @@
     <t>gwinyeni</t>
   </si>
   <si>
-    <t>bereni</t>
+    <t>bena</t>
   </si>
   <si>
     <t>pronouns (far, inanimate)</t>
@@ -6768,7 +6768,7 @@
     <t>The warrior drew his sword.</t>
   </si>
   <si>
-    <t>Gwin ere zlonde.</t>
+    <t>Gwen ere zlonde.</t>
   </si>
   <si>
     <t>I love you.</t>

--- a/Literature/Languages/Ranûdan.xlsx
+++ b/Literature/Languages/Ranûdan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3056" uniqueCount="2032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3053" uniqueCount="2031">
   <si>
     <t>Word</t>
   </si>
@@ -1899,7 +1899,7 @@
     <t>choir</t>
   </si>
   <si>
-    <t>gwûna</t>
+    <t>gwuna</t>
   </si>
   <si>
     <t>currency, money</t>
@@ -1929,1126 +1929,1126 @@
     <t>gender</t>
   </si>
   <si>
-    <t>hain</t>
+    <t>haiŋ</t>
+  </si>
+  <si>
+    <t>storm</t>
+  </si>
+  <si>
+    <t>loud</t>
+  </si>
+  <si>
+    <t>haish</t>
+  </si>
+  <si>
+    <t>hauberk</t>
+  </si>
+  <si>
+    <t>haissen</t>
+  </si>
+  <si>
+    <t>to hug, to embrace</t>
+  </si>
+  <si>
+    <t>halûin</t>
+  </si>
+  <si>
+    <t>dragon, wyrm</t>
+  </si>
+  <si>
+    <t>hasse</t>
+  </si>
+  <si>
+    <t>hand</t>
+  </si>
+  <si>
+    <t>heblen</t>
+  </si>
+  <si>
+    <t>to keep</t>
+  </si>
+  <si>
+    <t>hele</t>
+  </si>
+  <si>
+    <t>fire</t>
+  </si>
+  <si>
+    <t>helerôn</t>
+  </si>
+  <si>
+    <t>volcano</t>
+  </si>
+  <si>
+    <t>hembûin</t>
+  </si>
+  <si>
+    <t>salmon</t>
+  </si>
+  <si>
+    <t>heten</t>
+  </si>
+  <si>
+    <t>cubit</t>
+  </si>
+  <si>
+    <t>hewas</t>
+  </si>
+  <si>
+    <t>brown</t>
+  </si>
+  <si>
+    <t>hicesh</t>
+  </si>
+  <si>
+    <t>to skip around, to frolick merrily</t>
+  </si>
+  <si>
+    <t>himai</t>
+  </si>
+  <si>
+    <t>shirt, tunic</t>
+  </si>
+  <si>
+    <t>hiŋgen</t>
+  </si>
+  <si>
+    <t>to train, to teach</t>
+  </si>
+  <si>
+    <t>hiŋgesh</t>
+  </si>
+  <si>
+    <t>to practice, to train</t>
+  </si>
+  <si>
+    <t>hiôlash</t>
+  </si>
+  <si>
+    <t>to jump, to leap</t>
+  </si>
+  <si>
+    <t>hithen</t>
+  </si>
+  <si>
+    <t>to anger</t>
+  </si>
+  <si>
+    <t>hithes</t>
+  </si>
+  <si>
+    <t>angry</t>
+  </si>
+  <si>
+    <t>hob</t>
+  </si>
+  <si>
+    <t>goblin</t>
+  </si>
+  <si>
+    <t>hwassi</t>
+  </si>
+  <si>
+    <t>hour</t>
+  </si>
+  <si>
+    <t>hwer</t>
+  </si>
+  <si>
+    <t>fast, quick</t>
+  </si>
+  <si>
+    <t>hwes</t>
+  </si>
+  <si>
+    <t>seven</t>
+  </si>
+  <si>
+    <t>hweshe</t>
+  </si>
+  <si>
+    <t>sand</t>
+  </si>
+  <si>
+    <t>hwethae</t>
+  </si>
+  <si>
+    <t>list, collection</t>
+  </si>
+  <si>
+    <t>hwie</t>
+  </si>
+  <si>
+    <t>sweat</t>
+  </si>
+  <si>
+    <t>hwil</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>hwiôrlath</t>
+  </si>
+  <si>
+    <t>school, academy</t>
+  </si>
+  <si>
+    <t>hwir</t>
+  </si>
+  <si>
+    <t>simple</t>
+  </si>
+  <si>
+    <t>hwond</t>
+  </si>
+  <si>
+    <t>guard, guardsman, patroller, watchman</t>
+  </si>
+  <si>
+    <t>hwônden</t>
+  </si>
+  <si>
+    <t>to soak, to drench</t>
+  </si>
+  <si>
+    <t>hŷl</t>
+  </si>
+  <si>
+    <t>forest heather</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>seperator article put between the object and the subject and verb to distinguish "object + verb + subject + modal verb" sentences</t>
+  </si>
+  <si>
+    <t>ian</t>
+  </si>
+  <si>
+    <t>bridge</t>
+  </si>
+  <si>
+    <t>iar</t>
+  </si>
+  <si>
+    <t>hot</t>
+  </si>
+  <si>
+    <t>iare</t>
+  </si>
+  <si>
+    <t>heat</t>
+  </si>
+  <si>
+    <t>ilare</t>
+  </si>
+  <si>
+    <t>sky</t>
+  </si>
+  <si>
+    <t>ilbu</t>
+  </si>
+  <si>
+    <t>down, downwards</t>
+  </si>
+  <si>
+    <t>ilem</t>
+  </si>
+  <si>
+    <t>ink</t>
+  </si>
+  <si>
+    <t>indashas</t>
+  </si>
+  <si>
+    <t>possible</t>
+  </si>
+  <si>
+    <t>inde</t>
+  </si>
+  <si>
+    <t>to do, to act (no infinitive)</t>
+  </si>
+  <si>
+    <t>ine</t>
+  </si>
+  <si>
+    <t>zero</t>
+  </si>
+  <si>
+    <t>ine-</t>
+  </si>
+  <si>
+    <t>prefix</t>
+  </si>
+  <si>
+    <t>negator prefix</t>
+  </si>
+  <si>
+    <t>ineblewssebie</t>
+  </si>
+  <si>
+    <t>uncomfortable</t>
+  </si>
+  <si>
+    <t>ineindashas</t>
+  </si>
+  <si>
+    <t>impossible</t>
+  </si>
+  <si>
+    <t>inende</t>
+  </si>
+  <si>
+    <t>to do not</t>
+  </si>
+  <si>
+    <t>ineraeleshtil</t>
+  </si>
+  <si>
+    <t>eternal, forever, undying</t>
+  </si>
+  <si>
+    <t>inezile</t>
+  </si>
+  <si>
+    <t>wall</t>
+  </si>
+  <si>
+    <t>inyas</t>
+  </si>
+  <si>
+    <t>small, little</t>
+  </si>
+  <si>
+    <t>iraidôr</t>
+  </si>
+  <si>
+    <t>ruby</t>
+  </si>
+  <si>
+    <t>irithie</t>
+  </si>
+  <si>
+    <t>silver</t>
+  </si>
+  <si>
+    <t>isil</t>
+  </si>
+  <si>
+    <t>eye</t>
+  </si>
+  <si>
+    <t>ithamae</t>
+  </si>
+  <si>
+    <t>painting</t>
+  </si>
+  <si>
+    <t>ivereld</t>
+  </si>
+  <si>
+    <t>mission, quest</t>
+  </si>
+  <si>
+    <t>jaen</t>
+  </si>
+  <si>
+    <t>stairs</t>
+  </si>
+  <si>
+    <t>jaenen</t>
+  </si>
+  <si>
+    <t>to heal a wound</t>
+  </si>
+  <si>
+    <t>jaer</t>
+  </si>
+  <si>
+    <t>door</t>
+  </si>
+  <si>
+    <t>jaethan</t>
+  </si>
+  <si>
+    <t>to paint</t>
+  </si>
+  <si>
+    <t>jandre</t>
+  </si>
+  <si>
+    <t>a poetic, flowing song; a ballad</t>
+  </si>
+  <si>
+    <t>jane</t>
+  </si>
+  <si>
+    <t>jade</t>
+  </si>
+  <si>
+    <t>janûssi</t>
+  </si>
+  <si>
+    <t>disease, sickness, illness</t>
+  </si>
+  <si>
+    <t>jelen</t>
+  </si>
+  <si>
+    <t>late</t>
+  </si>
+  <si>
+    <t>jiôrien</t>
+  </si>
+  <si>
+    <t>scroll</t>
+  </si>
+  <si>
+    <t>jow</t>
+  </si>
+  <si>
+    <t>group, party, company</t>
+  </si>
+  <si>
+    <t>jûlen</t>
+  </si>
+  <si>
+    <t>to eat</t>
+  </si>
+  <si>
+    <t>jûrwen</t>
+  </si>
+  <si>
+    <t>ship</t>
+  </si>
+  <si>
+    <t>lacen</t>
+  </si>
+  <si>
+    <t>to scare, to frighten</t>
+  </si>
+  <si>
+    <t>lagwe</t>
+  </si>
+  <si>
+    <t>oil</t>
+  </si>
+  <si>
+    <t>lande</t>
+  </si>
+  <si>
+    <t>empty</t>
+  </si>
+  <si>
+    <t>lannae</t>
+  </si>
+  <si>
+    <t>woman</t>
+  </si>
+  <si>
+    <t>lante</t>
+  </si>
+  <si>
+    <t>lake</t>
+  </si>
+  <si>
+    <t>lanyan</t>
+  </si>
+  <si>
+    <t>to weave</t>
+  </si>
+  <si>
+    <t>larun</t>
+  </si>
+  <si>
+    <t>desert, desolate land</t>
+  </si>
+  <si>
+    <t>larunbie</t>
+  </si>
+  <si>
+    <t>desolate, deserted, completely empty</t>
+  </si>
+  <si>
+    <t>lemya</t>
+  </si>
+  <si>
+    <t>smell, aroma, fragrance</t>
+  </si>
+  <si>
+    <t>lendessil</t>
+  </si>
+  <si>
+    <t>grove</t>
+  </si>
+  <si>
+    <t>lerie</t>
+  </si>
+  <si>
+    <t>lyre</t>
+  </si>
+  <si>
+    <t>lewwe</t>
+  </si>
+  <si>
+    <t>smell, odor, aroma</t>
+  </si>
+  <si>
+    <t>linde</t>
+  </si>
+  <si>
+    <t>back</t>
+  </si>
+  <si>
+    <t>lindu</t>
+  </si>
+  <si>
+    <t>backwards</t>
+  </si>
+  <si>
+    <t>lindu cwen</t>
+  </si>
+  <si>
+    <t>to put away</t>
+  </si>
+  <si>
+    <t>liŋgash</t>
+  </si>
+  <si>
+    <t>to trail, to leave a trail</t>
+  </si>
+  <si>
+    <t>lir</t>
+  </si>
+  <si>
+    <t>but, yet, still</t>
+  </si>
+  <si>
+    <t>lisse</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>lissesiŋgae</t>
+  </si>
+  <si>
+    <t>saltwater brine</t>
+  </si>
+  <si>
+    <t>lith</t>
+  </si>
+  <si>
+    <t>dust, grime</t>
+  </si>
+  <si>
+    <t>lode</t>
+  </si>
+  <si>
+    <t>left</t>
+  </si>
+  <si>
+    <t>lodu</t>
+  </si>
+  <si>
+    <t>leftwards</t>
+  </si>
+  <si>
+    <t>loias</t>
+  </si>
+  <si>
+    <t>pink</t>
+  </si>
+  <si>
+    <t>lôin</t>
+  </si>
+  <si>
+    <t>now</t>
+  </si>
+  <si>
+    <t>lôl</t>
+  </si>
+  <si>
+    <t>hill</t>
+  </si>
+  <si>
+    <t>lômash</t>
+  </si>
+  <si>
+    <t>to learn</t>
+  </si>
+  <si>
+    <t>lômen</t>
+  </si>
+  <si>
+    <t>to teach</t>
+  </si>
+  <si>
+    <t>losse</t>
+  </si>
+  <si>
+    <t>snow</t>
+  </si>
+  <si>
+    <t>lôssen</t>
+  </si>
+  <si>
+    <t>to beg, to plead</t>
+  </si>
+  <si>
+    <t>loth</t>
+  </si>
+  <si>
+    <t>bread</t>
+  </si>
+  <si>
+    <t>lothie</t>
+  </si>
+  <si>
+    <t>temple, shrine, religious place</t>
+  </si>
+  <si>
+    <t>lûandar</t>
+  </si>
+  <si>
+    <t>steel</t>
+  </si>
+  <si>
+    <t>lûantir</t>
+  </si>
+  <si>
+    <t>crossbow (weapon)</t>
+  </si>
+  <si>
+    <t>luge</t>
+  </si>
+  <si>
+    <t>mud, ooze</t>
+  </si>
+  <si>
+    <t>lûi</t>
+  </si>
+  <si>
+    <t>river</t>
+  </si>
+  <si>
+    <t>lûind</t>
+  </si>
+  <si>
+    <t>village, town, settlement</t>
+  </si>
+  <si>
+    <t>lûise</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>lûl</t>
+  </si>
+  <si>
+    <t>life</t>
+  </si>
+  <si>
+    <t>lûmassash</t>
+  </si>
+  <si>
+    <t>to cry, to weep</t>
+  </si>
+  <si>
+    <t>lunas</t>
+  </si>
+  <si>
+    <t>mild, gentle, kind, nice, friendly, sweet</t>
+  </si>
+  <si>
+    <t>lûnge</t>
+  </si>
+  <si>
+    <t>bottom</t>
+  </si>
+  <si>
+    <t>lûngu</t>
+  </si>
+  <si>
+    <t>under</t>
+  </si>
+  <si>
+    <t>lûr</t>
+  </si>
+  <si>
+    <t>slow, slowly</t>
+  </si>
+  <si>
+    <t>lûrbie</t>
+  </si>
+  <si>
+    <t>lazy</t>
+  </si>
+  <si>
+    <t>maiepasvie</t>
+  </si>
+  <si>
+    <t>cathedral</t>
+  </si>
+  <si>
+    <t>maissen</t>
+  </si>
+  <si>
+    <t>to cheer up</t>
+  </si>
+  <si>
+    <t>maissenassi</t>
+  </si>
+  <si>
+    <t>happiness, joy, glee</t>
+  </si>
+  <si>
+    <t>maisses</t>
+  </si>
+  <si>
+    <t>happy, joyful, gleeful</t>
+  </si>
+  <si>
+    <t>maissetele</t>
+  </si>
+  <si>
+    <t>happy, joyful, gleeful (because of something); proud</t>
+  </si>
+  <si>
+    <t>malen</t>
+  </si>
+  <si>
+    <t>to mix, to blend, to stir</t>
+  </si>
+  <si>
+    <t>malessi</t>
+  </si>
+  <si>
+    <t>mix, blend, concoction; chaotic group, melting pot of things; compilation</t>
+  </si>
+  <si>
+    <t>malya</t>
+  </si>
+  <si>
+    <t>government</t>
+  </si>
+  <si>
+    <t>manaran</t>
+  </si>
+  <si>
+    <t>to escape, to flee</t>
+  </si>
+  <si>
+    <t>mansiel</t>
+  </si>
+  <si>
+    <t>diamond</t>
+  </si>
+  <si>
+    <t>mant</t>
+  </si>
+  <si>
+    <t>trouble, problem</t>
+  </si>
+  <si>
+    <t>maŋgar</t>
+  </si>
+  <si>
+    <t>brave, bold, courageous</t>
+  </si>
+  <si>
+    <t>maŋgwon</t>
+  </si>
+  <si>
+    <t>smell, stench</t>
+  </si>
+  <si>
+    <t>maŋwesh</t>
+  </si>
+  <si>
+    <t>to stink, to emit a bad smell, to emit a stench</t>
+  </si>
+  <si>
+    <t>maŋye</t>
+  </si>
+  <si>
+    <t>potion, concoction, mixture</t>
+  </si>
+  <si>
+    <t>mari</t>
+  </si>
+  <si>
+    <t>letter, rune</t>
+  </si>
+  <si>
+    <t>mashe</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>mashele</t>
+  </si>
+  <si>
+    <t>meal</t>
+  </si>
+  <si>
+    <t>masinde</t>
+  </si>
+  <si>
+    <t>result, conclusion, fate, destiny</t>
+  </si>
+  <si>
+    <t>maslom</t>
+  </si>
+  <si>
+    <t>ball, sphere</t>
+  </si>
+  <si>
+    <t>maslos</t>
+  </si>
+  <si>
+    <t>orange (color)</t>
+  </si>
+  <si>
+    <t>masse</t>
+  </si>
+  <si>
+    <t>bird</t>
+  </si>
+  <si>
+    <t>massil</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>mathash</t>
+  </si>
+  <si>
+    <t>to work, to labour</t>
+  </si>
+  <si>
+    <t>meca</t>
+  </si>
+  <si>
+    <t>brick</t>
+  </si>
+  <si>
+    <t>meidel</t>
+  </si>
+  <si>
+    <t>shovel</t>
+  </si>
+  <si>
+    <t>melanen</t>
+  </si>
+  <si>
+    <t>to help</t>
+  </si>
+  <si>
+    <t>melanssi</t>
+  </si>
+  <si>
+    <t>help, assistance</t>
+  </si>
+  <si>
+    <t>mele</t>
+  </si>
+  <si>
+    <t>melodic, lyrical</t>
+  </si>
+  <si>
+    <t>melessie</t>
+  </si>
+  <si>
+    <t>poem</t>
+  </si>
+  <si>
+    <t>meltie</t>
+  </si>
+  <si>
+    <t>when</t>
+  </si>
+  <si>
+    <t>melyabie</t>
+  </si>
+  <si>
+    <t>lovely, adorable</t>
+  </si>
+  <si>
+    <t>melyan</t>
+  </si>
+  <si>
+    <t>to love</t>
+  </si>
+  <si>
+    <t>menden</t>
+  </si>
+  <si>
+    <t>to pay</t>
+  </si>
+  <si>
+    <t>merassi</t>
+  </si>
+  <si>
+    <t>friend</t>
+  </si>
+  <si>
+    <t>mere</t>
+  </si>
+  <si>
+    <t>favourite</t>
+  </si>
+  <si>
+    <t>mesh</t>
+  </si>
+  <si>
+    <t>to can, to be able to</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
+    <t>in, inside</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>by, beside, with; of</t>
+  </si>
+  <si>
+    <t>min lûl ... na</t>
+  </si>
+  <si>
+    <t>alive</t>
+  </si>
+  <si>
+    <t>min molie ... na</t>
+  </si>
+  <si>
+    <t>busy</t>
+  </si>
+  <si>
+    <t>miôren</t>
+  </si>
+  <si>
+    <t>to care for, to nurture</t>
+  </si>
+  <si>
+    <t>mironden</t>
+  </si>
+  <si>
+    <t>to infect</t>
+  </si>
+  <si>
+    <t>missi</t>
+  </si>
+  <si>
+    <t>inside</t>
+  </si>
+  <si>
+    <t>miu</t>
+  </si>
+  <si>
+    <t>into</t>
+  </si>
+  <si>
+    <t>miu ôlaish</t>
+  </si>
+  <si>
+    <t>to fall asleep</t>
+  </si>
+  <si>
+    <t>mô</t>
+  </si>
+  <si>
+    <t>or</t>
+  </si>
+  <si>
+    <t>moile</t>
+  </si>
+  <si>
+    <t>hole</t>
+  </si>
+  <si>
+    <t>molai</t>
+  </si>
+  <si>
+    <t>more</t>
+  </si>
+  <si>
+    <t>môlde</t>
+  </si>
+  <si>
+    <t>battle</t>
+  </si>
+  <si>
+    <t>môldehwond</t>
+  </si>
+  <si>
+    <t>warrior</t>
+  </si>
+  <si>
+    <t>molie</t>
+  </si>
+  <si>
+    <t>work, labour, job</t>
+  </si>
+  <si>
+    <t>momil</t>
+  </si>
+  <si>
+    <t>owl</t>
+  </si>
+  <si>
+    <t>monae</t>
+  </si>
+  <si>
+    <t>body, torso</t>
+  </si>
+  <si>
+    <t>mône</t>
+  </si>
+  <si>
+    <t>smart, intelligent</t>
+  </si>
+  <si>
+    <t>morda</t>
+  </si>
+  <si>
+    <t>map</t>
+  </si>
+  <si>
+    <t>môre</t>
+  </si>
+  <si>
+    <t>fox</t>
+  </si>
+  <si>
+    <t>môril</t>
+  </si>
+  <si>
+    <t>bowl</t>
+  </si>
+  <si>
+    <t>môrlas</t>
+  </si>
+  <si>
+    <t>wrong</t>
+  </si>
+  <si>
+    <t>môth</t>
+  </si>
+  <si>
+    <t>wraith</t>
+  </si>
+  <si>
+    <t>mrônan</t>
+  </si>
+  <si>
+    <t>to kiss passionately</t>
+  </si>
+  <si>
+    <t>mrûne</t>
+  </si>
+  <si>
+    <t>hungry</t>
+  </si>
+  <si>
+    <t>mûiral</t>
+  </si>
+  <si>
+    <t>armor, armour</t>
+  </si>
+  <si>
+    <t>munas</t>
+  </si>
+  <si>
+    <t>sleepy, tired, drowsy</t>
+  </si>
+  <si>
+    <t>mûr</t>
+  </si>
+  <si>
+    <t>basin, sink</t>
+  </si>
+  <si>
+    <t>mŷcûl</t>
+  </si>
+  <si>
+    <t>witch, hag</t>
+  </si>
+  <si>
+    <t>mŷl</t>
+  </si>
+  <si>
+    <t>gull, seagull</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>to be (verb group b)</t>
+  </si>
+  <si>
+    <t>naben</t>
+  </si>
+  <si>
+    <t>to take, to get</t>
+  </si>
+  <si>
+    <t>nacen</t>
+  </si>
+  <si>
+    <t>to chop, to slice</t>
+  </si>
+  <si>
+    <t>naese</t>
+  </si>
+  <si>
+    <t>leg</t>
+  </si>
+  <si>
+    <t>nagwa</t>
+  </si>
+  <si>
+    <t>scar</t>
+  </si>
+  <si>
+    <t>naie</t>
+  </si>
+  <si>
+    <t>here</t>
+  </si>
+  <si>
+    <t>nail</t>
+  </si>
+  <si>
+    <t>piece, part</t>
+  </si>
+  <si>
+    <t>naimash</t>
+  </si>
+  <si>
+    <t>to worry</t>
+  </si>
+  <si>
+    <t>naitie</t>
   </si>
   <si>
     <t>truth</t>
   </si>
   <si>
-    <t>hainbie</t>
+    <t>naitiebie</t>
   </si>
   <si>
     <t>true, right, correct</t>
-  </si>
-  <si>
-    <t>haiŋ</t>
-  </si>
-  <si>
-    <t>storm</t>
-  </si>
-  <si>
-    <t>loud</t>
-  </si>
-  <si>
-    <t>haish</t>
-  </si>
-  <si>
-    <t>hauberk</t>
-  </si>
-  <si>
-    <t>haissen</t>
-  </si>
-  <si>
-    <t>to hug, to embrace</t>
-  </si>
-  <si>
-    <t>halûin</t>
-  </si>
-  <si>
-    <t>dragon, wyrm</t>
-  </si>
-  <si>
-    <t>hasse</t>
-  </si>
-  <si>
-    <t>hand</t>
-  </si>
-  <si>
-    <t>heblen</t>
-  </si>
-  <si>
-    <t>to keep</t>
-  </si>
-  <si>
-    <t>hele</t>
-  </si>
-  <si>
-    <t>fire</t>
-  </si>
-  <si>
-    <t>helerôn</t>
-  </si>
-  <si>
-    <t>volcano</t>
-  </si>
-  <si>
-    <t>hembûin</t>
-  </si>
-  <si>
-    <t>salmon</t>
-  </si>
-  <si>
-    <t>heten</t>
-  </si>
-  <si>
-    <t>cubit</t>
-  </si>
-  <si>
-    <t>hewas</t>
-  </si>
-  <si>
-    <t>brown</t>
-  </si>
-  <si>
-    <t>hicesh</t>
-  </si>
-  <si>
-    <t>to skip around, to frolick merrily</t>
-  </si>
-  <si>
-    <t>himai</t>
-  </si>
-  <si>
-    <t>shirt, tunic</t>
-  </si>
-  <si>
-    <t>hiŋgen</t>
-  </si>
-  <si>
-    <t>to train, to teach</t>
-  </si>
-  <si>
-    <t>hiŋgesh</t>
-  </si>
-  <si>
-    <t>to practice, to train</t>
-  </si>
-  <si>
-    <t>hiôlash</t>
-  </si>
-  <si>
-    <t>to jump, to leap</t>
-  </si>
-  <si>
-    <t>hithen</t>
-  </si>
-  <si>
-    <t>to anger</t>
-  </si>
-  <si>
-    <t>hithes</t>
-  </si>
-  <si>
-    <t>angry</t>
-  </si>
-  <si>
-    <t>hob</t>
-  </si>
-  <si>
-    <t>goblin</t>
-  </si>
-  <si>
-    <t>hwassi</t>
-  </si>
-  <si>
-    <t>hour</t>
-  </si>
-  <si>
-    <t>hwer</t>
-  </si>
-  <si>
-    <t>fast, quick</t>
-  </si>
-  <si>
-    <t>hwes</t>
-  </si>
-  <si>
-    <t>seven</t>
-  </si>
-  <si>
-    <t>hweshe</t>
-  </si>
-  <si>
-    <t>sand</t>
-  </si>
-  <si>
-    <t>hwethae</t>
-  </si>
-  <si>
-    <t>list, collection</t>
-  </si>
-  <si>
-    <t>hwie</t>
-  </si>
-  <si>
-    <t>sweat</t>
-  </si>
-  <si>
-    <t>hwil</t>
-  </si>
-  <si>
-    <t>time</t>
-  </si>
-  <si>
-    <t>hwiôrlath</t>
-  </si>
-  <si>
-    <t>school, academy</t>
-  </si>
-  <si>
-    <t>hwir</t>
-  </si>
-  <si>
-    <t>simple</t>
-  </si>
-  <si>
-    <t>hwond</t>
-  </si>
-  <si>
-    <t>guard, guardsman, patroller, watchman</t>
-  </si>
-  <si>
-    <t>hwônden</t>
-  </si>
-  <si>
-    <t>to soak, to drench</t>
-  </si>
-  <si>
-    <t>hŷl</t>
-  </si>
-  <si>
-    <t>forest heather</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>seperator article put between the object and the subject and verb to distinguish "object + verb + subject + modal verb" sentences</t>
-  </si>
-  <si>
-    <t>ian</t>
-  </si>
-  <si>
-    <t>bridge</t>
-  </si>
-  <si>
-    <t>iar</t>
-  </si>
-  <si>
-    <t>hot</t>
-  </si>
-  <si>
-    <t>iare</t>
-  </si>
-  <si>
-    <t>heat</t>
-  </si>
-  <si>
-    <t>ilare</t>
-  </si>
-  <si>
-    <t>sky</t>
-  </si>
-  <si>
-    <t>ilbu</t>
-  </si>
-  <si>
-    <t>down, downwards</t>
-  </si>
-  <si>
-    <t>ilem</t>
-  </si>
-  <si>
-    <t>ink</t>
-  </si>
-  <si>
-    <t>indashas</t>
-  </si>
-  <si>
-    <t>possible</t>
-  </si>
-  <si>
-    <t>inde</t>
-  </si>
-  <si>
-    <t>to do, to act (no infinitive)</t>
-  </si>
-  <si>
-    <t>ine</t>
-  </si>
-  <si>
-    <t>zero</t>
-  </si>
-  <si>
-    <t>ine-</t>
-  </si>
-  <si>
-    <t>prefix</t>
-  </si>
-  <si>
-    <t>negator prefix</t>
-  </si>
-  <si>
-    <t>ineblewssebie</t>
-  </si>
-  <si>
-    <t>uncomfortable</t>
-  </si>
-  <si>
-    <t>ineindashas</t>
-  </si>
-  <si>
-    <t>impossible</t>
-  </si>
-  <si>
-    <t>inende</t>
-  </si>
-  <si>
-    <t>to do not</t>
-  </si>
-  <si>
-    <t>ineraeleshtil</t>
-  </si>
-  <si>
-    <t>eternal, forever, undying</t>
-  </si>
-  <si>
-    <t>inezile</t>
-  </si>
-  <si>
-    <t>wall</t>
-  </si>
-  <si>
-    <t>inyas</t>
-  </si>
-  <si>
-    <t>small, little</t>
-  </si>
-  <si>
-    <t>iraidôr</t>
-  </si>
-  <si>
-    <t>ruby</t>
-  </si>
-  <si>
-    <t>irithie</t>
-  </si>
-  <si>
-    <t>silver</t>
-  </si>
-  <si>
-    <t>isil</t>
-  </si>
-  <si>
-    <t>eye</t>
-  </si>
-  <si>
-    <t>ithamae</t>
-  </si>
-  <si>
-    <t>painting</t>
-  </si>
-  <si>
-    <t>ivereld</t>
-  </si>
-  <si>
-    <t>mission, quest</t>
-  </si>
-  <si>
-    <t>jaen</t>
-  </si>
-  <si>
-    <t>stairs</t>
-  </si>
-  <si>
-    <t>jaenen</t>
-  </si>
-  <si>
-    <t>to heal a wound</t>
-  </si>
-  <si>
-    <t>jaer</t>
-  </si>
-  <si>
-    <t>door</t>
-  </si>
-  <si>
-    <t>jaethan</t>
-  </si>
-  <si>
-    <t>to paint</t>
-  </si>
-  <si>
-    <t>jandre</t>
-  </si>
-  <si>
-    <t>a poetic, flowing song; a ballad</t>
-  </si>
-  <si>
-    <t>jane</t>
-  </si>
-  <si>
-    <t>jade</t>
-  </si>
-  <si>
-    <t>janûssi</t>
-  </si>
-  <si>
-    <t>disease, sickness, illness</t>
-  </si>
-  <si>
-    <t>jelen</t>
-  </si>
-  <si>
-    <t>late</t>
-  </si>
-  <si>
-    <t>jiôrien</t>
-  </si>
-  <si>
-    <t>scroll</t>
-  </si>
-  <si>
-    <t>jow</t>
-  </si>
-  <si>
-    <t>group, party, company</t>
-  </si>
-  <si>
-    <t>jûlen</t>
-  </si>
-  <si>
-    <t>to eat</t>
-  </si>
-  <si>
-    <t>jûrwen</t>
-  </si>
-  <si>
-    <t>ship</t>
-  </si>
-  <si>
-    <t>lacen</t>
-  </si>
-  <si>
-    <t>to scare, to frighten</t>
-  </si>
-  <si>
-    <t>lagwe</t>
-  </si>
-  <si>
-    <t>oil</t>
-  </si>
-  <si>
-    <t>lande</t>
-  </si>
-  <si>
-    <t>empty</t>
-  </si>
-  <si>
-    <t>lannae</t>
-  </si>
-  <si>
-    <t>woman</t>
-  </si>
-  <si>
-    <t>lante</t>
-  </si>
-  <si>
-    <t>lake</t>
-  </si>
-  <si>
-    <t>lanyan</t>
-  </si>
-  <si>
-    <t>to weave</t>
-  </si>
-  <si>
-    <t>larun</t>
-  </si>
-  <si>
-    <t>desert, desolate land</t>
-  </si>
-  <si>
-    <t>larunbie</t>
-  </si>
-  <si>
-    <t>desolate, deserted, completely empty</t>
-  </si>
-  <si>
-    <t>lemya</t>
-  </si>
-  <si>
-    <t>smell, aroma, fragrance</t>
-  </si>
-  <si>
-    <t>lendessil</t>
-  </si>
-  <si>
-    <t>grove</t>
-  </si>
-  <si>
-    <t>lerie</t>
-  </si>
-  <si>
-    <t>lyre</t>
-  </si>
-  <si>
-    <t>lewwe</t>
-  </si>
-  <si>
-    <t>smell, odor, aroma</t>
-  </si>
-  <si>
-    <t>linde</t>
-  </si>
-  <si>
-    <t>back</t>
-  </si>
-  <si>
-    <t>lindu</t>
-  </si>
-  <si>
-    <t>backwards</t>
-  </si>
-  <si>
-    <t>lindu cwen</t>
-  </si>
-  <si>
-    <t>to put away</t>
-  </si>
-  <si>
-    <t>liŋgash</t>
-  </si>
-  <si>
-    <t>to trail, to leave a trail</t>
-  </si>
-  <si>
-    <t>lir</t>
-  </si>
-  <si>
-    <t>but, yet, still</t>
-  </si>
-  <si>
-    <t>lisse</t>
-  </si>
-  <si>
-    <t>water</t>
-  </si>
-  <si>
-    <t>lissesiŋgae</t>
-  </si>
-  <si>
-    <t>saltwater brine</t>
-  </si>
-  <si>
-    <t>lith</t>
-  </si>
-  <si>
-    <t>dust, grime</t>
-  </si>
-  <si>
-    <t>lode</t>
-  </si>
-  <si>
-    <t>left</t>
-  </si>
-  <si>
-    <t>lodu</t>
-  </si>
-  <si>
-    <t>leftwards</t>
-  </si>
-  <si>
-    <t>loias</t>
-  </si>
-  <si>
-    <t>pink</t>
-  </si>
-  <si>
-    <t>lôin</t>
-  </si>
-  <si>
-    <t>now</t>
-  </si>
-  <si>
-    <t>lôl</t>
-  </si>
-  <si>
-    <t>hill</t>
-  </si>
-  <si>
-    <t>lômash</t>
-  </si>
-  <si>
-    <t>to learn</t>
-  </si>
-  <si>
-    <t>lômen</t>
-  </si>
-  <si>
-    <t>to teach</t>
-  </si>
-  <si>
-    <t>losse</t>
-  </si>
-  <si>
-    <t>snow</t>
-  </si>
-  <si>
-    <t>lôssen</t>
-  </si>
-  <si>
-    <t>to beg, to plead</t>
-  </si>
-  <si>
-    <t>loth</t>
-  </si>
-  <si>
-    <t>bread</t>
-  </si>
-  <si>
-    <t>lothie</t>
-  </si>
-  <si>
-    <t>temple, shrine, religious place</t>
-  </si>
-  <si>
-    <t>lûandar</t>
-  </si>
-  <si>
-    <t>steel</t>
-  </si>
-  <si>
-    <t>lûantir</t>
-  </si>
-  <si>
-    <t>crossbow (weapon)</t>
-  </si>
-  <si>
-    <t>luge</t>
-  </si>
-  <si>
-    <t>mud, ooze</t>
-  </si>
-  <si>
-    <t>lûi</t>
-  </si>
-  <si>
-    <t>river</t>
-  </si>
-  <si>
-    <t>lûind</t>
-  </si>
-  <si>
-    <t>village, town, settlement</t>
-  </si>
-  <si>
-    <t>lûise</t>
-  </si>
-  <si>
-    <t>month</t>
-  </si>
-  <si>
-    <t>lûl</t>
-  </si>
-  <si>
-    <t>life</t>
-  </si>
-  <si>
-    <t>lûmassash</t>
-  </si>
-  <si>
-    <t>to cry, to weep</t>
-  </si>
-  <si>
-    <t>lunas</t>
-  </si>
-  <si>
-    <t>mild, gentle, kind, nice, friendly, sweet</t>
-  </si>
-  <si>
-    <t>lûnge</t>
-  </si>
-  <si>
-    <t>bottom</t>
-  </si>
-  <si>
-    <t>lûngu</t>
-  </si>
-  <si>
-    <t>under</t>
-  </si>
-  <si>
-    <t>lûr</t>
-  </si>
-  <si>
-    <t>slow, slowly</t>
-  </si>
-  <si>
-    <t>lûrbie</t>
-  </si>
-  <si>
-    <t>lazy</t>
-  </si>
-  <si>
-    <t>maiepasvie</t>
-  </si>
-  <si>
-    <t>cathedral</t>
-  </si>
-  <si>
-    <t>maissen</t>
-  </si>
-  <si>
-    <t>to cheer up</t>
-  </si>
-  <si>
-    <t>maissenassi</t>
-  </si>
-  <si>
-    <t>happiness, joy, glee</t>
-  </si>
-  <si>
-    <t>maisses</t>
-  </si>
-  <si>
-    <t>happy, joyful, gleeful</t>
-  </si>
-  <si>
-    <t>maissetele</t>
-  </si>
-  <si>
-    <t>happy, joyful, gleeful (because of something); proud</t>
-  </si>
-  <si>
-    <t>malen</t>
-  </si>
-  <si>
-    <t>to mix, to blend, to stir</t>
-  </si>
-  <si>
-    <t>malessi</t>
-  </si>
-  <si>
-    <t>mix, blend, concoction; chaotic group, melting pot of things; compilation</t>
-  </si>
-  <si>
-    <t>malya</t>
-  </si>
-  <si>
-    <t>government</t>
-  </si>
-  <si>
-    <t>manaran</t>
-  </si>
-  <si>
-    <t>to escape, to flee</t>
-  </si>
-  <si>
-    <t>mansiel</t>
-  </si>
-  <si>
-    <t>diamond</t>
-  </si>
-  <si>
-    <t>mant</t>
-  </si>
-  <si>
-    <t>trouble, problem</t>
-  </si>
-  <si>
-    <t>maŋgar</t>
-  </si>
-  <si>
-    <t>brave, bold, courageous</t>
-  </si>
-  <si>
-    <t>maŋgwon</t>
-  </si>
-  <si>
-    <t>smell, stench</t>
-  </si>
-  <si>
-    <t>maŋwesh</t>
-  </si>
-  <si>
-    <t>to stink, to emit a bad smell, to emit a stench</t>
-  </si>
-  <si>
-    <t>maŋye</t>
-  </si>
-  <si>
-    <t>potion, concoction, mixture</t>
-  </si>
-  <si>
-    <t>mari</t>
-  </si>
-  <si>
-    <t>letter, rune</t>
-  </si>
-  <si>
-    <t>mashe</t>
-  </si>
-  <si>
-    <t>food</t>
-  </si>
-  <si>
-    <t>mashele</t>
-  </si>
-  <si>
-    <t>meal</t>
-  </si>
-  <si>
-    <t>masinde</t>
-  </si>
-  <si>
-    <t>result, conclusion, fate, destiny</t>
-  </si>
-  <si>
-    <t>maslom</t>
-  </si>
-  <si>
-    <t>ball, sphere</t>
-  </si>
-  <si>
-    <t>maslos</t>
-  </si>
-  <si>
-    <t>orange (color)</t>
-  </si>
-  <si>
-    <t>masse</t>
-  </si>
-  <si>
-    <t>bird</t>
-  </si>
-  <si>
-    <t>massil</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>mathash</t>
-  </si>
-  <si>
-    <t>to work, to labour</t>
-  </si>
-  <si>
-    <t>meca</t>
-  </si>
-  <si>
-    <t>brick</t>
-  </si>
-  <si>
-    <t>meidel</t>
-  </si>
-  <si>
-    <t>shovel</t>
-  </si>
-  <si>
-    <t>melanen</t>
-  </si>
-  <si>
-    <t>to help</t>
-  </si>
-  <si>
-    <t>melanssi</t>
-  </si>
-  <si>
-    <t>help, assistance</t>
-  </si>
-  <si>
-    <t>mele</t>
-  </si>
-  <si>
-    <t>melodic, lyrical</t>
-  </si>
-  <si>
-    <t>melessie</t>
-  </si>
-  <si>
-    <t>poem</t>
-  </si>
-  <si>
-    <t>meltie</t>
-  </si>
-  <si>
-    <t>when</t>
-  </si>
-  <si>
-    <t>melyabie</t>
-  </si>
-  <si>
-    <t>lovely, adorable</t>
-  </si>
-  <si>
-    <t>melyan</t>
-  </si>
-  <si>
-    <t>to love</t>
-  </si>
-  <si>
-    <t>menden</t>
-  </si>
-  <si>
-    <t>to pay</t>
-  </si>
-  <si>
-    <t>merassi</t>
-  </si>
-  <si>
-    <t>friend</t>
-  </si>
-  <si>
-    <t>mere</t>
-  </si>
-  <si>
-    <t>favourite</t>
-  </si>
-  <si>
-    <t>mesh</t>
-  </si>
-  <si>
-    <t>to can, to be able to</t>
-  </si>
-  <si>
-    <t>mi</t>
-  </si>
-  <si>
-    <t>in, inside</t>
-  </si>
-  <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>by, beside, with; of</t>
-  </si>
-  <si>
-    <t>min lûl ... na</t>
-  </si>
-  <si>
-    <t>alive</t>
-  </si>
-  <si>
-    <t>min molie ... na</t>
-  </si>
-  <si>
-    <t>busy</t>
-  </si>
-  <si>
-    <t>miôren</t>
-  </si>
-  <si>
-    <t>to care for, to nurture</t>
-  </si>
-  <si>
-    <t>mironden</t>
-  </si>
-  <si>
-    <t>to infect</t>
-  </si>
-  <si>
-    <t>missi</t>
-  </si>
-  <si>
-    <t>inside</t>
-  </si>
-  <si>
-    <t>miu</t>
-  </si>
-  <si>
-    <t>into</t>
-  </si>
-  <si>
-    <t>miu ôlaish</t>
-  </si>
-  <si>
-    <t>to fall asleep</t>
-  </si>
-  <si>
-    <t>mô</t>
-  </si>
-  <si>
-    <t>or</t>
-  </si>
-  <si>
-    <t>moile</t>
-  </si>
-  <si>
-    <t>hole</t>
-  </si>
-  <si>
-    <t>molai</t>
-  </si>
-  <si>
-    <t>more</t>
-  </si>
-  <si>
-    <t>môlde</t>
-  </si>
-  <si>
-    <t>battle</t>
-  </si>
-  <si>
-    <t>môldehwond</t>
-  </si>
-  <si>
-    <t>warrior</t>
-  </si>
-  <si>
-    <t>molie</t>
-  </si>
-  <si>
-    <t>work, labour, job</t>
-  </si>
-  <si>
-    <t>momil</t>
-  </si>
-  <si>
-    <t>owl</t>
-  </si>
-  <si>
-    <t>monae</t>
-  </si>
-  <si>
-    <t>body, torso</t>
-  </si>
-  <si>
-    <t>mône</t>
-  </si>
-  <si>
-    <t>smart, intelligent</t>
-  </si>
-  <si>
-    <t>morda</t>
-  </si>
-  <si>
-    <t>map</t>
-  </si>
-  <si>
-    <t>môre</t>
-  </si>
-  <si>
-    <t>fox</t>
-  </si>
-  <si>
-    <t>môril</t>
-  </si>
-  <si>
-    <t>bowl</t>
-  </si>
-  <si>
-    <t>môrlas</t>
-  </si>
-  <si>
-    <t>wrong</t>
-  </si>
-  <si>
-    <t>môth</t>
-  </si>
-  <si>
-    <t>wraith</t>
-  </si>
-  <si>
-    <t>mrônan</t>
-  </si>
-  <si>
-    <t>to kiss passionately</t>
-  </si>
-  <si>
-    <t>mrûne</t>
-  </si>
-  <si>
-    <t>hungry</t>
-  </si>
-  <si>
-    <t>mûiral</t>
-  </si>
-  <si>
-    <t>armor, armour</t>
-  </si>
-  <si>
-    <t>munas</t>
-  </si>
-  <si>
-    <t>sleepy, tired, drowsy</t>
-  </si>
-  <si>
-    <t>mûr</t>
-  </si>
-  <si>
-    <t>basin, sink</t>
-  </si>
-  <si>
-    <t>mŷcûl</t>
-  </si>
-  <si>
-    <t>witch, hag</t>
-  </si>
-  <si>
-    <t>mŷl</t>
-  </si>
-  <si>
-    <t>gull, seagull</t>
-  </si>
-  <si>
-    <t>na</t>
-  </si>
-  <si>
-    <t>to be (verb group b)</t>
-  </si>
-  <si>
-    <t>naben</t>
-  </si>
-  <si>
-    <t>to take, to get</t>
-  </si>
-  <si>
-    <t>nacen</t>
-  </si>
-  <si>
-    <t>to chop, to slice</t>
-  </si>
-  <si>
-    <t>naese</t>
-  </si>
-  <si>
-    <t>leg</t>
-  </si>
-  <si>
-    <t>nagwa</t>
-  </si>
-  <si>
-    <t>scar</t>
-  </si>
-  <si>
-    <t>naie</t>
-  </si>
-  <si>
-    <t>here</t>
-  </si>
-  <si>
-    <t>nail</t>
-  </si>
-  <si>
-    <t>piece, part</t>
-  </si>
-  <si>
-    <t>naimash</t>
-  </si>
-  <si>
-    <t>to worry</t>
   </si>
   <si>
     <t>nalash</t>
@@ -6663,28 +6663,25 @@
     <t>never ends a syllable</t>
   </si>
   <si>
-    <t>k</t>
+    <t>/l/</t>
+  </si>
+  <si>
+    <t>/m/</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>/n/</t>
+  </si>
+  <si>
+    <t>ŋ</t>
+  </si>
+  <si>
+    <t>/ŋ/</t>
   </si>
   <si>
     <t>never begins a syllable</t>
-  </si>
-  <si>
-    <t>/l/</t>
-  </si>
-  <si>
-    <t>/m/</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>/n/</t>
-  </si>
-  <si>
-    <t>ŋ</t>
-  </si>
-  <si>
-    <t>/ŋ/</t>
   </si>
   <si>
     <t>p</t>
@@ -11818,13 +11815,13 @@
       <c r="G305" s="2"/>
     </row>
     <row r="306" ht="22.5" customHeight="1">
-      <c r="A306" s="9" t="s">
+      <c r="A306" s="11" t="s">
         <v>636</v>
       </c>
       <c r="B306" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C306" s="6" t="s">
+      <c r="C306" s="12" t="s">
         <v>637</v>
       </c>
       <c r="D306" s="2"/>
@@ -11834,13 +11831,13 @@
     </row>
     <row r="307" ht="22.5" customHeight="1">
       <c r="A307" s="11" t="s">
-        <v>638</v>
+        <v>515</v>
       </c>
       <c r="B307" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C307" s="12" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D307" s="2"/>
       <c r="E307" s="2"/>
@@ -11848,14 +11845,14 @@
       <c r="G307" s="2"/>
     </row>
     <row r="308" ht="22.5" customHeight="1">
-      <c r="A308" s="11" t="s">
+      <c r="A308" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C308" s="6" t="s">
         <v>640</v>
-      </c>
-      <c r="B308" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C308" s="12" t="s">
-        <v>641</v>
       </c>
       <c r="D308" s="2"/>
       <c r="E308" s="2"/>
@@ -11864,10 +11861,10 @@
     </row>
     <row r="309" ht="22.5" customHeight="1">
       <c r="A309" s="11" t="s">
-        <v>515</v>
+        <v>641</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="C309" s="12" t="s">
         <v>642</v>
@@ -11878,13 +11875,13 @@
       <c r="G309" s="2"/>
     </row>
     <row r="310" ht="22.5" customHeight="1">
-      <c r="A310" s="4" t="s">
+      <c r="A310" s="11" t="s">
         <v>643</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C310" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C310" s="12" t="s">
         <v>644</v>
       </c>
       <c r="D310" s="2"/>
@@ -11893,13 +11890,13 @@
       <c r="G310" s="2"/>
     </row>
     <row r="311" ht="22.5" customHeight="1">
-      <c r="A311" s="11" t="s">
+      <c r="A311" s="4" t="s">
         <v>645</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C311" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C311" s="6" t="s">
         <v>646</v>
       </c>
       <c r="D311" s="2"/>
@@ -11908,13 +11905,13 @@
       <c r="G311" s="2"/>
     </row>
     <row r="312" ht="22.5" customHeight="1">
-      <c r="A312" s="11" t="s">
+      <c r="A312" s="9" t="s">
         <v>647</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C312" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C312" s="10" t="s">
         <v>648</v>
       </c>
       <c r="D312" s="2"/>
@@ -11923,7 +11920,7 @@
       <c r="G312" s="2"/>
     </row>
     <row r="313" ht="22.5" customHeight="1">
-      <c r="A313" s="4" t="s">
+      <c r="A313" s="9" t="s">
         <v>649</v>
       </c>
       <c r="B313" s="5" t="s">
@@ -11942,7 +11939,7 @@
         <v>651</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C314" s="10" t="s">
         <v>652</v>
@@ -11959,7 +11956,7 @@
       <c r="B315" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C315" s="6" t="s">
+      <c r="C315" s="10" t="s">
         <v>654</v>
       </c>
       <c r="D315" s="2"/>
@@ -11968,13 +11965,13 @@
       <c r="G315" s="2"/>
     </row>
     <row r="316" ht="22.5" customHeight="1">
-      <c r="A316" s="9" t="s">
+      <c r="A316" s="11" t="s">
         <v>655</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C316" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C316" s="12" t="s">
         <v>656</v>
       </c>
       <c r="D316" s="2"/>
@@ -11983,11 +11980,11 @@
       <c r="G316" s="2"/>
     </row>
     <row r="317" ht="22.5" customHeight="1">
-      <c r="A317" s="9" t="s">
+      <c r="A317" s="11" t="s">
         <v>657</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C317" s="10" t="s">
         <v>658</v>
@@ -11998,13 +11995,13 @@
       <c r="G317" s="2"/>
     </row>
     <row r="318" ht="22.5" customHeight="1">
-      <c r="A318" s="11" t="s">
+      <c r="A318" s="9" t="s">
         <v>659</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C318" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C318" s="10" t="s">
         <v>660</v>
       </c>
       <c r="D318" s="2"/>
@@ -12017,9 +12014,9 @@
         <v>661</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C319" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C319" s="12" t="s">
         <v>662</v>
       </c>
       <c r="D319" s="2"/>
@@ -12043,13 +12040,13 @@
       <c r="G320" s="2"/>
     </row>
     <row r="321" ht="22.5" customHeight="1">
-      <c r="A321" s="11" t="s">
+      <c r="A321" s="9" t="s">
         <v>665</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C321" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C321" s="10" t="s">
         <v>666</v>
       </c>
       <c r="D321" s="2"/>
@@ -12058,13 +12055,13 @@
       <c r="G321" s="2"/>
     </row>
     <row r="322" ht="22.5" customHeight="1">
-      <c r="A322" s="9" t="s">
+      <c r="A322" s="11" t="s">
         <v>667</v>
       </c>
       <c r="B322" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C322" s="10" t="s">
+      <c r="C322" s="12" t="s">
         <v>668</v>
       </c>
       <c r="D322" s="2"/>
@@ -12088,13 +12085,13 @@
       <c r="G323" s="2"/>
     </row>
     <row r="324" ht="22.5" customHeight="1">
-      <c r="A324" s="11" t="s">
+      <c r="A324" s="9" t="s">
         <v>671</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C324" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C324" s="10" t="s">
         <v>672</v>
       </c>
       <c r="D324" s="2"/>
@@ -12107,7 +12104,7 @@
         <v>673</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C325" s="10" t="s">
         <v>674</v>
@@ -12118,13 +12115,13 @@
       <c r="G325" s="2"/>
     </row>
     <row r="326" ht="22.5" customHeight="1">
-      <c r="A326" s="9" t="s">
+      <c r="A326" s="4" t="s">
         <v>675</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C326" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C326" s="6" t="s">
         <v>676</v>
       </c>
       <c r="D326" s="2"/>
@@ -12133,13 +12130,13 @@
       <c r="G326" s="2"/>
     </row>
     <row r="327" ht="22.5" customHeight="1">
-      <c r="A327" s="9" t="s">
+      <c r="A327" s="4" t="s">
         <v>677</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C327" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="C327" s="6" t="s">
         <v>678</v>
       </c>
       <c r="D327" s="2"/>
@@ -12152,7 +12149,7 @@
         <v>679</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="C328" s="6" t="s">
         <v>680</v>
@@ -12167,7 +12164,7 @@
         <v>681</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>288</v>
+        <v>20</v>
       </c>
       <c r="C329" s="6" t="s">
         <v>682</v>
@@ -12182,7 +12179,7 @@
         <v>683</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="C330" s="6" t="s">
         <v>684</v>
@@ -12193,13 +12190,13 @@
       <c r="G330" s="2"/>
     </row>
     <row r="331" ht="22.5" customHeight="1">
-      <c r="A331" s="4" t="s">
+      <c r="A331" s="9" t="s">
         <v>685</v>
       </c>
       <c r="B331" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C331" s="6" t="s">
+      <c r="C331" s="10" t="s">
         <v>686</v>
       </c>
       <c r="D331" s="2"/>
@@ -12223,13 +12220,13 @@
       <c r="G332" s="2"/>
     </row>
     <row r="333" ht="22.5" customHeight="1">
-      <c r="A333" s="9" t="s">
+      <c r="A333" s="4" t="s">
         <v>689</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C333" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C333" s="6" t="s">
         <v>690</v>
       </c>
       <c r="D333" s="2"/>
@@ -12238,13 +12235,13 @@
       <c r="G333" s="2"/>
     </row>
     <row r="334" ht="22.5" customHeight="1">
-      <c r="A334" s="4" t="s">
+      <c r="A334" s="9" t="s">
         <v>691</v>
       </c>
       <c r="B334" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C334" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C334" s="10" t="s">
         <v>692</v>
       </c>
       <c r="D334" s="2"/>
@@ -12268,13 +12265,13 @@
       <c r="G335" s="2"/>
     </row>
     <row r="336" ht="22.5" customHeight="1">
-      <c r="A336" s="9" t="s">
+      <c r="A336" s="4" t="s">
         <v>695</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C336" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C336" s="6" t="s">
         <v>696</v>
       </c>
       <c r="D336" s="2"/>
@@ -12283,13 +12280,13 @@
       <c r="G336" s="2"/>
     </row>
     <row r="337" ht="22.5" customHeight="1">
-      <c r="A337" s="4" t="s">
+      <c r="A337" s="9" t="s">
         <v>697</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C337" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C337" s="10" t="s">
         <v>698</v>
       </c>
       <c r="D337" s="2"/>
@@ -12302,7 +12299,7 @@
         <v>699</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>45</v>
+        <v>400</v>
       </c>
       <c r="C338" s="6" t="s">
         <v>700</v>
@@ -12313,13 +12310,13 @@
       <c r="G338" s="2"/>
     </row>
     <row r="339" ht="22.5" customHeight="1">
-      <c r="A339" s="9" t="s">
+      <c r="A339" s="4" t="s">
         <v>701</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C339" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C339" s="6" t="s">
         <v>702</v>
       </c>
       <c r="D339" s="2"/>
@@ -12328,13 +12325,13 @@
       <c r="G339" s="2"/>
     </row>
     <row r="340" ht="22.5" customHeight="1">
-      <c r="A340" s="4" t="s">
+      <c r="A340" s="9" t="s">
         <v>703</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="C340" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C340" s="10" t="s">
         <v>704</v>
       </c>
       <c r="D340" s="2"/>
@@ -12343,13 +12340,13 @@
       <c r="G340" s="2"/>
     </row>
     <row r="341" ht="22.5" customHeight="1">
-      <c r="A341" s="4" t="s">
+      <c r="A341" s="9" t="s">
         <v>705</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C341" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C341" s="10" t="s">
         <v>706</v>
       </c>
       <c r="D341" s="2"/>
@@ -12362,9 +12359,9 @@
         <v>707</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C342" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C342" s="6" t="s">
         <v>708</v>
       </c>
       <c r="D342" s="2"/>
@@ -12373,13 +12370,13 @@
       <c r="G342" s="2"/>
     </row>
     <row r="343" ht="22.5" customHeight="1">
-      <c r="A343" s="9" t="s">
+      <c r="A343" s="4" t="s">
         <v>709</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C343" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C343" s="6" t="s">
         <v>710</v>
       </c>
       <c r="D343" s="2"/>
@@ -12388,7 +12385,7 @@
       <c r="G343" s="2"/>
     </row>
     <row r="344" ht="22.5" customHeight="1">
-      <c r="A344" s="9" t="s">
+      <c r="A344" s="4" t="s">
         <v>711</v>
       </c>
       <c r="B344" s="5" t="s">
@@ -12403,11 +12400,11 @@
       <c r="G344" s="2"/>
     </row>
     <row r="345" ht="22.5" customHeight="1">
-      <c r="A345" s="4" t="s">
+      <c r="A345" s="9" t="s">
         <v>713</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>24</v>
+        <v>288</v>
       </c>
       <c r="C345" s="6" t="s">
         <v>714</v>
@@ -12422,7 +12419,7 @@
         <v>715</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C346" s="6" t="s">
         <v>716</v>
@@ -12433,11 +12430,11 @@
       <c r="G346" s="2"/>
     </row>
     <row r="347" ht="22.5" customHeight="1">
-      <c r="A347" s="9" t="s">
+      <c r="A347" s="4" t="s">
         <v>717</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>288</v>
+        <v>119</v>
       </c>
       <c r="C347" s="6" t="s">
         <v>718</v>
@@ -12452,10 +12449,10 @@
         <v>719</v>
       </c>
       <c r="B348" s="5" t="s">
-        <v>45</v>
+        <v>720</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D348" s="2"/>
       <c r="E348" s="2"/>
@@ -12463,14 +12460,14 @@
       <c r="G348" s="2"/>
     </row>
     <row r="349" ht="22.5" customHeight="1">
-      <c r="A349" s="4" t="s">
-        <v>721</v>
+      <c r="A349" s="9" t="s">
+        <v>722</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C349" s="6" t="s">
-        <v>722</v>
+        <v>9</v>
+      </c>
+      <c r="C349" s="10" t="s">
+        <v>723</v>
       </c>
       <c r="D349" s="2"/>
       <c r="E349" s="2"/>
@@ -12479,10 +12476,10 @@
     </row>
     <row r="350" ht="22.5" customHeight="1">
       <c r="A350" s="4" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>724</v>
+        <v>288</v>
       </c>
       <c r="C350" s="6" t="s">
         <v>725</v>
@@ -12493,13 +12490,13 @@
       <c r="G350" s="2"/>
     </row>
     <row r="351" ht="22.5" customHeight="1">
-      <c r="A351" s="9" t="s">
+      <c r="A351" s="4" t="s">
         <v>726</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C351" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C351" s="6" t="s">
         <v>727</v>
       </c>
       <c r="D351" s="2"/>
@@ -12508,13 +12505,13 @@
       <c r="G351" s="2"/>
     </row>
     <row r="352" ht="22.5" customHeight="1">
-      <c r="A352" s="4" t="s">
+      <c r="A352" s="9" t="s">
         <v>728</v>
       </c>
       <c r="B352" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="C352" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C352" s="10" t="s">
         <v>729</v>
       </c>
       <c r="D352" s="2"/>
@@ -12527,7 +12524,7 @@
         <v>730</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C353" s="6" t="s">
         <v>731</v>
@@ -12538,13 +12535,13 @@
       <c r="G353" s="2"/>
     </row>
     <row r="354" ht="22.5" customHeight="1">
-      <c r="A354" s="9" t="s">
+      <c r="A354" s="4" t="s">
         <v>732</v>
       </c>
       <c r="B354" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C354" s="10" t="s">
+      <c r="C354" s="6" t="s">
         <v>733</v>
       </c>
       <c r="D354" s="2"/>
@@ -12557,7 +12554,7 @@
         <v>734</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="C355" s="6" t="s">
         <v>735</v>
@@ -12572,7 +12569,7 @@
         <v>736</v>
       </c>
       <c r="B356" s="5" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C356" s="6" t="s">
         <v>737</v>
@@ -12602,7 +12599,7 @@
         <v>740</v>
       </c>
       <c r="B358" s="5" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C358" s="6" t="s">
         <v>741</v>
@@ -12617,9 +12614,9 @@
         <v>742</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C359" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C359" s="10" t="s">
         <v>743</v>
       </c>
       <c r="D359" s="2"/>
@@ -12632,7 +12629,7 @@
         <v>744</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C360" s="6" t="s">
         <v>745</v>
@@ -12643,11 +12640,11 @@
       <c r="G360" s="2"/>
     </row>
     <row r="361" ht="22.5" customHeight="1">
-      <c r="A361" s="4" t="s">
+      <c r="A361" s="9" t="s">
         <v>746</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C361" s="10" t="s">
         <v>747</v>
@@ -12688,13 +12685,13 @@
       <c r="G363" s="2"/>
     </row>
     <row r="364" ht="22.5" customHeight="1">
-      <c r="A364" s="4" t="s">
+      <c r="A364" s="9" t="s">
         <v>752</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C364" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C364" s="10" t="s">
         <v>753</v>
       </c>
       <c r="D364" s="2"/>
@@ -12703,13 +12700,13 @@
       <c r="G364" s="2"/>
     </row>
     <row r="365" ht="22.5" customHeight="1">
-      <c r="A365" s="9" t="s">
+      <c r="A365" s="4" t="s">
         <v>754</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C365" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C365" s="6" t="s">
         <v>755</v>
       </c>
       <c r="D365" s="2"/>
@@ -12718,13 +12715,13 @@
       <c r="G365" s="2"/>
     </row>
     <row r="366" ht="22.5" customHeight="1">
-      <c r="A366" s="9" t="s">
+      <c r="A366" s="4" t="s">
         <v>756</v>
       </c>
       <c r="B366" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C366" s="10" t="s">
+      <c r="C366" s="6" t="s">
         <v>757</v>
       </c>
       <c r="D366" s="2"/>
@@ -12737,7 +12734,7 @@
         <v>758</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C367" s="6" t="s">
         <v>759</v>
@@ -12752,7 +12749,7 @@
         <v>760</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="C368" s="6" t="s">
         <v>761</v>
@@ -12767,7 +12764,7 @@
         <v>762</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="C369" s="6" t="s">
         <v>763</v>
@@ -12782,7 +12779,7 @@
         <v>764</v>
       </c>
       <c r="B370" s="5" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C370" s="6" t="s">
         <v>765</v>
@@ -12793,13 +12790,13 @@
       <c r="G370" s="2"/>
     </row>
     <row r="371" ht="22.5" customHeight="1">
-      <c r="A371" s="4" t="s">
+      <c r="A371" s="9" t="s">
         <v>766</v>
       </c>
       <c r="B371" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C371" s="6" t="s">
+      <c r="C371" s="10" t="s">
         <v>767</v>
       </c>
       <c r="D371" s="2"/>
@@ -12808,7 +12805,7 @@
       <c r="G371" s="2"/>
     </row>
     <row r="372" ht="22.5" customHeight="1">
-      <c r="A372" s="4" t="s">
+      <c r="A372" s="11" t="s">
         <v>768</v>
       </c>
       <c r="B372" s="5" t="s">
@@ -12827,9 +12824,9 @@
         <v>770</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C373" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C373" s="6" t="s">
         <v>771</v>
       </c>
       <c r="D373" s="2"/>
@@ -12838,11 +12835,11 @@
       <c r="G373" s="2"/>
     </row>
     <row r="374" ht="22.5" customHeight="1">
-      <c r="A374" s="11" t="s">
+      <c r="A374" s="4" t="s">
         <v>772</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C374" s="6" t="s">
         <v>773</v>
@@ -12853,7 +12850,7 @@
       <c r="G374" s="2"/>
     </row>
     <row r="375" ht="22.5" customHeight="1">
-      <c r="A375" s="9" t="s">
+      <c r="A375" s="4" t="s">
         <v>774</v>
       </c>
       <c r="B375" s="5" t="s">
@@ -12872,7 +12869,7 @@
         <v>776</v>
       </c>
       <c r="B376" s="5" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C376" s="6" t="s">
         <v>777</v>
@@ -12883,13 +12880,13 @@
       <c r="G376" s="2"/>
     </row>
     <row r="377" ht="22.5" customHeight="1">
-      <c r="A377" s="4" t="s">
+      <c r="A377" s="9" t="s">
         <v>778</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C377" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C377" s="10" t="s">
         <v>779</v>
       </c>
       <c r="D377" s="2"/>
@@ -12898,11 +12895,11 @@
       <c r="G377" s="2"/>
     </row>
     <row r="378" ht="22.5" customHeight="1">
-      <c r="A378" s="4" t="s">
+      <c r="A378" s="9" t="s">
         <v>780</v>
       </c>
       <c r="B378" s="5" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="C378" s="6" t="s">
         <v>781</v>
@@ -12913,13 +12910,13 @@
       <c r="G378" s="2"/>
     </row>
     <row r="379" ht="22.5" customHeight="1">
-      <c r="A379" s="9" t="s">
+      <c r="A379" s="4" t="s">
         <v>782</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C379" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C379" s="6" t="s">
         <v>783</v>
       </c>
       <c r="D379" s="2"/>
@@ -12932,9 +12929,9 @@
         <v>784</v>
       </c>
       <c r="B380" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C380" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C380" s="10" t="s">
         <v>785</v>
       </c>
       <c r="D380" s="2"/>
@@ -12947,7 +12944,7 @@
         <v>786</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C381" s="6" t="s">
         <v>787</v>
@@ -12973,13 +12970,13 @@
       <c r="G382" s="2"/>
     </row>
     <row r="383" ht="22.5" customHeight="1">
-      <c r="A383" s="4" t="s">
+      <c r="A383" s="9" t="s">
         <v>790</v>
       </c>
       <c r="B383" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C383" s="6" t="s">
+      <c r="C383" s="10" t="s">
         <v>791</v>
       </c>
       <c r="D383" s="2"/>
@@ -12988,13 +12985,13 @@
       <c r="G383" s="2"/>
     </row>
     <row r="384" ht="22.5" customHeight="1">
-      <c r="A384" s="9" t="s">
+      <c r="A384" s="4" t="s">
         <v>792</v>
       </c>
       <c r="B384" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C384" s="10" t="s">
+      <c r="C384" s="6" t="s">
         <v>793</v>
       </c>
       <c r="D384" s="2"/>
@@ -13003,13 +13000,13 @@
       <c r="G384" s="2"/>
     </row>
     <row r="385" ht="22.5" customHeight="1">
-      <c r="A385" s="9" t="s">
+      <c r="A385" s="4" t="s">
         <v>794</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C385" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C385" s="6" t="s">
         <v>795</v>
       </c>
       <c r="D385" s="2"/>
@@ -13018,13 +13015,13 @@
       <c r="G385" s="2"/>
     </row>
     <row r="386" ht="22.5" customHeight="1">
-      <c r="A386" s="4" t="s">
+      <c r="A386" s="9" t="s">
         <v>796</v>
       </c>
       <c r="B386" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C386" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C386" s="10" t="s">
         <v>797</v>
       </c>
       <c r="D386" s="2"/>
@@ -13033,13 +13030,13 @@
       <c r="G386" s="2"/>
     </row>
     <row r="387" ht="22.5" customHeight="1">
-      <c r="A387" s="4" t="s">
+      <c r="A387" s="9" t="s">
         <v>798</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C387" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C387" s="10" t="s">
         <v>799</v>
       </c>
       <c r="D387" s="2"/>
@@ -13048,13 +13045,13 @@
       <c r="G387" s="2"/>
     </row>
     <row r="388" ht="22.5" customHeight="1">
-      <c r="A388" s="9" t="s">
+      <c r="A388" s="4" t="s">
         <v>800</v>
       </c>
       <c r="B388" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C388" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C388" s="6" t="s">
         <v>801</v>
       </c>
       <c r="D388" s="2"/>
@@ -13063,13 +13060,13 @@
       <c r="G388" s="2"/>
     </row>
     <row r="389" ht="22.5" customHeight="1">
-      <c r="A389" s="9" t="s">
+      <c r="A389" s="4" t="s">
         <v>802</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C389" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C389" s="6" t="s">
         <v>803</v>
       </c>
       <c r="D389" s="2"/>
@@ -13082,7 +13079,7 @@
         <v>804</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C390" s="6" t="s">
         <v>805</v>
@@ -13097,7 +13094,7 @@
         <v>806</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="C391" s="6" t="s">
         <v>807</v>
@@ -13127,7 +13124,7 @@
         <v>810</v>
       </c>
       <c r="B393" s="5" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="C393" s="6" t="s">
         <v>811</v>
@@ -13142,7 +13139,7 @@
         <v>812</v>
       </c>
       <c r="B394" s="5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C394" s="6" t="s">
         <v>813</v>
@@ -13172,7 +13169,7 @@
         <v>816</v>
       </c>
       <c r="B396" s="5" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C396" s="6" t="s">
         <v>817</v>
@@ -13187,7 +13184,7 @@
         <v>818</v>
       </c>
       <c r="B397" s="5" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C397" s="6" t="s">
         <v>819</v>
@@ -13202,7 +13199,7 @@
         <v>820</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C398" s="6" t="s">
         <v>821</v>
@@ -13213,13 +13210,13 @@
       <c r="G398" s="2"/>
     </row>
     <row r="399" ht="22.5" customHeight="1">
-      <c r="A399" s="4" t="s">
+      <c r="A399" s="9" t="s">
         <v>822</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C399" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C399" s="10" t="s">
         <v>823</v>
       </c>
       <c r="D399" s="2"/>
@@ -13243,13 +13240,13 @@
       <c r="G400" s="2"/>
     </row>
     <row r="401" ht="22.5" customHeight="1">
-      <c r="A401" s="9" t="s">
+      <c r="A401" s="4" t="s">
         <v>826</v>
       </c>
       <c r="B401" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C401" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C401" s="6" t="s">
         <v>827</v>
       </c>
       <c r="D401" s="2"/>
@@ -13262,9 +13259,9 @@
         <v>828</v>
       </c>
       <c r="B402" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C402" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C402" s="10" t="s">
         <v>829</v>
       </c>
       <c r="D402" s="2"/>
@@ -13273,7 +13270,7 @@
       <c r="G402" s="2"/>
     </row>
     <row r="403" ht="22.5" customHeight="1">
-      <c r="A403" s="4" t="s">
+      <c r="A403" s="9" t="s">
         <v>830</v>
       </c>
       <c r="B403" s="5" t="s">
@@ -13288,13 +13285,13 @@
       <c r="G403" s="2"/>
     </row>
     <row r="404" ht="22.5" customHeight="1">
-      <c r="A404" s="4" t="s">
+      <c r="A404" s="9" t="s">
         <v>832</v>
       </c>
       <c r="B404" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C404" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C404" s="6" t="s">
         <v>833</v>
       </c>
       <c r="D404" s="2"/>
@@ -13307,9 +13304,9 @@
         <v>834</v>
       </c>
       <c r="B405" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C405" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C405" s="10" t="s">
         <v>835</v>
       </c>
       <c r="D405" s="2"/>
@@ -13322,9 +13319,9 @@
         <v>836</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C406" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C406" s="10" t="s">
         <v>837</v>
       </c>
       <c r="D406" s="2"/>
@@ -13333,13 +13330,13 @@
       <c r="G406" s="2"/>
     </row>
     <row r="407" ht="22.5" customHeight="1">
-      <c r="A407" s="9" t="s">
+      <c r="A407" s="11" t="s">
         <v>838</v>
       </c>
       <c r="B407" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C407" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C407" s="12" t="s">
         <v>839</v>
       </c>
       <c r="D407" s="2"/>
@@ -13348,13 +13345,13 @@
       <c r="G407" s="2"/>
     </row>
     <row r="408" ht="22.5" customHeight="1">
-      <c r="A408" s="9" t="s">
+      <c r="A408" s="11" t="s">
         <v>840</v>
       </c>
       <c r="B408" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C408" s="10" t="s">
+      <c r="C408" s="6" t="s">
         <v>841</v>
       </c>
       <c r="D408" s="2"/>
@@ -13363,13 +13360,13 @@
       <c r="G408" s="2"/>
     </row>
     <row r="409" ht="22.5" customHeight="1">
-      <c r="A409" s="11" t="s">
+      <c r="A409" s="9" t="s">
         <v>842</v>
       </c>
       <c r="B409" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C409" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C409" s="6" t="s">
         <v>843</v>
       </c>
       <c r="D409" s="2"/>
@@ -13378,11 +13375,11 @@
       <c r="G409" s="2"/>
     </row>
     <row r="410" ht="22.5" customHeight="1">
-      <c r="A410" s="11" t="s">
+      <c r="A410" s="9" t="s">
         <v>844</v>
       </c>
       <c r="B410" s="5" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C410" s="6" t="s">
         <v>845</v>
@@ -13397,7 +13394,7 @@
         <v>846</v>
       </c>
       <c r="B411" s="5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C411" s="6" t="s">
         <v>847</v>
@@ -13408,11 +13405,11 @@
       <c r="G411" s="2"/>
     </row>
     <row r="412" ht="22.5" customHeight="1">
-      <c r="A412" s="9" t="s">
+      <c r="A412" s="4" t="s">
         <v>848</v>
       </c>
       <c r="B412" s="5" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C412" s="6" t="s">
         <v>849</v>
@@ -13423,11 +13420,11 @@
       <c r="G412" s="2"/>
     </row>
     <row r="413" ht="22.5" customHeight="1">
-      <c r="A413" s="9" t="s">
+      <c r="A413" s="4" t="s">
         <v>850</v>
       </c>
       <c r="B413" s="5" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C413" s="6" t="s">
         <v>851</v>
@@ -13438,11 +13435,11 @@
       <c r="G413" s="2"/>
     </row>
     <row r="414" ht="22.5" customHeight="1">
-      <c r="A414" s="4" t="s">
+      <c r="A414" s="9" t="s">
         <v>852</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>20</v>
+        <v>288</v>
       </c>
       <c r="C414" s="6" t="s">
         <v>853</v>
@@ -13453,11 +13450,11 @@
       <c r="G414" s="2"/>
     </row>
     <row r="415" ht="22.5" customHeight="1">
-      <c r="A415" s="4" t="s">
+      <c r="A415" s="9" t="s">
         <v>854</v>
       </c>
       <c r="B415" s="5" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
       <c r="C415" s="6" t="s">
         <v>855</v>
@@ -13472,9 +13469,9 @@
         <v>856</v>
       </c>
       <c r="B416" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="C416" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C416" s="10" t="s">
         <v>857</v>
       </c>
       <c r="D416" s="2"/>
@@ -13487,7 +13484,7 @@
         <v>858</v>
       </c>
       <c r="B417" s="5" t="s">
-        <v>288</v>
+        <v>45</v>
       </c>
       <c r="C417" s="6" t="s">
         <v>859</v>
@@ -13502,9 +13499,9 @@
         <v>860</v>
       </c>
       <c r="B418" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C418" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C418" s="6" t="s">
         <v>861</v>
       </c>
       <c r="D418" s="2"/>
@@ -13517,7 +13514,7 @@
         <v>862</v>
       </c>
       <c r="B419" s="5" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C419" s="6" t="s">
         <v>863</v>
@@ -13532,7 +13529,7 @@
         <v>864</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C420" s="6" t="s">
         <v>865</v>
@@ -13543,13 +13540,13 @@
       <c r="G420" s="2"/>
     </row>
     <row r="421" ht="22.5" customHeight="1">
-      <c r="A421" s="9" t="s">
+      <c r="A421" s="4" t="s">
         <v>866</v>
       </c>
       <c r="B421" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C421" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C421" s="12" t="s">
         <v>867</v>
       </c>
       <c r="D421" s="2"/>
@@ -13562,9 +13559,9 @@
         <v>868</v>
       </c>
       <c r="B422" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C422" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C422" s="10" t="s">
         <v>869</v>
       </c>
       <c r="D422" s="2"/>
@@ -13573,13 +13570,13 @@
       <c r="G422" s="2"/>
     </row>
     <row r="423" ht="22.5" customHeight="1">
-      <c r="A423" s="4" t="s">
+      <c r="A423" s="9" t="s">
         <v>870</v>
       </c>
       <c r="B423" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C423" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C423" s="10" t="s">
         <v>871</v>
       </c>
       <c r="D423" s="2"/>
@@ -13592,9 +13589,9 @@
         <v>872</v>
       </c>
       <c r="B424" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C424" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C424" s="6" t="s">
         <v>873</v>
       </c>
       <c r="D424" s="2"/>
@@ -13607,9 +13604,9 @@
         <v>874</v>
       </c>
       <c r="B425" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C425" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C425" s="6" t="s">
         <v>875</v>
       </c>
       <c r="D425" s="2"/>
@@ -13622,9 +13619,9 @@
         <v>876</v>
       </c>
       <c r="B426" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C426" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C426" s="10" t="s">
         <v>877</v>
       </c>
       <c r="D426" s="2"/>
@@ -13633,13 +13630,13 @@
       <c r="G426" s="2"/>
     </row>
     <row r="427" ht="22.5" customHeight="1">
-      <c r="A427" s="9" t="s">
+      <c r="A427" s="11" t="s">
         <v>878</v>
       </c>
       <c r="B427" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C427" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C427" s="10" t="s">
         <v>879</v>
       </c>
       <c r="D427" s="2"/>
@@ -13663,11 +13660,11 @@
       <c r="G428" s="2"/>
     </row>
     <row r="429" ht="22.5" customHeight="1">
-      <c r="A429" s="11" t="s">
+      <c r="A429" s="9" t="s">
         <v>882</v>
       </c>
       <c r="B429" s="5" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="C429" s="10" t="s">
         <v>883</v>
@@ -13678,11 +13675,11 @@
       <c r="G429" s="2"/>
     </row>
     <row r="430" ht="22.5" customHeight="1">
-      <c r="A430" s="9" t="s">
+      <c r="A430" s="11" t="s">
         <v>884</v>
       </c>
       <c r="B430" s="5" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="C430" s="10" t="s">
         <v>885</v>
@@ -13697,7 +13694,7 @@
         <v>886</v>
       </c>
       <c r="B431" s="5" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C431" s="10" t="s">
         <v>887</v>
@@ -13708,13 +13705,13 @@
       <c r="G431" s="2"/>
     </row>
     <row r="432" ht="22.5" customHeight="1">
-      <c r="A432" s="11" t="s">
+      <c r="A432" s="4" t="s">
         <v>888</v>
       </c>
       <c r="B432" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C432" s="10" t="s">
+      <c r="C432" s="6" t="s">
         <v>889</v>
       </c>
       <c r="D432" s="2"/>
@@ -13729,7 +13726,7 @@
       <c r="B433" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C433" s="10" t="s">
+      <c r="C433" s="6" t="s">
         <v>891</v>
       </c>
       <c r="D433" s="2"/>
@@ -13738,13 +13735,13 @@
       <c r="G433" s="2"/>
     </row>
     <row r="434" ht="22.5" customHeight="1">
-      <c r="A434" s="4" t="s">
+      <c r="A434" s="9" t="s">
         <v>892</v>
       </c>
       <c r="B434" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C434" s="6" t="s">
+      <c r="C434" s="10" t="s">
         <v>893</v>
       </c>
       <c r="D434" s="2"/>
@@ -13753,7 +13750,7 @@
       <c r="G434" s="2"/>
     </row>
     <row r="435" ht="22.5" customHeight="1">
-      <c r="A435" s="9" t="s">
+      <c r="A435" s="4" t="s">
         <v>894</v>
       </c>
       <c r="B435" s="5" t="s">
@@ -13772,9 +13769,9 @@
         <v>896</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C436" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C436" s="6" t="s">
         <v>897</v>
       </c>
       <c r="D436" s="2"/>
@@ -13783,7 +13780,7 @@
       <c r="G436" s="2"/>
     </row>
     <row r="437" ht="22.5" customHeight="1">
-      <c r="A437" s="4" t="s">
+      <c r="A437" s="9" t="s">
         <v>898</v>
       </c>
       <c r="B437" s="5" t="s">
@@ -13802,7 +13799,7 @@
         <v>900</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C438" s="6" t="s">
         <v>901</v>
@@ -13813,11 +13810,11 @@
       <c r="G438" s="2"/>
     </row>
     <row r="439" ht="22.5" customHeight="1">
-      <c r="A439" s="9" t="s">
+      <c r="A439" s="4" t="s">
         <v>902</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C439" s="6" t="s">
         <v>903</v>
@@ -13828,11 +13825,11 @@
       <c r="G439" s="2"/>
     </row>
     <row r="440" ht="22.5" customHeight="1">
-      <c r="A440" s="9" t="s">
+      <c r="A440" s="4" t="s">
         <v>904</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="C440" s="6" t="s">
         <v>905</v>
@@ -13843,13 +13840,13 @@
       <c r="G440" s="2"/>
     </row>
     <row r="441" ht="22.5" customHeight="1">
-      <c r="A441" s="4" t="s">
+      <c r="A441" s="9" t="s">
         <v>906</v>
       </c>
       <c r="B441" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C441" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C441" s="10" t="s">
         <v>907</v>
       </c>
       <c r="D441" s="2"/>
@@ -13858,11 +13855,11 @@
       <c r="G441" s="2"/>
     </row>
     <row r="442" ht="22.5" customHeight="1">
-      <c r="A442" s="4" t="s">
+      <c r="A442" s="9" t="s">
         <v>908</v>
       </c>
       <c r="B442" s="5" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C442" s="6" t="s">
         <v>909</v>
@@ -13877,7 +13874,7 @@
         <v>910</v>
       </c>
       <c r="B443" s="5" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="C443" s="10" t="s">
         <v>911</v>
@@ -13888,13 +13885,13 @@
       <c r="G443" s="2"/>
     </row>
     <row r="444" ht="22.5" customHeight="1">
-      <c r="A444" s="9" t="s">
+      <c r="A444" s="11" t="s">
         <v>912</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C444" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C444" s="10" t="s">
         <v>913</v>
       </c>
       <c r="D444" s="2"/>
@@ -13903,13 +13900,13 @@
       <c r="G444" s="2"/>
     </row>
     <row r="445" ht="22.5" customHeight="1">
-      <c r="A445" s="9" t="s">
+      <c r="A445" s="11" t="s">
         <v>914</v>
       </c>
       <c r="B445" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C445" s="10" t="s">
+      <c r="C445" s="6" t="s">
         <v>915</v>
       </c>
       <c r="D445" s="2"/>
@@ -13922,9 +13919,9 @@
         <v>916</v>
       </c>
       <c r="B446" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C446" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C446" s="6" t="s">
         <v>917</v>
       </c>
       <c r="D446" s="2"/>
@@ -13933,11 +13930,11 @@
       <c r="G446" s="2"/>
     </row>
     <row r="447" ht="22.5" customHeight="1">
-      <c r="A447" s="11" t="s">
+      <c r="A447" s="4" t="s">
         <v>918</v>
       </c>
       <c r="B447" s="5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C447" s="6" t="s">
         <v>919</v>
@@ -13948,11 +13945,11 @@
       <c r="G447" s="2"/>
     </row>
     <row r="448" ht="22.5" customHeight="1">
-      <c r="A448" s="11" t="s">
+      <c r="A448" s="4" t="s">
         <v>920</v>
       </c>
       <c r="B448" s="5" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="C448" s="6" t="s">
         <v>921</v>
@@ -13963,13 +13960,13 @@
       <c r="G448" s="2"/>
     </row>
     <row r="449" ht="22.5" customHeight="1">
-      <c r="A449" s="4" t="s">
+      <c r="A449" s="9" t="s">
         <v>922</v>
       </c>
       <c r="B449" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C449" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C449" s="10" t="s">
         <v>923</v>
       </c>
       <c r="D449" s="2"/>
@@ -13978,11 +13975,11 @@
       <c r="G449" s="2"/>
     </row>
     <row r="450" ht="22.5" customHeight="1">
-      <c r="A450" s="4" t="s">
+      <c r="A450" s="9" t="s">
         <v>924</v>
       </c>
       <c r="B450" s="5" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C450" s="6" t="s">
         <v>925</v>
@@ -13993,13 +13990,13 @@
       <c r="G450" s="2"/>
     </row>
     <row r="451" ht="22.5" customHeight="1">
-      <c r="A451" s="9" t="s">
+      <c r="A451" s="4" t="s">
         <v>926</v>
       </c>
       <c r="B451" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C451" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C451" s="6" t="s">
         <v>927</v>
       </c>
       <c r="D451" s="2"/>
@@ -14012,7 +14009,7 @@
         <v>928</v>
       </c>
       <c r="B452" s="5" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C452" s="6" t="s">
         <v>929</v>
@@ -14027,7 +14024,7 @@
         <v>930</v>
       </c>
       <c r="B453" s="5" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="C453" s="6" t="s">
         <v>931</v>
@@ -14038,11 +14035,11 @@
       <c r="G453" s="2"/>
     </row>
     <row r="454" ht="22.5" customHeight="1">
-      <c r="A454" s="9" t="s">
+      <c r="A454" s="4" t="s">
         <v>932</v>
       </c>
       <c r="B454" s="5" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C454" s="6" t="s">
         <v>933</v>
@@ -14053,11 +14050,11 @@
       <c r="G454" s="2"/>
     </row>
     <row r="455" ht="22.5" customHeight="1">
-      <c r="A455" s="4" t="s">
+      <c r="A455" s="9" t="s">
         <v>934</v>
       </c>
       <c r="B455" s="5" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C455" s="6" t="s">
         <v>935</v>
@@ -14072,7 +14069,7 @@
         <v>936</v>
       </c>
       <c r="B456" s="5" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C456" s="6" t="s">
         <v>937</v>
@@ -14083,11 +14080,11 @@
       <c r="G456" s="2"/>
     </row>
     <row r="457" ht="22.5" customHeight="1">
-      <c r="A457" s="9" t="s">
+      <c r="A457" s="4" t="s">
         <v>938</v>
       </c>
       <c r="B457" s="5" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="C457" s="6" t="s">
         <v>939</v>
@@ -14098,11 +14095,11 @@
       <c r="G457" s="2"/>
     </row>
     <row r="458" ht="22.5" customHeight="1">
-      <c r="A458" s="4" t="s">
+      <c r="A458" s="9" t="s">
         <v>940</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="C458" s="6" t="s">
         <v>941</v>
@@ -14117,7 +14114,7 @@
         <v>942</v>
       </c>
       <c r="B459" s="5" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C459" s="6" t="s">
         <v>943</v>
@@ -14132,7 +14129,7 @@
         <v>944</v>
       </c>
       <c r="B460" s="5" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C460" s="6" t="s">
         <v>945</v>
@@ -14143,11 +14140,11 @@
       <c r="G460" s="2"/>
     </row>
     <row r="461" ht="22.5" customHeight="1">
-      <c r="A461" s="4" t="s">
+      <c r="A461" s="9" t="s">
         <v>946</v>
       </c>
       <c r="B461" s="5" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C461" s="6" t="s">
         <v>947</v>
@@ -14158,11 +14155,11 @@
       <c r="G461" s="2"/>
     </row>
     <row r="462" ht="22.5" customHeight="1">
-      <c r="A462" s="9" t="s">
+      <c r="A462" s="4" t="s">
         <v>948</v>
       </c>
       <c r="B462" s="5" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="C462" s="6" t="s">
         <v>949</v>
@@ -14177,7 +14174,7 @@
         <v>950</v>
       </c>
       <c r="B463" s="5" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C463" s="6" t="s">
         <v>951</v>
@@ -14188,11 +14185,11 @@
       <c r="G463" s="2"/>
     </row>
     <row r="464" ht="22.5" customHeight="1">
-      <c r="A464" s="4" t="s">
+      <c r="A464" s="9" t="s">
         <v>952</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="C464" s="6" t="s">
         <v>953</v>
@@ -14207,9 +14204,9 @@
         <v>954</v>
       </c>
       <c r="B465" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C465" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C465" s="10" t="s">
         <v>955</v>
       </c>
       <c r="D465" s="2"/>
@@ -14222,9 +14219,9 @@
         <v>956</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C466" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C466" s="10" t="s">
         <v>957</v>
       </c>
       <c r="D466" s="2"/>
@@ -14233,13 +14230,13 @@
       <c r="G466" s="2"/>
     </row>
     <row r="467" ht="22.5" customHeight="1">
-      <c r="A467" s="9" t="s">
+      <c r="A467" s="4" t="s">
         <v>958</v>
       </c>
       <c r="B467" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C467" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C467" s="6" t="s">
         <v>959</v>
       </c>
       <c r="D467" s="2"/>
@@ -14248,13 +14245,13 @@
       <c r="G467" s="2"/>
     </row>
     <row r="468" ht="22.5" customHeight="1">
-      <c r="A468" s="9" t="s">
+      <c r="A468" s="4" t="s">
         <v>960</v>
       </c>
       <c r="B468" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C468" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C468" s="6" t="s">
         <v>961</v>
       </c>
       <c r="D468" s="2"/>
@@ -14263,13 +14260,13 @@
       <c r="G468" s="2"/>
     </row>
     <row r="469" ht="22.5" customHeight="1">
-      <c r="A469" s="4" t="s">
+      <c r="A469" s="9" t="s">
         <v>962</v>
       </c>
       <c r="B469" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C469" s="6" t="s">
+      <c r="C469" s="10" t="s">
         <v>963</v>
       </c>
       <c r="D469" s="2"/>
@@ -14278,11 +14275,11 @@
       <c r="G469" s="2"/>
     </row>
     <row r="470" ht="22.5" customHeight="1">
-      <c r="A470" s="4" t="s">
+      <c r="A470" s="9" t="s">
         <v>964</v>
       </c>
       <c r="B470" s="5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C470" s="6" t="s">
         <v>965</v>
@@ -14297,9 +14294,9 @@
         <v>966</v>
       </c>
       <c r="B471" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C471" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C471" s="6" t="s">
         <v>967</v>
       </c>
       <c r="D471" s="2"/>
@@ -14312,7 +14309,7 @@
         <v>968</v>
       </c>
       <c r="B472" s="5" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C472" s="6" t="s">
         <v>969</v>
@@ -14342,7 +14339,7 @@
         <v>972</v>
       </c>
       <c r="B474" s="5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C474" s="6" t="s">
         <v>973</v>
@@ -14357,7 +14354,7 @@
         <v>974</v>
       </c>
       <c r="B475" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C475" s="6" t="s">
         <v>975</v>
@@ -14368,13 +14365,13 @@
       <c r="G475" s="2"/>
     </row>
     <row r="476" ht="22.5" customHeight="1">
-      <c r="A476" s="9" t="s">
+      <c r="A476" s="11" t="s">
         <v>976</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C476" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C476" s="12" t="s">
         <v>977</v>
       </c>
       <c r="D476" s="2"/>
@@ -14387,7 +14384,7 @@
         <v>978</v>
       </c>
       <c r="B477" s="5" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="C477" s="6" t="s">
         <v>979</v>
@@ -14398,13 +14395,13 @@
       <c r="G477" s="2"/>
     </row>
     <row r="478" ht="22.5" customHeight="1">
-      <c r="A478" s="11" t="s">
+      <c r="A478" s="4" t="s">
         <v>980</v>
       </c>
       <c r="B478" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C478" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C478" s="6" t="s">
         <v>981</v>
       </c>
       <c r="D478" s="2"/>
@@ -14447,9 +14444,9 @@
         <v>986</v>
       </c>
       <c r="B481" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C481" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C481" s="10" t="s">
         <v>987</v>
       </c>
       <c r="D481" s="2"/>
@@ -14462,7 +14459,7 @@
         <v>988</v>
       </c>
       <c r="B482" s="5" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="C482" s="6" t="s">
         <v>989</v>
@@ -14477,9 +14474,9 @@
         <v>990</v>
       </c>
       <c r="B483" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C483" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C483" s="6" t="s">
         <v>991</v>
       </c>
       <c r="D483" s="2"/>
@@ -14488,11 +14485,11 @@
       <c r="G483" s="2"/>
     </row>
     <row r="484" ht="22.5" customHeight="1">
-      <c r="A484" s="4" t="s">
+      <c r="A484" s="9" t="s">
         <v>992</v>
       </c>
       <c r="B484" s="5" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C484" s="6" t="s">
         <v>993</v>
@@ -14509,7 +14506,7 @@
       <c r="B485" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C485" s="6" t="s">
+      <c r="C485" s="10" t="s">
         <v>995</v>
       </c>
       <c r="D485" s="2"/>
@@ -14522,7 +14519,7 @@
         <v>996</v>
       </c>
       <c r="B486" s="5" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C486" s="6" t="s">
         <v>997</v>
@@ -14537,7 +14534,7 @@
         <v>998</v>
       </c>
       <c r="B487" s="5" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C487" s="10" t="s">
         <v>999</v>
@@ -14552,7 +14549,7 @@
         <v>1000</v>
       </c>
       <c r="B488" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C488" s="6" t="s">
         <v>1001</v>
@@ -14578,11 +14575,11 @@
       <c r="G489" s="2"/>
     </row>
     <row r="490" ht="22.5" customHeight="1">
-      <c r="A490" s="9" t="s">
+      <c r="A490" s="4" t="s">
         <v>1004</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C490" s="6" t="s">
         <v>1005</v>
@@ -14599,7 +14596,7 @@
       <c r="B491" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C491" s="10" t="s">
+      <c r="C491" s="6" t="s">
         <v>1007</v>
       </c>
       <c r="D491" s="2"/>
@@ -14608,13 +14605,13 @@
       <c r="G491" s="2"/>
     </row>
     <row r="492" ht="22.5" customHeight="1">
-      <c r="A492" s="4" t="s">
+      <c r="A492" s="11" t="s">
         <v>1008</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C492" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C492" s="12" t="s">
         <v>1009</v>
       </c>
       <c r="D492" s="2"/>
@@ -20563,7 +20560,7 @@
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="15" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>1795</v>
@@ -22704,7 +22701,7 @@
         <v>1878</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
@@ -22734,7 +22731,7 @@
         <v>1881</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
@@ -22783,7 +22780,7 @@
         <v>1888</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="G6" s="16" t="s">
         <v>1891</v>
@@ -22816,7 +22813,7 @@
         <v>1894</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
@@ -23342,7 +23339,7 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>1944</v>
@@ -23556,24 +23553,22 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="7" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>1980</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>1967</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>1981</v>
-      </c>
+      <c r="C22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="C23" s="2"/>
       <c r="E23" s="2"/>
@@ -23582,7 +23577,7 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>1822</v>
+        <v>1982</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>1983</v>
@@ -23599,31 +23594,31 @@
       <c r="B25" s="7" t="s">
         <v>1985</v>
       </c>
-      <c r="C25" s="2"/>
+      <c r="C25" s="7" t="s">
+        <v>1986</v>
+      </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>1987</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>1981</v>
-      </c>
+        <v>1988</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="C27" s="2"/>
       <c r="E27" s="2"/>
@@ -23632,7 +23627,7 @@
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>1990</v>
+        <v>1823</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>1991</v>
@@ -23644,10 +23639,10 @@
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>1823</v>
+        <v>1992</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="C29" s="2"/>
       <c r="E29" s="2"/>
@@ -23656,10 +23651,10 @@
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="C30" s="2"/>
       <c r="E30" s="2"/>
@@ -23668,10 +23663,10 @@
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="C31" s="2"/>
       <c r="E31" s="2"/>
@@ -23680,10 +23675,10 @@
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="C32" s="2"/>
       <c r="E32" s="2"/>
@@ -23692,10 +23687,10 @@
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="C33" s="2"/>
       <c r="E33" s="2"/>
@@ -23704,10 +23699,10 @@
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="7" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="C34" s="2"/>
       <c r="E34" s="2"/>
@@ -23716,10 +23711,10 @@
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="C35" s="2"/>
       <c r="E35" s="2"/>
@@ -23727,13 +23722,10 @@
       <c r="G35" s="2"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="7" t="s">
-        <v>2005</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>2006</v>
-      </c>
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
       <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -24305,17 +24297,8 @@
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
     </row>
-    <row r="100" ht="18.75" customHeight="1">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
@@ -24329,16 +24312,15 @@
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -24356,19 +24338,19 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="7" t="s">
+        <v>2006</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>2007</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>2008</v>
       </c>
       <c r="G1" s="2"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="7" t="s">
+        <v>2008</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>2009</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>2010</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -24377,16 +24359,16 @@
         <v>1808</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="G3" s="2"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="7" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>2012</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>2013</v>
       </c>
       <c r="G4" s="2"/>
     </row>
@@ -24395,25 +24377,25 @@
         <v>1799</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="G5" s="2"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="7" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>2015</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>2016</v>
       </c>
       <c r="G6" s="2"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="7" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>2017</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>2018</v>
       </c>
       <c r="G7" s="2"/>
     </row>
@@ -24422,34 +24404,34 @@
         <v>1796</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="G8" s="2"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="7" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>2020</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>2021</v>
       </c>
       <c r="G9" s="2"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="7" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>2022</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>2023</v>
       </c>
       <c r="G10" s="2"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="7" t="s">
+        <v>2023</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>2024</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>2025</v>
       </c>
       <c r="G11" s="2"/>
     </row>
@@ -24467,25 +24449,25 @@
         <v>1805</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G13" s="2"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="7" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>2027</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>2028</v>
       </c>
       <c r="G14" s="2"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="7" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>2029</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>2030</v>
       </c>
       <c r="G15" s="2"/>
     </row>
@@ -24494,7 +24476,7 @@
         <v>1811</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="G16" s="2"/>
     </row>

--- a/Literature/Languages/Ranûdan.xlsx
+++ b/Literature/Languages/Ranûdan.xlsx
@@ -2523,7 +2523,7 @@
     <t>ship</t>
   </si>
   <si>
-    <t>jŷll</t>
+    <t>jŷl</t>
   </si>
   <si>
     <t>dew</t>
@@ -2835,18 +2835,18 @@
     <t>to mix, to blend, to stir</t>
   </si>
   <si>
+    <t>malentie</t>
+  </si>
+  <si>
+    <t>blue poppy (flower)</t>
+  </si>
+  <si>
     <t>malessi</t>
   </si>
   <si>
     <t>mix, blend, concoction; chaotic group, melting pot of things; compilation</t>
   </si>
   <si>
-    <t>mallentie</t>
-  </si>
-  <si>
-    <t>blue poppy (flower)</t>
-  </si>
-  <si>
     <t>malya</t>
   </si>
   <si>
@@ -3207,7 +3207,7 @@
     <t>witch, hag</t>
   </si>
   <si>
-    <t>mŷll</t>
+    <t>mŷl</t>
   </si>
   <si>
     <t>gull, seagull</t>
@@ -4530,7 +4530,7 @@
     <t>type, kind, sort</t>
   </si>
   <si>
-    <t>sŷllae</t>
+    <t>sŷlae</t>
   </si>
   <si>
     <t>swan</t>
@@ -4722,7 +4722,7 @@
     <t>to start, to begin</t>
   </si>
   <si>
-    <t>thellen</t>
+    <t>thelen</t>
   </si>
   <si>
     <t>to find, to look for</t>
@@ -4773,7 +4773,7 @@
     <t>game, sport</t>
   </si>
   <si>
-    <t>thillu</t>
+    <t>thilu</t>
   </si>
   <si>
     <t>far</t>
@@ -4959,7 +4959,7 @@
     <t>moon elf</t>
   </si>
   <si>
-    <t>tŷllai</t>
+    <t>tŷlai</t>
   </si>
   <si>
     <t>music</t>
@@ -5712,7 +5712,7 @@
     <t>to draw</t>
   </si>
   <si>
-    <t>zŷll</t>
+    <t>zŷl</t>
   </si>
   <si>
     <t>drop of liquid</t>
@@ -7228,7 +7228,7 @@
     <t>/l̪/</t>
   </si>
   <si>
-    <t>only when it follows an o or u vowel, followed by a non o or u vowel. can also end a syllable with ŷ like -ŷll</t>
+    <t>only when it follows an o or u vowel, followed by a non o or u vowel</t>
   </si>
   <si>
     <t>/m/</t>
@@ -7324,7 +7324,7 @@
     <t>I can eat glass, it doesn't hurt me.</t>
   </si>
   <si>
-    <t>Sa glame cwen ere thomash, dôre min molie bir na?</t>
+    <t>Sa glame cwen ere thomash, dôre min mollie bir na?</t>
   </si>
   <si>
     <t>I wish to see the king, is he busy?</t>
@@ -7354,7 +7354,7 @@
     <t>Go away.</t>
   </si>
   <si>
-    <t>Shelai tŷllai sa rassil pane.</t>
+    <t>Shelai tŷlai sa rassil pane.</t>
   </si>
   <si>
     <t>The forest has it's own music.</t>

--- a/Literature/Languages/Ranûdan.xlsx
+++ b/Literature/Languages/Ranûdan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3778" uniqueCount="2514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3784" uniqueCount="2520">
   <si>
     <t>Word</t>
   </si>
@@ -8062,28 +8062,46 @@
     <t>/auː/</t>
   </si>
   <si>
+    <t>ir</t>
+  </si>
+  <si>
+    <t>/ɪr/</t>
+  </si>
+  <si>
+    <t>bir /bɪr/</t>
+  </si>
+  <si>
+    <t>ûi</t>
+  </si>
+  <si>
+    <t>/u.ɪ/</t>
+  </si>
+  <si>
+    <t>wi</t>
+  </si>
+  <si>
+    <t>/wɪ/</t>
+  </si>
+  <si>
+    <t>gwin /cwɪn/</t>
+  </si>
+  <si>
+    <t>iô</t>
+  </si>
+  <si>
+    <t>/i.o/</t>
+  </si>
+  <si>
     <t>o</t>
   </si>
   <si>
     <t>/ɔ/</t>
   </si>
   <si>
-    <t>ûi</t>
-  </si>
-  <si>
-    <t>/u.ɪ/</t>
-  </si>
-  <si>
     <t>ô</t>
   </si>
   <si>
     <t>/ouː/</t>
-  </si>
-  <si>
-    <t>iô</t>
-  </si>
-  <si>
-    <t>/i.o/</t>
   </si>
   <si>
     <t>u</t>
@@ -28382,7 +28400,7 @@
       <c r="B6" s="7" t="s">
         <v>2399</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="7"/>
       <c r="D6" s="2"/>
       <c r="E6" s="7" t="s">
         <v>2400</v>
@@ -28400,41 +28418,45 @@
       <c r="B7" s="7" t="s">
         <v>2403</v>
       </c>
-      <c r="C7" s="2"/>
+      <c r="C7" s="7" t="s">
+        <v>2404</v>
+      </c>
       <c r="D7" s="2"/>
       <c r="E7" s="7" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>2407</v>
-      </c>
-      <c r="C8" s="2"/>
+        <v>2408</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>2409</v>
+      </c>
       <c r="D8" s="2"/>
       <c r="E8" s="7" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -28445,10 +28467,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -28459,10 +28481,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -28473,10 +28495,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -28486,8 +28508,12 @@
       <c r="H12" s="2"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
+      <c r="A13" s="7" t="s">
+        <v>2420</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>2421</v>
+      </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -28496,297 +28522,301 @@
       <c r="H13" s="2"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="7" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>2423</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" ht="18.75" customHeight="1">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" ht="18.75" customHeight="1">
+      <c r="A16" s="18" t="s">
         <v>2383</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B16" s="18" t="s">
         <v>2384</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>2418</v>
-      </c>
-      <c r="G14" s="18" t="s">
+      <c r="C16" s="18" t="s">
+        <v>2424</v>
+      </c>
+      <c r="G16" s="18" t="s">
         <v>2237</v>
       </c>
-    </row>
-    <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="7" t="s">
-        <v>2419</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>2420</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="7" t="s">
-        <v>2421</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>2422</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>2423</v>
-      </c>
-      <c r="G16" s="2"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="C17" s="2"/>
       <c r="G17" s="2"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>2427</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>2428</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>2429</v>
+      </c>
       <c r="G18" s="2"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="C19" s="2"/>
       <c r="G19" s="2"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="C20" s="2"/>
       <c r="G20" s="2"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>2433</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>2434</v>
-      </c>
+        <v>2435</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="G21" s="2"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>2195</v>
+        <v>2436</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="C22" s="2"/>
       <c r="G22" s="2"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>2438</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>2439</v>
-      </c>
+        <v>2440</v>
+      </c>
+      <c r="G23" s="2"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="C24" s="2"/>
       <c r="G24" s="2"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>2442</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="G25" s="2"/>
+        <v>2443</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>2444</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>2445</v>
+      </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>2443</v>
+        <v>2197</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>2444</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>2445</v>
-      </c>
+        <v>2446</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="G26" s="2"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="C27" s="2"/>
       <c r="G27" s="2"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>2449</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>2450</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>2451</v>
+      </c>
       <c r="G28" s="2"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>2198</v>
+        <v>2452</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>2450</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>2451</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>2452</v>
-      </c>
+        <v>2453</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="G29" s="2"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="C30" s="2"/>
       <c r="G30" s="2"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>2455</v>
+        <v>2198</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>2456</v>
       </c>
-      <c r="C31" s="2"/>
-      <c r="G31" s="2"/>
+      <c r="C31" s="7" t="s">
+        <v>2457</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>2458</v>
+      </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>2458</v>
+        <v>2460</v>
       </c>
       <c r="C32" s="2"/>
       <c r="G32" s="2"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="C33" s="2"/>
       <c r="G33" s="2"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="7" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
       <c r="C34" s="2"/>
       <c r="G34" s="2"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
       <c r="C35" s="2"/>
       <c r="G35" s="2"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="7" t="s">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="C36" s="2"/>
       <c r="G36" s="2"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="7" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="C37" s="2"/>
       <c r="G37" s="2"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="7" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="C38" s="2"/>
       <c r="G38" s="2"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
+      <c r="A39" s="7" t="s">
+        <v>2473</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>2474</v>
+      </c>
       <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" s="18" t="s">
-        <v>2471</v>
-      </c>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
+      <c r="A40" s="7" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" s="16" t="s">
-        <v>2472</v>
-      </c>
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
@@ -28795,10 +28825,7 @@
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="18" t="s">
-        <v>2473</v>
-      </c>
-      <c r="B42" s="18" t="s">
-        <v>2474</v>
+        <v>2477</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
@@ -28808,10 +28835,7 @@
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B43" s="16" t="s">
-        <v>2475</v>
+        <v>2478</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -28820,11 +28844,11 @@
       <c r="H43" s="2"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
-      <c r="A44" s="16" t="s">
-        <v>2476</v>
-      </c>
-      <c r="B44" s="16" t="s">
-        <v>2477</v>
+      <c r="A44" s="18" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>2480</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
@@ -28834,10 +28858,10 @@
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="16" t="s">
-        <v>295</v>
+        <v>90</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>2478</v>
+        <v>2481</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -28847,10 +28871,10 @@
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="16" t="s">
-        <v>1418</v>
+        <v>2482</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>2479</v>
+        <v>2483</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
@@ -28860,10 +28884,10 @@
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="16" t="s">
-        <v>1432</v>
+        <v>295</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>2480</v>
+        <v>2484</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
@@ -28873,10 +28897,10 @@
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" s="16" t="s">
-        <v>1899</v>
+        <v>1418</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>2481</v>
+        <v>2485</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -28886,10 +28910,10 @@
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" s="16" t="s">
-        <v>556</v>
+        <v>1432</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>2482</v>
+        <v>2486</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -28898,9 +28922,12 @@
       <c r="H49" s="2"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
+      <c r="A50" s="16" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>2487</v>
+      </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
@@ -28908,9 +28935,12 @@
       <c r="H50" s="2"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
+      <c r="A51" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>2488</v>
+      </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -29387,29 +29417,45 @@
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
     </row>
+    <row r="99" ht="18.75" customHeight="1">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+    </row>
+    <row r="100" ht="18.75" customHeight="1">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="C37:F37"/>
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="G38:H38"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="G16:H16"/>
+    <mergeCell ref="C17:F17"/>
     <mergeCell ref="G17:H17"/>
-    <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
     <mergeCell ref="C19:F19"/>
-    <mergeCell ref="G19:H19"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="C21:F21"/>
@@ -29418,12 +29464,12 @@
     <mergeCell ref="G22:H22"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="G23:H23"/>
+    <mergeCell ref="C24:F24"/>
     <mergeCell ref="G24:H24"/>
-    <mergeCell ref="C24:F24"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
     <mergeCell ref="C26:F26"/>
-    <mergeCell ref="G26:H26"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="G27:H27"/>
     <mergeCell ref="C28:F28"/>
@@ -29431,24 +29477,28 @@
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="C30:F30"/>
+    <mergeCell ref="G30:H30"/>
     <mergeCell ref="C31:F31"/>
-    <mergeCell ref="G30:H30"/>
     <mergeCell ref="G31:H31"/>
     <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
     <mergeCell ref="G32:H32"/>
-    <mergeCell ref="C33:F33"/>
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="G34:H34"/>
+    <mergeCell ref="C35:F35"/>
     <mergeCell ref="G35:H35"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="B46:C46"/>
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="B48:C48"/>
     <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -29466,18 +29516,18 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="7" t="s">
-        <v>2483</v>
+        <v>2489</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>2484</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>2485</v>
+        <v>2491</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>2486</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
@@ -29490,10 +29540,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>2487</v>
+        <v>2493</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>2488</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
@@ -29514,15 +29564,15 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>2489</v>
+        <v>2495</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>2490</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>2491</v>
+        <v>2497</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>2140</v>
@@ -29530,58 +29580,58 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>2492</v>
+        <v>2498</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>2493</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>2494</v>
+        <v>2500</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>2495</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>2496</v>
+        <v>2502</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>2497</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>2498</v>
+        <v>2504</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>2499</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>2500</v>
+        <v>2506</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>2501</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>2502</v>
+        <v>2508</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>2503</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>2504</v>
+        <v>2510</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>2505</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="16" ht="18.75" customHeight="1">
@@ -29601,19 +29651,19 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>2506</v>
+        <v>2512</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>2507</v>
+        <v>2513</v>
       </c>
       <c r="G18" s="2"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>2508</v>
+        <v>2514</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>2509</v>
+        <v>2515</v>
       </c>
       <c r="G19" s="2"/>
     </row>
@@ -29634,19 +29684,19 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="10" t="s">
-        <v>2510</v>
+        <v>2516</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>2511</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1"/>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="10" t="s">
-        <v>2512</v>
+        <v>2518</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>2513</v>
+        <v>2519</v>
       </c>
       <c r="G24" s="37"/>
     </row>

--- a/Literature/Languages/Ranûdan.xlsx
+++ b/Literature/Languages/Ranûdan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3856" uniqueCount="2574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3866" uniqueCount="2579">
   <si>
     <t>Word</t>
   </si>
@@ -4272,7 +4272,7 @@
     <t>tavern, restaurant</t>
   </si>
   <si>
-    <t>pessil</t>
+    <t>pesse</t>
   </si>
   <si>
     <t>skin</t>
@@ -4290,1291 +4290,1291 @@
     <t>to taunt, to provoke; to mock</t>
   </si>
   <si>
-    <t>pôl</t>
+    <t>pôlla</t>
+  </si>
+  <si>
+    <t>book</t>
+  </si>
+  <si>
+    <t>pôlômae</t>
+  </si>
+  <si>
+    <t>explosion</t>
+  </si>
+  <si>
+    <t>pôlômash</t>
+  </si>
+  <si>
+    <t>to explode</t>
+  </si>
+  <si>
+    <t>pônu</t>
+  </si>
+  <si>
+    <t>forwards</t>
+  </si>
+  <si>
+    <t>possai</t>
+  </si>
+  <si>
+    <t>many, much, a lot</t>
+  </si>
+  <si>
+    <t>pothe</t>
+  </si>
+  <si>
+    <t>head (anatomy)</t>
+  </si>
+  <si>
+    <t>pûllae</t>
+  </si>
+  <si>
+    <t>test, examination, assessment</t>
+  </si>
+  <si>
+    <t>pûllan</t>
+  </si>
+  <si>
+    <t>to test, to assess, to proof</t>
+  </si>
+  <si>
+    <t>pûmar</t>
+  </si>
+  <si>
+    <t>rude, mean, impolite</t>
+  </si>
+  <si>
+    <t>pŷŋ</t>
+  </si>
+  <si>
+    <t>sprig, branchlet</t>
+  </si>
+  <si>
+    <t>qwa</t>
+  </si>
+  <si>
+    <t>coin</t>
+  </si>
+  <si>
+    <t>qwael</t>
+  </si>
+  <si>
+    <t>cave, cavern</t>
+  </si>
+  <si>
+    <t>qwael-bie</t>
+  </si>
+  <si>
+    <t>undergound</t>
+  </si>
+  <si>
+    <t>qwaentan</t>
+  </si>
+  <si>
+    <t>to abandon</t>
+  </si>
+  <si>
+    <t>qwainen</t>
+  </si>
+  <si>
+    <t>to cure a sickness</t>
+  </si>
+  <si>
+    <t>qwaithe</t>
+  </si>
+  <si>
+    <t>hide (animal skin)</t>
+  </si>
+  <si>
+    <t>qwalan</t>
+  </si>
+  <si>
+    <t>to read</t>
+  </si>
+  <si>
+    <t>qwande</t>
+  </si>
+  <si>
+    <t>fruit</t>
+  </si>
+  <si>
+    <t>qwantash</t>
+  </si>
+  <si>
+    <t>to run, to sprint</t>
+  </si>
+  <si>
+    <t>qwas</t>
+  </si>
+  <si>
+    <t>purple</t>
+  </si>
+  <si>
+    <t>qwash</t>
+  </si>
+  <si>
+    <t>stew</t>
+  </si>
+  <si>
+    <t>qwasheme</t>
+  </si>
+  <si>
+    <t>pumpkin</t>
+  </si>
+  <si>
+    <t>qweldesh</t>
+  </si>
+  <si>
+    <t>to hide</t>
+  </si>
+  <si>
+    <t>qwelya-qwessie</t>
+  </si>
+  <si>
+    <t>high elf (d&amp;d)</t>
+  </si>
+  <si>
+    <t>qwelyas</t>
+  </si>
+  <si>
+    <t>great, magnificent</t>
+  </si>
+  <si>
+    <t>qwen</t>
+  </si>
+  <si>
+    <t>gold</t>
+  </si>
+  <si>
+    <t>qwerasir</t>
+  </si>
+  <si>
+    <t>kingdom, empire, nation</t>
+  </si>
+  <si>
+    <t>qwese</t>
+  </si>
+  <si>
+    <t>small river, stream</t>
+  </si>
+  <si>
+    <t>qwessa</t>
+  </si>
+  <si>
+    <t>pillow</t>
+  </si>
+  <si>
+    <t>qwessi-bie</t>
+  </si>
+  <si>
+    <t>elvish, elven</t>
+  </si>
+  <si>
+    <t>qwessi-dae</t>
+  </si>
+  <si>
+    <t>an elven language, an elvish language</t>
+  </si>
+  <si>
+    <t>qwessie</t>
+  </si>
+  <si>
+    <t>elf</t>
+  </si>
+  <si>
+    <t>qweth</t>
+  </si>
+  <si>
+    <t>soup</t>
+  </si>
+  <si>
+    <t>qwevie</t>
+  </si>
+  <si>
+    <t>thoughts, mind</t>
+  </si>
+  <si>
+    <t>qwiresh</t>
+  </si>
+  <si>
+    <t>to rain</t>
+  </si>
+  <si>
+    <t>qwiressi</t>
+  </si>
+  <si>
+    <t>rainfall</t>
+  </si>
+  <si>
+    <t>qwôl</t>
+  </si>
+  <si>
+    <t>dress, gown</t>
+  </si>
+  <si>
+    <t>qwôlar</t>
+  </si>
+  <si>
+    <t>hall, hallway</t>
+  </si>
+  <si>
+    <t>qwolôrna</t>
+  </si>
+  <si>
+    <t>million</t>
+  </si>
+  <si>
+    <t>qwoŋbalas</t>
+  </si>
+  <si>
+    <t>gorgeous</t>
+  </si>
+  <si>
+    <t>qwôra</t>
+  </si>
+  <si>
+    <t>chainmail, chain mail, maille</t>
+  </si>
+  <si>
+    <t>qwôren</t>
+  </si>
+  <si>
+    <t>to hug in a friendly way</t>
+  </si>
+  <si>
+    <t>qwossan</t>
+  </si>
+  <si>
+    <t>to remember</t>
+  </si>
+  <si>
+    <t>qwŷl</t>
+  </si>
+  <si>
+    <t>ray, shaft, beam; a shaft of light from the sun or the moon</t>
+  </si>
+  <si>
+    <t>raelesh</t>
+  </si>
+  <si>
+    <t>to die, to succumb</t>
+  </si>
+  <si>
+    <t>raeleshtil</t>
+  </si>
+  <si>
+    <t>dead</t>
+  </si>
+  <si>
+    <t>raien</t>
+  </si>
+  <si>
+    <t>to own, to have</t>
+  </si>
+  <si>
+    <t>raithen</t>
+  </si>
+  <si>
+    <t>to save, to rescue</t>
+  </si>
+  <si>
+    <t>ralwe</t>
+  </si>
+  <si>
+    <t>ghost, apparition, wisp, spirit, genie</t>
+  </si>
+  <si>
+    <t>Ranûdel</t>
+  </si>
+  <si>
+    <t>kingdom of ranudel</t>
+  </si>
+  <si>
+    <t>rassae</t>
+  </si>
+  <si>
+    <t>leaf</t>
+  </si>
+  <si>
+    <t>rassil</t>
+  </si>
+  <si>
+    <t>forest</t>
+  </si>
+  <si>
+    <t>rende</t>
+  </si>
+  <si>
+    <t>sick, infected, diseased</t>
+  </si>
+  <si>
+    <t>reŋmie</t>
+  </si>
+  <si>
+    <t>breast (mammal); one of a woman's breasts</t>
+  </si>
+  <si>
+    <t>ressie</t>
+  </si>
+  <si>
+    <t>plant seed</t>
+  </si>
+  <si>
+    <t>rielda</t>
+  </si>
+  <si>
+    <t>iron</t>
+  </si>
+  <si>
+    <t>rim</t>
+  </si>
+  <si>
+    <t>arm</t>
+  </si>
+  <si>
+    <t>rina</t>
+  </si>
+  <si>
+    <t>pouch, bag</t>
+  </si>
+  <si>
+    <t>rindalesh</t>
+  </si>
+  <si>
+    <t>to sing melodically</t>
+  </si>
+  <si>
+    <t>rindie</t>
+  </si>
+  <si>
+    <t>circle</t>
+  </si>
+  <si>
+    <t>rôcand</t>
+  </si>
+  <si>
+    <t>place of ruin, abandonment, or disaster; ancient ruin</t>
+  </si>
+  <si>
+    <t>roil</t>
+  </si>
+  <si>
+    <t>sludge, muck, decayed organic matter</t>
+  </si>
+  <si>
+    <t>rôl</t>
+  </si>
+  <si>
+    <t>mat, rug, carpet</t>
+  </si>
+  <si>
+    <t>rôn</t>
+  </si>
+  <si>
+    <t>mountain</t>
+  </si>
+  <si>
+    <t>rôn-beranae</t>
+  </si>
+  <si>
+    <t>mountain range</t>
+  </si>
+  <si>
+    <t>ronathas</t>
+  </si>
+  <si>
+    <t>great, mighty, powerful</t>
+  </si>
+  <si>
+    <t>rosse</t>
+  </si>
+  <si>
+    <t>window</t>
+  </si>
+  <si>
+    <t>rume</t>
+  </si>
+  <si>
+    <t>grass</t>
+  </si>
+  <si>
+    <t>rume-flowe</t>
+  </si>
+  <si>
+    <t>meadow, grassland, plains</t>
+  </si>
+  <si>
+    <t>rûnas</t>
+  </si>
+  <si>
+    <t>sweet, pleasant, nice, innocent</t>
+  </si>
+  <si>
+    <t>rûnathie</t>
+  </si>
+  <si>
+    <t>dream</t>
+  </si>
+  <si>
+    <t>rûndie</t>
+  </si>
+  <si>
+    <t>nine</t>
+  </si>
+  <si>
+    <t>rŷŋ</t>
+  </si>
+  <si>
+    <t>something ancient, old, mystical, or magical</t>
+  </si>
+  <si>
+    <t>rŷŋ-gwandar</t>
+  </si>
+  <si>
+    <t>wizardry</t>
+  </si>
+  <si>
+    <t>s'-</t>
+  </si>
+  <si>
+    <t>definite article shortened into prefix form, used with words that dont start with s- (sh- words are the exception) (informal)</t>
+  </si>
+  <si>
+    <t>sa (1)</t>
+  </si>
+  <si>
+    <t>that (non-genitive)</t>
+  </si>
+  <si>
+    <t>sa (2)</t>
+  </si>
+  <si>
+    <t>definite article</t>
+  </si>
+  <si>
+    <t>saelas</t>
+  </si>
+  <si>
+    <t>black</t>
+  </si>
+  <si>
+    <t>saerash</t>
+  </si>
+  <si>
+    <t>to end, to finish</t>
+  </si>
+  <si>
+    <t>saerassi</t>
+  </si>
+  <si>
+    <t>ending, end</t>
+  </si>
+  <si>
+    <t>sailan</t>
+  </si>
+  <si>
+    <t>to enlighten</t>
+  </si>
+  <si>
+    <t>sailas</t>
+  </si>
+  <si>
+    <t>wise</t>
+  </si>
+  <si>
+    <t>sailassi</t>
+  </si>
+  <si>
+    <t>wisdom</t>
+  </si>
+  <si>
+    <t>saldassi</t>
+  </si>
+  <si>
+    <t>lightning</t>
+  </si>
+  <si>
+    <t>samai</t>
+  </si>
+  <si>
+    <t>enough</t>
+  </si>
+  <si>
+    <t>sanaŋ</t>
+  </si>
+  <si>
+    <t>lizard</t>
+  </si>
+  <si>
+    <t>sanash</t>
+  </si>
+  <si>
+    <t>to will, to ought (future tense verb)</t>
+  </si>
+  <si>
+    <t>sani</t>
+  </si>
+  <si>
+    <t>that (genitive)</t>
+  </si>
+  <si>
+    <t>saru</t>
+  </si>
+  <si>
+    <t>last</t>
+  </si>
+  <si>
+    <t>sathas</t>
+  </si>
+  <si>
+    <t>grey, gray</t>
+  </si>
+  <si>
+    <t>seiren</t>
+  </si>
+  <si>
+    <t>to play an instument</t>
+  </si>
+  <si>
+    <t>seldiren</t>
+  </si>
+  <si>
+    <t>to frighten, to cause fear, to cause dread</t>
+  </si>
+  <si>
+    <t>selesh</t>
+  </si>
+  <si>
+    <t>to transform, to become, to turn into (with or without "ci")</t>
+  </si>
+  <si>
+    <t>selo</t>
+  </si>
+  <si>
+    <t>six</t>
+  </si>
+  <si>
+    <t>sentie</t>
+  </si>
+  <si>
+    <t>priest</t>
+  </si>
+  <si>
+    <t>serafalassi</t>
+  </si>
+  <si>
+    <t>butterfly</t>
+  </si>
+  <si>
+    <t>serenas</t>
+  </si>
+  <si>
+    <t>cute, pretty</t>
+  </si>
+  <si>
+    <t>serenevathas</t>
+  </si>
+  <si>
+    <t>beautiful, gorgeous</t>
+  </si>
+  <si>
+    <t>serie</t>
+  </si>
+  <si>
+    <t>girl</t>
+  </si>
+  <si>
+    <t>sesufele</t>
+  </si>
+  <si>
+    <t>description, appeareance</t>
+  </si>
+  <si>
+    <t>sevir</t>
+  </si>
+  <si>
+    <t>force, invisible force</t>
+  </si>
+  <si>
+    <t>shaelda</t>
+  </si>
+  <si>
+    <t>lever, switch</t>
+  </si>
+  <si>
+    <t>shan</t>
+  </si>
+  <si>
+    <t>pain</t>
+  </si>
+  <si>
+    <t>sheb</t>
+  </si>
+  <si>
+    <t>boot, shoe</t>
+  </si>
+  <si>
+    <t>shelai</t>
+  </si>
+  <si>
+    <t>such, so; like this, that sort of, that kind of</t>
+  </si>
+  <si>
+    <t>shele</t>
+  </si>
+  <si>
+    <t>thing, object, something</t>
+  </si>
+  <si>
+    <t>shelesse</t>
+  </si>
+  <si>
+    <t>mist</t>
+  </si>
+  <si>
+    <t>shelŷnas</t>
+  </si>
+  <si>
+    <t>delicious</t>
+  </si>
+  <si>
+    <t>shielde</t>
+  </si>
+  <si>
+    <t>tree</t>
+  </si>
+  <si>
+    <t>shôl</t>
+  </si>
+  <si>
+    <t>jewelry</t>
+  </si>
+  <si>
+    <t>shone</t>
+  </si>
+  <si>
+    <t>knowledge</t>
+  </si>
+  <si>
+    <t>shraeŋ</t>
+  </si>
+  <si>
+    <t>illusion</t>
+  </si>
+  <si>
+    <t>shrilie</t>
+  </si>
+  <si>
+    <t>choir of birds</t>
+  </si>
+  <si>
+    <t>shrond</t>
+  </si>
+  <si>
+    <t>temple</t>
+  </si>
+  <si>
+    <t>shrunen</t>
+  </si>
+  <si>
+    <t>to buy</t>
+  </si>
+  <si>
+    <t>shrŷlwe</t>
+  </si>
+  <si>
+    <t>magical aura</t>
+  </si>
+  <si>
+    <t>shrŷna</t>
+  </si>
+  <si>
+    <t>hood, cowl</t>
+  </si>
+  <si>
+    <t>shrŷŋ</t>
+  </si>
+  <si>
+    <t>mirror</t>
+  </si>
+  <si>
+    <t>shwiŋ</t>
+  </si>
+  <si>
+    <t>bone</t>
+  </si>
+  <si>
+    <t>shŷne</t>
+  </si>
+  <si>
+    <t>thyme</t>
+  </si>
+  <si>
+    <t>sidir</t>
+  </si>
+  <si>
+    <t>pants, trousers</t>
+  </si>
+  <si>
+    <t>silitha</t>
+  </si>
+  <si>
+    <t>writing</t>
+  </si>
+  <si>
+    <t>silssien</t>
+  </si>
+  <si>
+    <t>to like, to favour</t>
+  </si>
+  <si>
+    <t>sin</t>
+  </si>
+  <si>
+    <t>this (non-genitive)</t>
+  </si>
+  <si>
+    <t>sincultir</t>
+  </si>
+  <si>
+    <t>black hellebore (flower)</t>
+  </si>
+  <si>
+    <t>sini</t>
+  </si>
+  <si>
+    <t>this (genitive)</t>
+  </si>
+  <si>
+    <t>siŋga-lisse</t>
+  </si>
+  <si>
+    <t>saltwater brine</t>
+  </si>
+  <si>
+    <t>siŋgae</t>
+  </si>
+  <si>
+    <t>salt</t>
+  </si>
+  <si>
+    <t>siôrash</t>
+  </si>
+  <si>
+    <t>to bathe</t>
+  </si>
+  <si>
+    <t>siôren</t>
+  </si>
+  <si>
+    <t>to wash</t>
+  </si>
+  <si>
+    <t>siten</t>
+  </si>
+  <si>
+    <t>to grab</t>
+  </si>
+  <si>
+    <t>slacash</t>
+  </si>
+  <si>
+    <t>to scream, to screech</t>
+  </si>
+  <si>
+    <t>slande</t>
+  </si>
+  <si>
+    <t>weird, strange</t>
+  </si>
+  <si>
+    <t>slantha</t>
+  </si>
+  <si>
+    <t>chemise, frock, shift; a long, linen underdress</t>
+  </si>
+  <si>
+    <t>slend</t>
+  </si>
+  <si>
+    <t>an undergarment shirt/tunic, usually made of linen or cotton</t>
+  </si>
+  <si>
+    <t>sloren</t>
+  </si>
+  <si>
+    <t>to scare, to unnerve, to make tremble</t>
+  </si>
+  <si>
+    <t>slores</t>
+  </si>
+  <si>
+    <t>unnerved, uncomfortable</t>
+  </si>
+  <si>
+    <t>slôssie</t>
+  </si>
+  <si>
+    <t>juice</t>
+  </si>
+  <si>
+    <t>solonde</t>
+  </si>
+  <si>
+    <t>tranquility, serenity, calmness</t>
+  </si>
+  <si>
+    <t>solsse</t>
+  </si>
+  <si>
+    <t>minute</t>
+  </si>
+  <si>
+    <t>sontan</t>
+  </si>
+  <si>
+    <t>to cook</t>
+  </si>
+  <si>
+    <t>spacul</t>
+  </si>
+  <si>
+    <t>ghost, specter, apparition, spirit</t>
+  </si>
+  <si>
+    <t>spaida</t>
+  </si>
+  <si>
+    <t>scabbard</t>
+  </si>
+  <si>
+    <t>spiencelen</t>
+  </si>
+  <si>
+    <t>to violate someone, to rape</t>
+  </si>
+  <si>
+    <t>staelfe</t>
+  </si>
+  <si>
+    <t>tradition, custom</t>
+  </si>
+  <si>
+    <t>stûinde</t>
+  </si>
+  <si>
+    <t>animal, creature</t>
+  </si>
+  <si>
+    <t>suce</t>
+  </si>
+  <si>
+    <t>slime, ooze</t>
+  </si>
+  <si>
+    <t>swaesse</t>
+  </si>
+  <si>
+    <t>drink, beverage</t>
+  </si>
+  <si>
+    <t>swanze</t>
+  </si>
+  <si>
+    <t>sheep</t>
+  </si>
+  <si>
+    <t>swind</t>
+  </si>
+  <si>
+    <t>sign (for directions and text)</t>
+  </si>
+  <si>
+    <t>swintane</t>
+  </si>
+  <si>
+    <t>flute</t>
+  </si>
+  <si>
+    <t>swiŋye</t>
+  </si>
+  <si>
+    <t>type, kind, sort</t>
+  </si>
+  <si>
+    <t>sŷlae</t>
+  </si>
+  <si>
+    <t>swan</t>
+  </si>
+  <si>
+    <t>tacwel</t>
+  </si>
+  <si>
+    <t>hoe, cultivator, tiller</t>
+  </si>
+  <si>
+    <t>tael</t>
+  </si>
+  <si>
+    <t>god, deity</t>
+  </si>
+  <si>
+    <t>taend</t>
+  </si>
+  <si>
+    <t>a drum large enough that it's typically played whilst standing up</t>
+  </si>
+  <si>
+    <t>talaraŋ</t>
+  </si>
+  <si>
+    <t>sorcerer</t>
+  </si>
+  <si>
+    <t>taldaŋ</t>
+  </si>
+  <si>
+    <t>sorcery magic</t>
+  </si>
+  <si>
+    <t>tamalash</t>
+  </si>
+  <si>
+    <t>to shine brightly</t>
+  </si>
+  <si>
+    <t>tanten</t>
+  </si>
+  <si>
+    <t>to bake</t>
+  </si>
+  <si>
+    <t>taŋcan</t>
+  </si>
+  <si>
+    <t>to must, to shall</t>
+  </si>
+  <si>
+    <t>tarien</t>
+  </si>
+  <si>
+    <t>gift, present</t>
+  </si>
+  <si>
+    <t>tassie</t>
+  </si>
+  <si>
+    <t>crazy, mentally insane</t>
+  </si>
+  <si>
+    <t>tayandôr</t>
+  </si>
+  <si>
+    <t>orchid (flower)</t>
+  </si>
+  <si>
+    <t>tecse</t>
+  </si>
+  <si>
+    <t>sea shell, snail shell, clam shell</t>
+  </si>
+  <si>
+    <t>telde</t>
+  </si>
+  <si>
+    <t>wonder</t>
+  </si>
+  <si>
+    <t>teltan</t>
+  </si>
+  <si>
+    <t>to oath, to promise, to commit an oath, to make a promise</t>
+  </si>
+  <si>
+    <t>telyash</t>
+  </si>
+  <si>
+    <t>to stand up straight</t>
+  </si>
+  <si>
+    <t>tende</t>
+  </si>
+  <si>
+    <t>tall, high</t>
+  </si>
+  <si>
+    <t>tendiswe</t>
+  </si>
+  <si>
+    <t>height</t>
+  </si>
+  <si>
+    <t>tenild</t>
+  </si>
+  <si>
+    <t>arm ring</t>
+  </si>
+  <si>
+    <t>teŋgen</t>
+  </si>
+  <si>
+    <t>to arrive at, to reach, to get to</t>
+  </si>
+  <si>
+    <t>teŋgesh</t>
+  </si>
+  <si>
+    <t>to come</t>
+  </si>
+  <si>
+    <t>teŋnen</t>
+  </si>
+  <si>
+    <t>to hear</t>
+  </si>
+  <si>
+    <t>terasse</t>
+  </si>
+  <si>
+    <t>lute</t>
+  </si>
+  <si>
+    <t>tesse</t>
+  </si>
+  <si>
+    <t>right</t>
+  </si>
+  <si>
+    <t>tessu</t>
+  </si>
+  <si>
+    <t>rightwards</t>
+  </si>
+  <si>
+    <t>thael</t>
+  </si>
+  <si>
+    <t>clothing, apparel</t>
+  </si>
+  <si>
+    <t>thaiden</t>
+  </si>
+  <si>
+    <t>to stretch, to lengthen; to draw a bow</t>
+  </si>
+  <si>
+    <t>thaine</t>
+  </si>
+  <si>
+    <t>law, rules</t>
+  </si>
+  <si>
+    <t>thaisse</t>
+  </si>
+  <si>
+    <t>cloud, billow</t>
+  </si>
+  <si>
+    <t>thalashaŋ</t>
+  </si>
+  <si>
+    <t>druidry magic</t>
+  </si>
+  <si>
+    <t>thalassi</t>
+  </si>
+  <si>
+    <t>air</t>
+  </si>
+  <si>
+    <t>thas</t>
+  </si>
+  <si>
+    <t>five</t>
+  </si>
+  <si>
+    <t>thash</t>
+  </si>
+  <si>
+    <t>to start, to begin</t>
+  </si>
+  <si>
+    <t>thelen</t>
+  </si>
+  <si>
+    <t>to find, to look for</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>theren</t>
+  </si>
+  <si>
+    <t>for a long time</t>
+  </si>
+  <si>
+    <t>theressi</t>
+  </si>
+  <si>
+    <t>length</t>
+  </si>
+  <si>
+    <t>thewan</t>
+  </si>
+  <si>
+    <t>to sew (with or without "gai" or "mi")</t>
+  </si>
+  <si>
+    <t>thiemen</t>
+  </si>
+  <si>
+    <t>to lead, to guide</t>
+  </si>
+  <si>
+    <t>thiemen hassu</t>
+  </si>
+  <si>
+    <t>to hold someone's hand, to lead someone by hand (with "mi" + who)</t>
+  </si>
+  <si>
+    <t>thienas</t>
+  </si>
+  <si>
+    <t>ten</t>
+  </si>
+  <si>
+    <t>thilde</t>
+  </si>
+  <si>
+    <t>ally, teammate</t>
+  </si>
+  <si>
+    <t>thilende</t>
+  </si>
+  <si>
+    <t>game, sport</t>
+  </si>
+  <si>
+    <t>thilu</t>
+  </si>
+  <si>
+    <t>far</t>
+  </si>
+  <si>
+    <t>thime</t>
+  </si>
+  <si>
+    <t>silk</t>
+  </si>
+  <si>
+    <t>thiva</t>
+  </si>
+  <si>
+    <t>shears, scissors</t>
+  </si>
+  <si>
+    <t>thobae</t>
+  </si>
+  <si>
+    <t>finger</t>
+  </si>
+  <si>
+    <t>thomash</t>
+  </si>
+  <si>
+    <t>to want</t>
+  </si>
+  <si>
+    <t>thore</t>
+  </si>
+  <si>
+    <t>a loud, thunderous sound</t>
+  </si>
+  <si>
+    <t>thrande</t>
+  </si>
+  <si>
+    <t>orchard, garden</t>
+  </si>
+  <si>
+    <t>throssen</t>
+  </si>
+  <si>
+    <t>to suck</t>
+  </si>
+  <si>
+    <t>thrûvi</t>
+  </si>
+  <si>
+    <t>hay, thatch, dry grass</t>
+  </si>
+  <si>
+    <t>thrŷl</t>
+  </si>
+  <si>
+    <t>finger ring</t>
+  </si>
+  <si>
+    <t>thûca</t>
+  </si>
+  <si>
+    <t>hundred</t>
+  </si>
+  <si>
+    <t>thûicen</t>
+  </si>
+  <si>
+    <t>to mean something</t>
+  </si>
+  <si>
+    <t>thuŋ</t>
+  </si>
+  <si>
+    <t>fear, terror</t>
+  </si>
+  <si>
+    <t>thuŋnen</t>
+  </si>
+  <si>
+    <t>to terrorise, to cause terror</t>
+  </si>
+  <si>
+    <t>thûrda</t>
+  </si>
+  <si>
+    <t>polearm (weapon)</t>
+  </si>
+  <si>
+    <t>thûvala</t>
+  </si>
+  <si>
+    <t>spear</t>
+  </si>
+  <si>
+    <t>thwossiesh</t>
+  </si>
+  <si>
+    <t>to would</t>
+  </si>
+  <si>
+    <t>thŷlen</t>
+  </si>
+  <si>
+    <t>to taste</t>
+  </si>
+  <si>
+    <t>tilie</t>
+  </si>
+  <si>
+    <t>oath, promise</t>
+  </si>
+  <si>
+    <t>tima</t>
   </si>
   <si>
     <t>symbol, glyph</t>
-  </si>
-  <si>
-    <t>pôlafra</t>
-  </si>
-  <si>
-    <t>book</t>
-  </si>
-  <si>
-    <t>pôlômae</t>
-  </si>
-  <si>
-    <t>explosion</t>
-  </si>
-  <si>
-    <t>pôlômash</t>
-  </si>
-  <si>
-    <t>to explode</t>
-  </si>
-  <si>
-    <t>pônu</t>
-  </si>
-  <si>
-    <t>forwards</t>
-  </si>
-  <si>
-    <t>possai</t>
-  </si>
-  <si>
-    <t>many, much, a lot</t>
-  </si>
-  <si>
-    <t>pothe</t>
-  </si>
-  <si>
-    <t>head (anatomy)</t>
-  </si>
-  <si>
-    <t>pûllae</t>
-  </si>
-  <si>
-    <t>test, examination, assessment</t>
-  </si>
-  <si>
-    <t>pûllan</t>
-  </si>
-  <si>
-    <t>to test, to assess, to proof</t>
-  </si>
-  <si>
-    <t>pûmar</t>
-  </si>
-  <si>
-    <t>rude, mean, impolite</t>
-  </si>
-  <si>
-    <t>pŷŋ</t>
-  </si>
-  <si>
-    <t>sprig, branchlet</t>
-  </si>
-  <si>
-    <t>qwa</t>
-  </si>
-  <si>
-    <t>coin</t>
-  </si>
-  <si>
-    <t>qwael</t>
-  </si>
-  <si>
-    <t>cave, cavern</t>
-  </si>
-  <si>
-    <t>qwael-bie</t>
-  </si>
-  <si>
-    <t>undergound</t>
-  </si>
-  <si>
-    <t>qwaentan</t>
-  </si>
-  <si>
-    <t>to abandon</t>
-  </si>
-  <si>
-    <t>qwainen</t>
-  </si>
-  <si>
-    <t>to cure a sickness</t>
-  </si>
-  <si>
-    <t>qwaithe</t>
-  </si>
-  <si>
-    <t>hide (animal skin)</t>
-  </si>
-  <si>
-    <t>qwalan</t>
-  </si>
-  <si>
-    <t>to read</t>
-  </si>
-  <si>
-    <t>qwande</t>
-  </si>
-  <si>
-    <t>fruit</t>
-  </si>
-  <si>
-    <t>qwantash</t>
-  </si>
-  <si>
-    <t>to run, to sprint</t>
-  </si>
-  <si>
-    <t>qwas</t>
-  </si>
-  <si>
-    <t>purple</t>
-  </si>
-  <si>
-    <t>qwash</t>
-  </si>
-  <si>
-    <t>stew</t>
-  </si>
-  <si>
-    <t>qwasheme</t>
-  </si>
-  <si>
-    <t>pumpkin</t>
-  </si>
-  <si>
-    <t>qweldesh</t>
-  </si>
-  <si>
-    <t>to hide</t>
-  </si>
-  <si>
-    <t>qwelya-qwessie</t>
-  </si>
-  <si>
-    <t>high elf (d&amp;d)</t>
-  </si>
-  <si>
-    <t>qwelyas</t>
-  </si>
-  <si>
-    <t>great, magnificent</t>
-  </si>
-  <si>
-    <t>qwen</t>
-  </si>
-  <si>
-    <t>gold</t>
-  </si>
-  <si>
-    <t>qwerasir</t>
-  </si>
-  <si>
-    <t>kingdom, empire, nation</t>
-  </si>
-  <si>
-    <t>qwese</t>
-  </si>
-  <si>
-    <t>small river, stream</t>
-  </si>
-  <si>
-    <t>qwessa</t>
-  </si>
-  <si>
-    <t>pillow</t>
-  </si>
-  <si>
-    <t>qwessi-bie</t>
-  </si>
-  <si>
-    <t>elvish, elven</t>
-  </si>
-  <si>
-    <t>qwessi-dae</t>
-  </si>
-  <si>
-    <t>an elven language, an elvish language</t>
-  </si>
-  <si>
-    <t>qwessie</t>
-  </si>
-  <si>
-    <t>elf</t>
-  </si>
-  <si>
-    <t>qweth</t>
-  </si>
-  <si>
-    <t>soup</t>
-  </si>
-  <si>
-    <t>qwevie</t>
-  </si>
-  <si>
-    <t>thoughts, mind</t>
-  </si>
-  <si>
-    <t>qwiresh</t>
-  </si>
-  <si>
-    <t>to rain</t>
-  </si>
-  <si>
-    <t>qwiressi</t>
-  </si>
-  <si>
-    <t>rainfall</t>
-  </si>
-  <si>
-    <t>qwôl</t>
-  </si>
-  <si>
-    <t>dress, gown</t>
-  </si>
-  <si>
-    <t>qwôlar</t>
-  </si>
-  <si>
-    <t>hall, hallway</t>
-  </si>
-  <si>
-    <t>qwolôrna</t>
-  </si>
-  <si>
-    <t>million</t>
-  </si>
-  <si>
-    <t>qwoŋbalas</t>
-  </si>
-  <si>
-    <t>gorgeous</t>
-  </si>
-  <si>
-    <t>qwôra</t>
-  </si>
-  <si>
-    <t>chainmail, chain mail, maille</t>
-  </si>
-  <si>
-    <t>qwôren</t>
-  </si>
-  <si>
-    <t>to hug in a friendly way</t>
-  </si>
-  <si>
-    <t>qwossan</t>
-  </si>
-  <si>
-    <t>to remember</t>
-  </si>
-  <si>
-    <t>qwŷl</t>
-  </si>
-  <si>
-    <t>ray, shaft, beam; a shaft of light from the sun or the moon</t>
-  </si>
-  <si>
-    <t>raelesh</t>
-  </si>
-  <si>
-    <t>to die, to succumb</t>
-  </si>
-  <si>
-    <t>raeleshtil</t>
-  </si>
-  <si>
-    <t>dead</t>
-  </si>
-  <si>
-    <t>raien</t>
-  </si>
-  <si>
-    <t>to own, to have</t>
-  </si>
-  <si>
-    <t>raithen</t>
-  </si>
-  <si>
-    <t>to save, to rescue</t>
-  </si>
-  <si>
-    <t>ralwe</t>
-  </si>
-  <si>
-    <t>ghost, apparition, wisp, spirit, genie</t>
-  </si>
-  <si>
-    <t>Ranûdel</t>
-  </si>
-  <si>
-    <t>kingdom of ranudel</t>
-  </si>
-  <si>
-    <t>rassae</t>
-  </si>
-  <si>
-    <t>leaf</t>
-  </si>
-  <si>
-    <t>rassil</t>
-  </si>
-  <si>
-    <t>forest</t>
-  </si>
-  <si>
-    <t>rende</t>
-  </si>
-  <si>
-    <t>sick, infected, diseased</t>
-  </si>
-  <si>
-    <t>reŋmie</t>
-  </si>
-  <si>
-    <t>breast (mammal); one of a woman's breasts</t>
-  </si>
-  <si>
-    <t>ressie</t>
-  </si>
-  <si>
-    <t>plant seed</t>
-  </si>
-  <si>
-    <t>rielda</t>
-  </si>
-  <si>
-    <t>iron</t>
-  </si>
-  <si>
-    <t>rim</t>
-  </si>
-  <si>
-    <t>arm</t>
-  </si>
-  <si>
-    <t>rina</t>
-  </si>
-  <si>
-    <t>pouch, bag</t>
-  </si>
-  <si>
-    <t>rindalesh</t>
-  </si>
-  <si>
-    <t>to sing melodically</t>
-  </si>
-  <si>
-    <t>rindie</t>
-  </si>
-  <si>
-    <t>circle</t>
-  </si>
-  <si>
-    <t>rôcand</t>
-  </si>
-  <si>
-    <t>place of ruin, abandonment, or disaster; ancient ruin</t>
-  </si>
-  <si>
-    <t>roil</t>
-  </si>
-  <si>
-    <t>sludge, muck, decayed organic matter</t>
-  </si>
-  <si>
-    <t>rôl</t>
-  </si>
-  <si>
-    <t>mat, rug, carpet</t>
-  </si>
-  <si>
-    <t>rôn</t>
-  </si>
-  <si>
-    <t>mountain</t>
-  </si>
-  <si>
-    <t>rôn-beranae</t>
-  </si>
-  <si>
-    <t>mountain range</t>
-  </si>
-  <si>
-    <t>ronathas</t>
-  </si>
-  <si>
-    <t>great, mighty, powerful</t>
-  </si>
-  <si>
-    <t>rosse</t>
-  </si>
-  <si>
-    <t>window</t>
-  </si>
-  <si>
-    <t>rume</t>
-  </si>
-  <si>
-    <t>grass</t>
-  </si>
-  <si>
-    <t>rume-flowe</t>
-  </si>
-  <si>
-    <t>meadow, grassland, plains</t>
-  </si>
-  <si>
-    <t>rûnas</t>
-  </si>
-  <si>
-    <t>sweet, pleasant, nice, innocent</t>
-  </si>
-  <si>
-    <t>rûnathie</t>
-  </si>
-  <si>
-    <t>dream</t>
-  </si>
-  <si>
-    <t>rûndie</t>
-  </si>
-  <si>
-    <t>nine</t>
-  </si>
-  <si>
-    <t>rŷŋ</t>
-  </si>
-  <si>
-    <t>something ancient, old, mystical, or magical</t>
-  </si>
-  <si>
-    <t>rŷŋ-gwandar</t>
-  </si>
-  <si>
-    <t>wizardry</t>
-  </si>
-  <si>
-    <t>s'-</t>
-  </si>
-  <si>
-    <t>definite article shortened into prefix form, used with words that dont start with s- (sh- words are the exception) (informal)</t>
-  </si>
-  <si>
-    <t>sa (1)</t>
-  </si>
-  <si>
-    <t>that (non-genitive)</t>
-  </si>
-  <si>
-    <t>sa (2)</t>
-  </si>
-  <si>
-    <t>definite article</t>
-  </si>
-  <si>
-    <t>saelas</t>
-  </si>
-  <si>
-    <t>black</t>
-  </si>
-  <si>
-    <t>saerash</t>
-  </si>
-  <si>
-    <t>to end, to finish</t>
-  </si>
-  <si>
-    <t>saerassi</t>
-  </si>
-  <si>
-    <t>ending, end</t>
-  </si>
-  <si>
-    <t>sailan</t>
-  </si>
-  <si>
-    <t>to enlighten</t>
-  </si>
-  <si>
-    <t>sailas</t>
-  </si>
-  <si>
-    <t>wise</t>
-  </si>
-  <si>
-    <t>sailassi</t>
-  </si>
-  <si>
-    <t>wisdom</t>
-  </si>
-  <si>
-    <t>saldassi</t>
-  </si>
-  <si>
-    <t>lightning</t>
-  </si>
-  <si>
-    <t>samai</t>
-  </si>
-  <si>
-    <t>enough</t>
-  </si>
-  <si>
-    <t>sanaŋ</t>
-  </si>
-  <si>
-    <t>lizard</t>
-  </si>
-  <si>
-    <t>sanash</t>
-  </si>
-  <si>
-    <t>to will, to ought (future tense verb)</t>
-  </si>
-  <si>
-    <t>sani</t>
-  </si>
-  <si>
-    <t>that (genitive)</t>
-  </si>
-  <si>
-    <t>saru</t>
-  </si>
-  <si>
-    <t>last</t>
-  </si>
-  <si>
-    <t>sathas</t>
-  </si>
-  <si>
-    <t>grey, gray</t>
-  </si>
-  <si>
-    <t>seiren</t>
-  </si>
-  <si>
-    <t>to play an instument</t>
-  </si>
-  <si>
-    <t>seldiren</t>
-  </si>
-  <si>
-    <t>to frighten, to cause fear, to cause dread</t>
-  </si>
-  <si>
-    <t>selesh</t>
-  </si>
-  <si>
-    <t>to transform, to become, to turn into (with or without "ci")</t>
-  </si>
-  <si>
-    <t>selo</t>
-  </si>
-  <si>
-    <t>six</t>
-  </si>
-  <si>
-    <t>sentie</t>
-  </si>
-  <si>
-    <t>priest</t>
-  </si>
-  <si>
-    <t>serafalassi</t>
-  </si>
-  <si>
-    <t>butterfly</t>
-  </si>
-  <si>
-    <t>serenas</t>
-  </si>
-  <si>
-    <t>cute, pretty</t>
-  </si>
-  <si>
-    <t>serenevathas</t>
-  </si>
-  <si>
-    <t>beautiful, gorgeous</t>
-  </si>
-  <si>
-    <t>serie</t>
-  </si>
-  <si>
-    <t>girl</t>
-  </si>
-  <si>
-    <t>sesufele</t>
-  </si>
-  <si>
-    <t>description, appeareance</t>
-  </si>
-  <si>
-    <t>sevir</t>
-  </si>
-  <si>
-    <t>force, invisible force</t>
-  </si>
-  <si>
-    <t>shaelda</t>
-  </si>
-  <si>
-    <t>lever, switch</t>
-  </si>
-  <si>
-    <t>shan</t>
-  </si>
-  <si>
-    <t>pain</t>
-  </si>
-  <si>
-    <t>sheb</t>
-  </si>
-  <si>
-    <t>boot, shoe</t>
-  </si>
-  <si>
-    <t>shelai</t>
-  </si>
-  <si>
-    <t>such, so; like this, that sort of, that kind of</t>
-  </si>
-  <si>
-    <t>shele</t>
-  </si>
-  <si>
-    <t>thing, object, something</t>
-  </si>
-  <si>
-    <t>shelesse</t>
-  </si>
-  <si>
-    <t>mist</t>
-  </si>
-  <si>
-    <t>shelŷnas</t>
-  </si>
-  <si>
-    <t>delicious</t>
-  </si>
-  <si>
-    <t>shielde</t>
-  </si>
-  <si>
-    <t>tree</t>
-  </si>
-  <si>
-    <t>shôl</t>
-  </si>
-  <si>
-    <t>jewelry</t>
-  </si>
-  <si>
-    <t>shone</t>
-  </si>
-  <si>
-    <t>knowledge</t>
-  </si>
-  <si>
-    <t>shraeŋ</t>
-  </si>
-  <si>
-    <t>illusion</t>
-  </si>
-  <si>
-    <t>shrilie</t>
-  </si>
-  <si>
-    <t>choir of birds</t>
-  </si>
-  <si>
-    <t>shrond</t>
-  </si>
-  <si>
-    <t>temple</t>
-  </si>
-  <si>
-    <t>shrunen</t>
-  </si>
-  <si>
-    <t>to buy</t>
-  </si>
-  <si>
-    <t>shrŷlwe</t>
-  </si>
-  <si>
-    <t>magical aura</t>
-  </si>
-  <si>
-    <t>shrŷna</t>
-  </si>
-  <si>
-    <t>hood, cowl</t>
-  </si>
-  <si>
-    <t>shrŷŋ</t>
-  </si>
-  <si>
-    <t>mirror</t>
-  </si>
-  <si>
-    <t>shwiŋ</t>
-  </si>
-  <si>
-    <t>bone</t>
-  </si>
-  <si>
-    <t>shŷne</t>
-  </si>
-  <si>
-    <t>thyme</t>
-  </si>
-  <si>
-    <t>sidir</t>
-  </si>
-  <si>
-    <t>pants, trousers</t>
-  </si>
-  <si>
-    <t>silitha</t>
-  </si>
-  <si>
-    <t>writing</t>
-  </si>
-  <si>
-    <t>silssien</t>
-  </si>
-  <si>
-    <t>to like, to favour</t>
-  </si>
-  <si>
-    <t>sin</t>
-  </si>
-  <si>
-    <t>this (non-genitive)</t>
-  </si>
-  <si>
-    <t>sincultir</t>
-  </si>
-  <si>
-    <t>black hellebore (flower)</t>
-  </si>
-  <si>
-    <t>sini</t>
-  </si>
-  <si>
-    <t>this (genitive)</t>
-  </si>
-  <si>
-    <t>siŋga-lisse</t>
-  </si>
-  <si>
-    <t>saltwater brine</t>
-  </si>
-  <si>
-    <t>siŋgae</t>
-  </si>
-  <si>
-    <t>salt</t>
-  </si>
-  <si>
-    <t>siôrash</t>
-  </si>
-  <si>
-    <t>to bathe</t>
-  </si>
-  <si>
-    <t>siôren</t>
-  </si>
-  <si>
-    <t>to wash</t>
-  </si>
-  <si>
-    <t>siten</t>
-  </si>
-  <si>
-    <t>to grab</t>
-  </si>
-  <si>
-    <t>slacash</t>
-  </si>
-  <si>
-    <t>to scream, to screech</t>
-  </si>
-  <si>
-    <t>slande</t>
-  </si>
-  <si>
-    <t>weird, strange</t>
-  </si>
-  <si>
-    <t>slantha</t>
-  </si>
-  <si>
-    <t>chemise, frock, shift; a long, linen underdress</t>
-  </si>
-  <si>
-    <t>slend</t>
-  </si>
-  <si>
-    <t>an undergarment shirt/tunic, usually made of linen or cotton</t>
-  </si>
-  <si>
-    <t>sloren</t>
-  </si>
-  <si>
-    <t>to scare, to unnerve, to make tremble</t>
-  </si>
-  <si>
-    <t>slores</t>
-  </si>
-  <si>
-    <t>unnerved, uncomfortable</t>
-  </si>
-  <si>
-    <t>slôssie</t>
-  </si>
-  <si>
-    <t>juice</t>
-  </si>
-  <si>
-    <t>solonde</t>
-  </si>
-  <si>
-    <t>tranquility, serenity, calmness</t>
-  </si>
-  <si>
-    <t>solsse</t>
-  </si>
-  <si>
-    <t>minute</t>
-  </si>
-  <si>
-    <t>sontan</t>
-  </si>
-  <si>
-    <t>to cook</t>
-  </si>
-  <si>
-    <t>spacul</t>
-  </si>
-  <si>
-    <t>ghost, specter, apparition, spirit</t>
-  </si>
-  <si>
-    <t>spaida</t>
-  </si>
-  <si>
-    <t>scabbard</t>
-  </si>
-  <si>
-    <t>spiencelen</t>
-  </si>
-  <si>
-    <t>to violate someone, to rape</t>
-  </si>
-  <si>
-    <t>staelfe</t>
-  </si>
-  <si>
-    <t>tradition, custom</t>
-  </si>
-  <si>
-    <t>stûinde</t>
-  </si>
-  <si>
-    <t>animal, creature</t>
-  </si>
-  <si>
-    <t>suce</t>
-  </si>
-  <si>
-    <t>slime, ooze</t>
-  </si>
-  <si>
-    <t>swaesse</t>
-  </si>
-  <si>
-    <t>drink, beverage</t>
-  </si>
-  <si>
-    <t>swanze</t>
-  </si>
-  <si>
-    <t>sheep</t>
-  </si>
-  <si>
-    <t>swind</t>
-  </si>
-  <si>
-    <t>sign (for directions and text)</t>
-  </si>
-  <si>
-    <t>swintane</t>
-  </si>
-  <si>
-    <t>flute</t>
-  </si>
-  <si>
-    <t>swiŋye</t>
-  </si>
-  <si>
-    <t>type, kind, sort</t>
-  </si>
-  <si>
-    <t>sŷlae</t>
-  </si>
-  <si>
-    <t>swan</t>
-  </si>
-  <si>
-    <t>tacwel</t>
-  </si>
-  <si>
-    <t>hoe, cultivator, tiller</t>
-  </si>
-  <si>
-    <t>tael</t>
-  </si>
-  <si>
-    <t>god, deity</t>
-  </si>
-  <si>
-    <t>taend</t>
-  </si>
-  <si>
-    <t>a drum large enough that it's typically played whilst standing up</t>
-  </si>
-  <si>
-    <t>talaraŋ</t>
-  </si>
-  <si>
-    <t>sorcerer</t>
-  </si>
-  <si>
-    <t>taldaŋ</t>
-  </si>
-  <si>
-    <t>sorcery magic</t>
-  </si>
-  <si>
-    <t>tamalash</t>
-  </si>
-  <si>
-    <t>to shine brightly</t>
-  </si>
-  <si>
-    <t>tanten</t>
-  </si>
-  <si>
-    <t>to bake</t>
-  </si>
-  <si>
-    <t>taŋcan</t>
-  </si>
-  <si>
-    <t>to must, to shall</t>
-  </si>
-  <si>
-    <t>tarien</t>
-  </si>
-  <si>
-    <t>gift, present</t>
-  </si>
-  <si>
-    <t>tassie</t>
-  </si>
-  <si>
-    <t>crazy, mentally insane</t>
-  </si>
-  <si>
-    <t>tayandôr</t>
-  </si>
-  <si>
-    <t>orchid (flower)</t>
-  </si>
-  <si>
-    <t>tecse</t>
-  </si>
-  <si>
-    <t>sea shell, snail shell, clam shell</t>
-  </si>
-  <si>
-    <t>telde</t>
-  </si>
-  <si>
-    <t>wonder</t>
-  </si>
-  <si>
-    <t>teltan</t>
-  </si>
-  <si>
-    <t>to oath, to promise, to commit an oath, to make a promise</t>
-  </si>
-  <si>
-    <t>telyash</t>
-  </si>
-  <si>
-    <t>to stand up straight</t>
-  </si>
-  <si>
-    <t>tende</t>
-  </si>
-  <si>
-    <t>tall, high</t>
-  </si>
-  <si>
-    <t>tendiswe</t>
-  </si>
-  <si>
-    <t>height</t>
-  </si>
-  <si>
-    <t>tenild</t>
-  </si>
-  <si>
-    <t>arm ring</t>
-  </si>
-  <si>
-    <t>teŋgen</t>
-  </si>
-  <si>
-    <t>to arrive at, to reach, to get to</t>
-  </si>
-  <si>
-    <t>teŋgesh</t>
-  </si>
-  <si>
-    <t>to come</t>
-  </si>
-  <si>
-    <t>teŋnen</t>
-  </si>
-  <si>
-    <t>to hear</t>
-  </si>
-  <si>
-    <t>terasse</t>
-  </si>
-  <si>
-    <t>lute</t>
-  </si>
-  <si>
-    <t>tesse</t>
-  </si>
-  <si>
-    <t>right</t>
-  </si>
-  <si>
-    <t>tessu</t>
-  </si>
-  <si>
-    <t>rightwards</t>
-  </si>
-  <si>
-    <t>thael</t>
-  </si>
-  <si>
-    <t>clothing, apparel</t>
-  </si>
-  <si>
-    <t>thaiden</t>
-  </si>
-  <si>
-    <t>to stretch, to lengthen; to draw a bow</t>
-  </si>
-  <si>
-    <t>thaine</t>
-  </si>
-  <si>
-    <t>law, rules</t>
-  </si>
-  <si>
-    <t>thaisse</t>
-  </si>
-  <si>
-    <t>cloud, billow</t>
-  </si>
-  <si>
-    <t>thalashaŋ</t>
-  </si>
-  <si>
-    <t>druidry magic</t>
-  </si>
-  <si>
-    <t>thalassi</t>
-  </si>
-  <si>
-    <t>air</t>
-  </si>
-  <si>
-    <t>thas</t>
-  </si>
-  <si>
-    <t>five</t>
-  </si>
-  <si>
-    <t>thash</t>
-  </si>
-  <si>
-    <t>to start, to begin</t>
-  </si>
-  <si>
-    <t>thelen</t>
-  </si>
-  <si>
-    <t>to find, to look for</t>
-  </si>
-  <si>
-    <t>long</t>
-  </si>
-  <si>
-    <t>theren</t>
-  </si>
-  <si>
-    <t>for a long time</t>
-  </si>
-  <si>
-    <t>theressi</t>
-  </si>
-  <si>
-    <t>length</t>
-  </si>
-  <si>
-    <t>thewan</t>
-  </si>
-  <si>
-    <t>to sew (with or without "gai" or "mi")</t>
-  </si>
-  <si>
-    <t>thiemen</t>
-  </si>
-  <si>
-    <t>to lead, to guide</t>
-  </si>
-  <si>
-    <t>thiemen hassu</t>
-  </si>
-  <si>
-    <t>to hold someone's hand, to lead someone by hand (with "mi" + who)</t>
-  </si>
-  <si>
-    <t>thienas</t>
-  </si>
-  <si>
-    <t>ten</t>
-  </si>
-  <si>
-    <t>thilde</t>
-  </si>
-  <si>
-    <t>ally, teammate</t>
-  </si>
-  <si>
-    <t>thilende</t>
-  </si>
-  <si>
-    <t>game, sport</t>
-  </si>
-  <si>
-    <t>thilu</t>
-  </si>
-  <si>
-    <t>far</t>
-  </si>
-  <si>
-    <t>thime</t>
-  </si>
-  <si>
-    <t>silk</t>
-  </si>
-  <si>
-    <t>thiva</t>
-  </si>
-  <si>
-    <t>shears, scissors</t>
-  </si>
-  <si>
-    <t>thobae</t>
-  </si>
-  <si>
-    <t>finger</t>
-  </si>
-  <si>
-    <t>thomash</t>
-  </si>
-  <si>
-    <t>to want</t>
-  </si>
-  <si>
-    <t>thore</t>
-  </si>
-  <si>
-    <t>a loud, thunderous sound</t>
-  </si>
-  <si>
-    <t>thrande</t>
-  </si>
-  <si>
-    <t>orchard, garden</t>
-  </si>
-  <si>
-    <t>throssen</t>
-  </si>
-  <si>
-    <t>to suck</t>
-  </si>
-  <si>
-    <t>thrûvi</t>
-  </si>
-  <si>
-    <t>hay, thatch, dry grass</t>
-  </si>
-  <si>
-    <t>thrŷl</t>
-  </si>
-  <si>
-    <t>finger ring</t>
-  </si>
-  <si>
-    <t>thûca</t>
-  </si>
-  <si>
-    <t>hundred</t>
-  </si>
-  <si>
-    <t>thûicen</t>
-  </si>
-  <si>
-    <t>to mean something</t>
-  </si>
-  <si>
-    <t>thuŋ</t>
-  </si>
-  <si>
-    <t>fear, terror</t>
-  </si>
-  <si>
-    <t>thuŋnen</t>
-  </si>
-  <si>
-    <t>to terrorise, to cause terror</t>
-  </si>
-  <si>
-    <t>thûrda</t>
-  </si>
-  <si>
-    <t>polearm (weapon)</t>
-  </si>
-  <si>
-    <t>thûvala</t>
-  </si>
-  <si>
-    <t>spear</t>
-  </si>
-  <si>
-    <t>thwossiesh</t>
-  </si>
-  <si>
-    <t>to would</t>
-  </si>
-  <si>
-    <t>thŷlen</t>
-  </si>
-  <si>
-    <t>to taste</t>
-  </si>
-  <si>
-    <t>tilie</t>
-  </si>
-  <si>
-    <t>oath, promise</t>
   </si>
   <si>
     <t>tiôr</t>
@@ -8449,16 +8449,31 @@
     <t>/sʲ/</t>
   </si>
   <si>
+    <t>devoicing</t>
+  </si>
+  <si>
+    <t>consonants get devoiced if the consonant before it is voiceless</t>
+  </si>
+  <si>
+    <t>example word</t>
+  </si>
+  <si>
+    <t>example pronunciation</t>
+  </si>
+  <si>
+    <t>/ˈkl̥æiːdwɛn/</t>
+  </si>
+  <si>
+    <t>/kl̥ʏd/</t>
+  </si>
+  <si>
+    <t>/ˈsl̥anθa/</t>
+  </si>
+  <si>
     <t>stress</t>
   </si>
   <si>
     <t>word stress is always on the second last syllable</t>
-  </si>
-  <si>
-    <t>example word</t>
-  </si>
-  <si>
-    <t>example pronunciation</t>
   </si>
   <si>
     <t>/aluːˈandɛ/</t>
@@ -19600,7 +19615,7 @@
         <v>1425</v>
       </c>
       <c r="B700" s="5" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C700" s="6" t="s">
         <v>1426</v>
@@ -19615,7 +19630,7 @@
         <v>1427</v>
       </c>
       <c r="B701" s="5" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C701" s="6" t="s">
         <v>1428</v>
@@ -19626,11 +19641,11 @@
       <c r="G701" s="2"/>
     </row>
     <row r="702" ht="22.5" customHeight="1">
-      <c r="A702" s="8" t="s">
+      <c r="A702" s="4" t="s">
         <v>1429</v>
       </c>
       <c r="B702" s="5" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="C702" s="6" t="s">
         <v>1430</v>
@@ -19641,7 +19656,7 @@
       <c r="G702" s="2"/>
     </row>
     <row r="703" ht="22.5" customHeight="1">
-      <c r="A703" s="4" t="s">
+      <c r="A703" s="8" t="s">
         <v>1431</v>
       </c>
       <c r="B703" s="5" t="s">
@@ -19660,7 +19675,7 @@
         <v>1433</v>
       </c>
       <c r="B704" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C704" s="6" t="s">
         <v>1434</v>
@@ -19677,7 +19692,7 @@
       <c r="B705" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C705" s="6" t="s">
+      <c r="C705" s="9" t="s">
         <v>1436</v>
       </c>
       <c r="D705" s="2"/>
@@ -19690,7 +19705,7 @@
         <v>1437</v>
       </c>
       <c r="B706" s="5" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C706" s="9" t="s">
         <v>1438</v>
@@ -19705,9 +19720,9 @@
         <v>1439</v>
       </c>
       <c r="B707" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C707" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C707" s="6" t="s">
         <v>1440</v>
       </c>
       <c r="D707" s="2"/>
@@ -19716,11 +19731,11 @@
       <c r="G707" s="2"/>
     </row>
     <row r="708" ht="22.5" customHeight="1">
-      <c r="A708" s="8" t="s">
+      <c r="A708" s="4" t="s">
         <v>1441</v>
       </c>
       <c r="B708" s="5" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C708" s="6" t="s">
         <v>1442</v>
@@ -19731,13 +19746,13 @@
       <c r="G708" s="2"/>
     </row>
     <row r="709" ht="22.5" customHeight="1">
-      <c r="A709" s="4" t="s">
+      <c r="A709" s="8" t="s">
         <v>1443</v>
       </c>
       <c r="B709" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C709" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C709" s="9" t="s">
         <v>1444</v>
       </c>
       <c r="D709" s="2"/>
@@ -19750,9 +19765,9 @@
         <v>1445</v>
       </c>
       <c r="B710" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C710" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C710" s="6" t="s">
         <v>1446</v>
       </c>
       <c r="D710" s="2"/>
@@ -19765,9 +19780,9 @@
         <v>1447</v>
       </c>
       <c r="B711" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C711" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C711" s="9" t="s">
         <v>1448</v>
       </c>
       <c r="D711" s="2"/>
@@ -19780,7 +19795,7 @@
         <v>1449</v>
       </c>
       <c r="B712" s="5" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="C712" s="9" t="s">
         <v>1450</v>
@@ -19810,7 +19825,7 @@
         <v>1453</v>
       </c>
       <c r="B714" s="5" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C714" s="9" t="s">
         <v>1454</v>
@@ -19825,9 +19840,9 @@
         <v>1455</v>
       </c>
       <c r="B715" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C715" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C715" s="6" t="s">
         <v>1456</v>
       </c>
       <c r="D715" s="2"/>
@@ -19840,7 +19855,7 @@
         <v>1457</v>
       </c>
       <c r="B716" s="5" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C716" s="6" t="s">
         <v>1458</v>
@@ -19855,9 +19870,9 @@
         <v>1459</v>
       </c>
       <c r="B717" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C717" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C717" s="9" t="s">
         <v>1460</v>
       </c>
       <c r="D717" s="2"/>
@@ -19866,13 +19881,13 @@
       <c r="G717" s="2"/>
     </row>
     <row r="718" ht="22.5" customHeight="1">
-      <c r="A718" s="8" t="s">
+      <c r="A718" s="4" t="s">
         <v>1461</v>
       </c>
       <c r="B718" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C718" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C718" s="6" t="s">
         <v>1462</v>
       </c>
       <c r="D718" s="2"/>
@@ -19881,11 +19896,11 @@
       <c r="G718" s="2"/>
     </row>
     <row r="719" ht="22.5" customHeight="1">
-      <c r="A719" s="4" t="s">
+      <c r="A719" s="8" t="s">
         <v>1463</v>
       </c>
       <c r="B719" s="5" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="C719" s="6" t="s">
         <v>1464</v>
@@ -19900,7 +19915,7 @@
         <v>1465</v>
       </c>
       <c r="B720" s="5" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C720" s="6" t="s">
         <v>1466</v>
@@ -19915,7 +19930,7 @@
         <v>1467</v>
       </c>
       <c r="B721" s="5" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C721" s="6" t="s">
         <v>1468</v>
@@ -19930,9 +19945,9 @@
         <v>1469</v>
       </c>
       <c r="B722" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C722" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C722" s="9" t="s">
         <v>1470</v>
       </c>
       <c r="D722" s="2"/>
@@ -19945,9 +19960,9 @@
         <v>1471</v>
       </c>
       <c r="B723" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C723" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C723" s="6" t="s">
         <v>1472</v>
       </c>
       <c r="D723" s="2"/>
@@ -19960,7 +19975,7 @@
         <v>1473</v>
       </c>
       <c r="B724" s="5" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="C724" s="6" t="s">
         <v>1474</v>
@@ -19971,7 +19986,7 @@
       <c r="G724" s="2"/>
     </row>
     <row r="725" ht="22.5" customHeight="1">
-      <c r="A725" s="8" t="s">
+      <c r="A725" s="4" t="s">
         <v>1475</v>
       </c>
       <c r="B725" s="5" t="s">
@@ -19986,13 +20001,13 @@
       <c r="G725" s="2"/>
     </row>
     <row r="726" ht="22.5" customHeight="1">
-      <c r="A726" s="4" t="s">
+      <c r="A726" s="11" t="s">
         <v>1477</v>
       </c>
       <c r="B726" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C726" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C726" s="9" t="s">
         <v>1478</v>
       </c>
       <c r="D726" s="2"/>
@@ -20001,11 +20016,11 @@
       <c r="G726" s="2"/>
     </row>
     <row r="727" ht="22.5" customHeight="1">
-      <c r="A727" s="11" t="s">
+      <c r="A727" s="8" t="s">
         <v>1479</v>
       </c>
       <c r="B727" s="5" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="C727" s="9" t="s">
         <v>1480</v>
@@ -20016,13 +20031,13 @@
       <c r="G727" s="2"/>
     </row>
     <row r="728" ht="22.5" customHeight="1">
-      <c r="A728" s="8" t="s">
+      <c r="A728" s="4" t="s">
         <v>1481</v>
       </c>
       <c r="B728" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C728" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C728" s="6" t="s">
         <v>1482</v>
       </c>
       <c r="D728" s="2"/>
@@ -20035,7 +20050,7 @@
         <v>1483</v>
       </c>
       <c r="B729" s="5" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C729" s="6" t="s">
         <v>1484</v>
@@ -20046,7 +20061,7 @@
       <c r="G729" s="2"/>
     </row>
     <row r="730" ht="22.5" customHeight="1">
-      <c r="A730" s="4" t="s">
+      <c r="A730" s="8" t="s">
         <v>1485</v>
       </c>
       <c r="B730" s="5" t="s">
@@ -20061,11 +20076,11 @@
       <c r="G730" s="2"/>
     </row>
     <row r="731" ht="22.5" customHeight="1">
-      <c r="A731" s="8" t="s">
+      <c r="A731" s="11" t="s">
         <v>1487</v>
       </c>
       <c r="B731" s="5" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="C731" s="6" t="s">
         <v>1488</v>
@@ -20076,13 +20091,13 @@
       <c r="G731" s="2"/>
     </row>
     <row r="732" ht="22.5" customHeight="1">
-      <c r="A732" s="11" t="s">
+      <c r="A732" s="8" t="s">
         <v>1489</v>
       </c>
       <c r="B732" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C732" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C732" s="9" t="s">
         <v>1490</v>
       </c>
       <c r="D732" s="2"/>
@@ -20095,9 +20110,9 @@
         <v>1491</v>
       </c>
       <c r="B733" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C733" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C733" s="6" t="s">
         <v>1492</v>
       </c>
       <c r="D733" s="2"/>
@@ -20110,7 +20125,7 @@
         <v>1493</v>
       </c>
       <c r="B734" s="5" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C734" s="6" t="s">
         <v>1494</v>
@@ -20125,7 +20140,7 @@
         <v>1495</v>
       </c>
       <c r="B735" s="5" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="C735" s="6" t="s">
         <v>1496</v>
@@ -20136,7 +20151,7 @@
       <c r="G735" s="2"/>
     </row>
     <row r="736" ht="22.5" customHeight="1">
-      <c r="A736" s="8" t="s">
+      <c r="A736" s="4" t="s">
         <v>1497</v>
       </c>
       <c r="B736" s="5" t="s">
@@ -20151,11 +20166,11 @@
       <c r="G736" s="2"/>
     </row>
     <row r="737" ht="22.5" customHeight="1">
-      <c r="A737" s="4" t="s">
+      <c r="A737" s="8" t="s">
         <v>1499</v>
       </c>
       <c r="B737" s="5" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="C737" s="6" t="s">
         <v>1500</v>
@@ -20166,11 +20181,11 @@
       <c r="G737" s="2"/>
     </row>
     <row r="738" ht="22.5" customHeight="1">
-      <c r="A738" s="8" t="s">
+      <c r="A738" s="11" t="s">
         <v>1501</v>
       </c>
       <c r="B738" s="5" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="C738" s="6" t="s">
         <v>1502</v>
@@ -20181,11 +20196,11 @@
       <c r="G738" s="2"/>
     </row>
     <row r="739" ht="22.5" customHeight="1">
-      <c r="A739" s="11" t="s">
+      <c r="A739" s="8" t="s">
         <v>1503</v>
       </c>
       <c r="B739" s="5" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="C739" s="6" t="s">
         <v>1504</v>
@@ -20200,7 +20215,7 @@
         <v>1505</v>
       </c>
       <c r="B740" s="5" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="C740" s="6" t="s">
         <v>1506</v>
@@ -20230,9 +20245,9 @@
         <v>1509</v>
       </c>
       <c r="B742" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C742" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C742" s="9" t="s">
         <v>1510</v>
       </c>
       <c r="D742" s="2"/>
@@ -20241,13 +20256,13 @@
       <c r="G742" s="2"/>
     </row>
     <row r="743" ht="22.5" customHeight="1">
-      <c r="A743" s="8" t="s">
+      <c r="A743" s="4" t="s">
         <v>1511</v>
       </c>
       <c r="B743" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C743" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C743" s="6" t="s">
         <v>1512</v>
       </c>
       <c r="D743" s="2"/>
@@ -20256,11 +20271,11 @@
       <c r="G743" s="2"/>
     </row>
     <row r="744" ht="22.5" customHeight="1">
-      <c r="A744" s="4" t="s">
+      <c r="A744" s="8" t="s">
         <v>1513</v>
       </c>
       <c r="B744" s="5" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="C744" s="6" t="s">
         <v>1514</v>
@@ -20275,7 +20290,7 @@
         <v>1515</v>
       </c>
       <c r="B745" s="5" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="C745" s="6" t="s">
         <v>1516</v>
@@ -20292,7 +20307,7 @@
       <c r="B746" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C746" s="6" t="s">
+      <c r="C746" s="9" t="s">
         <v>1518</v>
       </c>
       <c r="D746" s="2"/>
@@ -20305,7 +20320,7 @@
         <v>1519</v>
       </c>
       <c r="B747" s="5" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C747" s="9" t="s">
         <v>1520</v>
@@ -20316,13 +20331,13 @@
       <c r="G747" s="2"/>
     </row>
     <row r="748" ht="22.5" customHeight="1">
-      <c r="A748" s="8" t="s">
+      <c r="A748" s="4" t="s">
         <v>1521</v>
       </c>
       <c r="B748" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C748" s="9" t="s">
+      <c r="C748" s="6" t="s">
         <v>1522</v>
       </c>
       <c r="D748" s="2"/>
@@ -20331,7 +20346,7 @@
       <c r="G748" s="2"/>
     </row>
     <row r="749" ht="22.5" customHeight="1">
-      <c r="A749" s="4" t="s">
+      <c r="A749" s="8" t="s">
         <v>1523</v>
       </c>
       <c r="B749" s="5" t="s">
@@ -20365,9 +20380,9 @@
         <v>1527</v>
       </c>
       <c r="B751" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C751" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C751" s="9" t="s">
         <v>1528</v>
       </c>
       <c r="D751" s="2"/>
@@ -20380,9 +20395,9 @@
         <v>1529</v>
       </c>
       <c r="B752" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C752" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C752" s="12" t="s">
         <v>1530</v>
       </c>
       <c r="D752" s="2"/>
@@ -20391,13 +20406,13 @@
       <c r="G752" s="2"/>
     </row>
     <row r="753" ht="22.5" customHeight="1">
-      <c r="A753" s="8" t="s">
+      <c r="A753" s="11" t="s">
         <v>1531</v>
       </c>
       <c r="B753" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C753" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C753" s="6" t="s">
         <v>1532</v>
       </c>
       <c r="D753" s="2"/>
@@ -20406,11 +20421,11 @@
       <c r="G753" s="2"/>
     </row>
     <row r="754" ht="22.5" customHeight="1">
-      <c r="A754" s="11" t="s">
+      <c r="A754" s="8" t="s">
         <v>1533</v>
       </c>
       <c r="B754" s="5" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="C754" s="6" t="s">
         <v>1534</v>
@@ -20425,7 +20440,7 @@
         <v>1535</v>
       </c>
       <c r="B755" s="5" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C755" s="6" t="s">
         <v>1536</v>
@@ -20440,7 +20455,7 @@
         <v>1537</v>
       </c>
       <c r="B756" s="5" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="C756" s="6" t="s">
         <v>1538</v>
@@ -20451,11 +20466,11 @@
       <c r="G756" s="2"/>
     </row>
     <row r="757" ht="22.5" customHeight="1">
-      <c r="A757" s="8" t="s">
+      <c r="A757" s="4" t="s">
         <v>1539</v>
       </c>
       <c r="B757" s="5" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="C757" s="6" t="s">
         <v>1540</v>
@@ -20466,13 +20481,13 @@
       <c r="G757" s="2"/>
     </row>
     <row r="758" ht="22.5" customHeight="1">
-      <c r="A758" s="4" t="s">
+      <c r="A758" s="8" t="s">
         <v>1541</v>
       </c>
       <c r="B758" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C758" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C758" s="9" t="s">
         <v>1542</v>
       </c>
       <c r="D758" s="2"/>
@@ -20485,7 +20500,7 @@
         <v>1543</v>
       </c>
       <c r="B759" s="5" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="C759" s="9" t="s">
         <v>1544</v>
@@ -20515,7 +20530,7 @@
         <v>1547</v>
       </c>
       <c r="B761" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C761" s="9" t="s">
         <v>1548</v>
@@ -20526,13 +20541,13 @@
       <c r="G761" s="2"/>
     </row>
     <row r="762" ht="22.5" customHeight="1">
-      <c r="A762" s="8" t="s">
+      <c r="A762" s="4" t="s">
         <v>1549</v>
       </c>
       <c r="B762" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C762" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C762" s="6" t="s">
         <v>1550</v>
       </c>
       <c r="D762" s="2"/>
@@ -20541,13 +20556,13 @@
       <c r="G762" s="2"/>
     </row>
     <row r="763" ht="22.5" customHeight="1">
-      <c r="A763" s="4" t="s">
+      <c r="A763" s="8" t="s">
         <v>1551</v>
       </c>
       <c r="B763" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C763" s="6" t="s">
+      <c r="C763" s="9" t="s">
         <v>1552</v>
       </c>
       <c r="D763" s="2"/>
@@ -20560,7 +20575,7 @@
         <v>1553</v>
       </c>
       <c r="B764" s="5" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C764" s="9" t="s">
         <v>1554</v>
@@ -20571,13 +20586,13 @@
       <c r="G764" s="2"/>
     </row>
     <row r="765" ht="22.5" customHeight="1">
-      <c r="A765" s="8" t="s">
+      <c r="A765" s="4" t="s">
         <v>1555</v>
       </c>
       <c r="B765" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C765" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C765" s="6" t="s">
         <v>1556</v>
       </c>
       <c r="D765" s="2"/>
@@ -20586,7 +20601,7 @@
       <c r="G765" s="2"/>
     </row>
     <row r="766" ht="22.5" customHeight="1">
-      <c r="A766" s="4" t="s">
+      <c r="A766" s="8" t="s">
         <v>1557</v>
       </c>
       <c r="B766" s="5" t="s">
@@ -20601,7 +20616,7 @@
       <c r="G766" s="2"/>
     </row>
     <row r="767" ht="22.5" customHeight="1">
-      <c r="A767" s="8" t="s">
+      <c r="A767" s="4" t="s">
         <v>1559</v>
       </c>
       <c r="B767" s="5" t="s">
@@ -20616,11 +20631,11 @@
       <c r="G767" s="2"/>
     </row>
     <row r="768" ht="22.5" customHeight="1">
-      <c r="A768" s="4" t="s">
+      <c r="A768" s="8" t="s">
         <v>1561</v>
       </c>
       <c r="B768" s="5" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C768" s="6" t="s">
         <v>1562</v>
@@ -20635,7 +20650,7 @@
         <v>1563</v>
       </c>
       <c r="B769" s="5" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C769" s="6" t="s">
         <v>1564</v>
@@ -20646,11 +20661,11 @@
       <c r="G769" s="2"/>
     </row>
     <row r="770" ht="22.5" customHeight="1">
-      <c r="A770" s="8" t="s">
+      <c r="A770" s="11" t="s">
         <v>1565</v>
       </c>
       <c r="B770" s="5" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="C770" s="6" t="s">
         <v>1566</v>
@@ -20661,13 +20676,13 @@
       <c r="G770" s="2"/>
     </row>
     <row r="771" ht="22.5" customHeight="1">
-      <c r="A771" s="11" t="s">
+      <c r="A771" s="8" t="s">
         <v>1567</v>
       </c>
       <c r="B771" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C771" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C771" s="9" t="s">
         <v>1568</v>
       </c>
       <c r="D771" s="2"/>
@@ -20691,13 +20706,13 @@
       <c r="G772" s="2"/>
     </row>
     <row r="773" ht="22.5" customHeight="1">
-      <c r="A773" s="8" t="s">
+      <c r="A773" s="4" t="s">
         <v>1571</v>
       </c>
       <c r="B773" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C773" s="9" t="s">
+        <v>892</v>
+      </c>
+      <c r="C773" s="6" t="s">
         <v>1572</v>
       </c>
       <c r="D773" s="2"/>
@@ -20710,7 +20725,7 @@
         <v>1573</v>
       </c>
       <c r="B774" s="5" t="s">
-        <v>892</v>
+        <v>183</v>
       </c>
       <c r="C774" s="6" t="s">
         <v>1574</v>
@@ -20725,7 +20740,7 @@
         <v>1575</v>
       </c>
       <c r="B775" s="5" t="s">
-        <v>183</v>
+        <v>488</v>
       </c>
       <c r="C775" s="6" t="s">
         <v>1576</v>
@@ -20736,11 +20751,11 @@
       <c r="G775" s="2"/>
     </row>
     <row r="776" ht="22.5" customHeight="1">
-      <c r="A776" s="4" t="s">
+      <c r="A776" s="8" t="s">
         <v>1577</v>
       </c>
       <c r="B776" s="5" t="s">
-        <v>488</v>
+        <v>9</v>
       </c>
       <c r="C776" s="6" t="s">
         <v>1578</v>
@@ -20755,7 +20770,7 @@
         <v>1579</v>
       </c>
       <c r="B777" s="5" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="C777" s="6" t="s">
         <v>1580</v>
@@ -20770,7 +20785,7 @@
         <v>1581</v>
       </c>
       <c r="B778" s="5" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C778" s="6" t="s">
         <v>1582</v>
@@ -20785,9 +20800,9 @@
         <v>1583</v>
       </c>
       <c r="B779" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C779" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C779" s="9" t="s">
         <v>1584</v>
       </c>
       <c r="D779" s="2"/>
@@ -20800,7 +20815,7 @@
         <v>1585</v>
       </c>
       <c r="B780" s="5" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="C780" s="9" t="s">
         <v>1586</v>
@@ -20815,7 +20830,7 @@
         <v>1587</v>
       </c>
       <c r="B781" s="5" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C781" s="9" t="s">
         <v>1588</v>
@@ -20832,7 +20847,7 @@
       <c r="B782" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C782" s="9" t="s">
+      <c r="C782" s="6" t="s">
         <v>1590</v>
       </c>
       <c r="D782" s="2"/>
@@ -20845,7 +20860,7 @@
         <v>1591</v>
       </c>
       <c r="B783" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C783" s="6" t="s">
         <v>1592</v>
@@ -20860,7 +20875,7 @@
         <v>1593</v>
       </c>
       <c r="B784" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C784" s="6" t="s">
         <v>1594</v>
@@ -20871,11 +20886,11 @@
       <c r="G784" s="2"/>
     </row>
     <row r="785" ht="22.5" customHeight="1">
-      <c r="A785" s="8" t="s">
+      <c r="A785" s="4" t="s">
         <v>1595</v>
       </c>
       <c r="B785" s="5" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C785" s="6" t="s">
         <v>1596</v>
@@ -20890,7 +20905,7 @@
         <v>1597</v>
       </c>
       <c r="B786" s="5" t="s">
-        <v>66</v>
+        <v>183</v>
       </c>
       <c r="C786" s="6" t="s">
         <v>1598</v>
@@ -20901,13 +20916,13 @@
       <c r="G786" s="2"/>
     </row>
     <row r="787" ht="22.5" customHeight="1">
-      <c r="A787" s="4" t="s">
+      <c r="A787" s="8" t="s">
         <v>1599</v>
       </c>
       <c r="B787" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C787" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C787" s="9" t="s">
         <v>1600</v>
       </c>
       <c r="D787" s="2"/>
@@ -20920,9 +20935,9 @@
         <v>1601</v>
       </c>
       <c r="B788" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C788" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C788" s="6" t="s">
         <v>1602</v>
       </c>
       <c r="D788" s="2"/>
@@ -20935,9 +20950,9 @@
         <v>1603</v>
       </c>
       <c r="B789" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C789" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C789" s="9" t="s">
         <v>1604</v>
       </c>
       <c r="D789" s="2"/>
@@ -20946,13 +20961,13 @@
       <c r="G789" s="2"/>
     </row>
     <row r="790" ht="22.5" customHeight="1">
-      <c r="A790" s="8" t="s">
+      <c r="A790" s="4" t="s">
         <v>1605</v>
       </c>
       <c r="B790" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C790" s="9" t="s">
+      <c r="C790" s="6" t="s">
         <v>1606</v>
       </c>
       <c r="D790" s="2"/>
@@ -20961,13 +20976,13 @@
       <c r="G790" s="2"/>
     </row>
     <row r="791" ht="22.5" customHeight="1">
-      <c r="A791" s="4" t="s">
+      <c r="A791" s="8" t="s">
         <v>1607</v>
       </c>
       <c r="B791" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C791" s="6" t="s">
+      <c r="C791" s="9" t="s">
         <v>1608</v>
       </c>
       <c r="D791" s="2"/>
@@ -20980,9 +20995,9 @@
         <v>1609</v>
       </c>
       <c r="B792" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C792" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C792" s="6" t="s">
         <v>1610</v>
       </c>
       <c r="D792" s="2"/>
@@ -20995,9 +21010,9 @@
         <v>1611</v>
       </c>
       <c r="B793" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C793" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C793" s="9" t="s">
         <v>1612</v>
       </c>
       <c r="D793" s="2"/>
@@ -21025,9 +21040,9 @@
         <v>1615</v>
       </c>
       <c r="B795" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C795" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C795" s="6" t="s">
         <v>1616</v>
       </c>
       <c r="D795" s="2"/>
@@ -21036,7 +21051,7 @@
       <c r="G795" s="2"/>
     </row>
     <row r="796" ht="22.5" customHeight="1">
-      <c r="A796" s="8" t="s">
+      <c r="A796" s="4" t="s">
         <v>1617</v>
       </c>
       <c r="B796" s="5" t="s">
@@ -21051,11 +21066,11 @@
       <c r="G796" s="2"/>
     </row>
     <row r="797" ht="22.5" customHeight="1">
-      <c r="A797" s="4" t="s">
+      <c r="A797" s="8" t="s">
         <v>1619</v>
       </c>
       <c r="B797" s="5" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C797" s="6" t="s">
         <v>1620</v>
@@ -21087,7 +21102,7 @@
       <c r="B799" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C799" s="6" t="s">
+      <c r="C799" s="9" t="s">
         <v>1624</v>
       </c>
       <c r="D799" s="2"/>
@@ -21100,7 +21115,7 @@
         <v>1625</v>
       </c>
       <c r="B800" s="5" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="C800" s="9" t="s">
         <v>1626</v>
@@ -21115,7 +21130,7 @@
         <v>1627</v>
       </c>
       <c r="B801" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C801" s="9" t="s">
         <v>1628</v>
@@ -21130,7 +21145,7 @@
         <v>1629</v>
       </c>
       <c r="B802" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C802" s="9" t="s">
         <v>1630</v>
@@ -21145,7 +21160,7 @@
         <v>1631</v>
       </c>
       <c r="B803" s="5" t="s">
-        <v>96</v>
+        <v>356</v>
       </c>
       <c r="C803" s="9" t="s">
         <v>1632</v>
@@ -21160,7 +21175,7 @@
         <v>1633</v>
       </c>
       <c r="B804" s="5" t="s">
-        <v>356</v>
+        <v>27</v>
       </c>
       <c r="C804" s="9" t="s">
         <v>1634</v>
@@ -21186,13 +21201,13 @@
       <c r="G805" s="2"/>
     </row>
     <row r="806" ht="22.5" customHeight="1">
-      <c r="A806" s="8" t="s">
+      <c r="A806" s="4" t="s">
         <v>1637</v>
       </c>
       <c r="B806" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C806" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C806" s="6" t="s">
         <v>1638</v>
       </c>
       <c r="D806" s="2"/>
@@ -21201,13 +21216,13 @@
       <c r="G806" s="2"/>
     </row>
     <row r="807" ht="22.5" customHeight="1">
-      <c r="A807" s="4" t="s">
+      <c r="A807" s="8" t="s">
         <v>1639</v>
       </c>
       <c r="B807" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C807" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C807" s="9" t="s">
         <v>1640</v>
       </c>
       <c r="D807" s="2"/>
@@ -21216,13 +21231,13 @@
       <c r="G807" s="2"/>
     </row>
     <row r="808" ht="22.5" customHeight="1">
-      <c r="A808" s="8" t="s">
+      <c r="A808" s="4" t="s">
         <v>1641</v>
       </c>
       <c r="B808" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C808" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C808" s="6" t="s">
         <v>1642</v>
       </c>
       <c r="D808" s="2"/>
@@ -21231,13 +21246,13 @@
       <c r="G808" s="2"/>
     </row>
     <row r="809" ht="22.5" customHeight="1">
-      <c r="A809" s="4" t="s">
+      <c r="A809" s="8" t="s">
         <v>1643</v>
       </c>
       <c r="B809" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C809" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C809" s="9" t="s">
         <v>1644</v>
       </c>
       <c r="D809" s="2"/>
@@ -21250,7 +21265,7 @@
         <v>1645</v>
       </c>
       <c r="B810" s="5" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="C810" s="9" t="s">
         <v>1646</v>
@@ -21265,7 +21280,7 @@
         <v>1647</v>
       </c>
       <c r="B811" s="5" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C811" s="9" t="s">
         <v>1648</v>
@@ -21280,7 +21295,7 @@
         <v>1649</v>
       </c>
       <c r="B812" s="5" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="C812" s="9" t="s">
         <v>1650</v>
@@ -21295,7 +21310,7 @@
         <v>1651</v>
       </c>
       <c r="B813" s="5" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="C813" s="9" t="s">
         <v>1652</v>
@@ -21310,7 +21325,7 @@
         <v>1653</v>
       </c>
       <c r="B814" s="5" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C814" s="9" t="s">
         <v>1654</v>
@@ -21325,7 +21340,7 @@
         <v>1655</v>
       </c>
       <c r="B815" s="5" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="C815" s="9" t="s">
         <v>1656</v>
@@ -21351,11 +21366,11 @@
       <c r="G816" s="2"/>
     </row>
     <row r="817" ht="22.5" customHeight="1">
-      <c r="A817" s="8" t="s">
+      <c r="A817" s="11" t="s">
         <v>1659</v>
       </c>
       <c r="B817" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C817" s="9" t="s">
         <v>1660</v>
@@ -21366,11 +21381,11 @@
       <c r="G817" s="2"/>
     </row>
     <row r="818" ht="22.5" customHeight="1">
-      <c r="A818" s="11" t="s">
+      <c r="A818" s="8" t="s">
         <v>1661</v>
       </c>
       <c r="B818" s="5" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="C818" s="9" t="s">
         <v>1662</v>
@@ -21381,13 +21396,13 @@
       <c r="G818" s="2"/>
     </row>
     <row r="819" ht="22.5" customHeight="1">
-      <c r="A819" s="8" t="s">
+      <c r="A819" s="4" t="s">
         <v>1663</v>
       </c>
       <c r="B819" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C819" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C819" s="6" t="s">
         <v>1664</v>
       </c>
       <c r="D819" s="2"/>
@@ -21396,13 +21411,13 @@
       <c r="G819" s="2"/>
     </row>
     <row r="820" ht="22.5" customHeight="1">
-      <c r="A820" s="4" t="s">
+      <c r="A820" s="8" t="s">
         <v>1665</v>
       </c>
       <c r="B820" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C820" s="6" t="s">
+      <c r="C820" s="9" t="s">
         <v>1666</v>
       </c>
       <c r="D820" s="2"/>
@@ -21411,13 +21426,13 @@
       <c r="G820" s="2"/>
     </row>
     <row r="821" ht="22.5" customHeight="1">
-      <c r="A821" s="8" t="s">
+      <c r="A821" s="4" t="s">
         <v>1667</v>
       </c>
       <c r="B821" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C821" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C821" s="6" t="s">
         <v>1668</v>
       </c>
       <c r="D821" s="2"/>
@@ -21430,7 +21445,7 @@
         <v>1669</v>
       </c>
       <c r="B822" s="5" t="s">
-        <v>66</v>
+        <v>183</v>
       </c>
       <c r="C822" s="6" t="s">
         <v>1670</v>
@@ -21441,13 +21456,13 @@
       <c r="G822" s="2"/>
     </row>
     <row r="823" ht="22.5" customHeight="1">
-      <c r="A823" s="4" t="s">
+      <c r="A823" s="8" t="s">
         <v>1671</v>
       </c>
       <c r="B823" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C823" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C823" s="9" t="s">
         <v>1672</v>
       </c>
       <c r="D823" s="2"/>
@@ -21456,13 +21471,13 @@
       <c r="G823" s="2"/>
     </row>
     <row r="824" ht="22.5" customHeight="1">
-      <c r="A824" s="8" t="s">
+      <c r="A824" s="4" t="s">
         <v>1673</v>
       </c>
       <c r="B824" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C824" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C824" s="6" t="s">
         <v>1674</v>
       </c>
       <c r="D824" s="2"/>
@@ -21475,7 +21490,7 @@
         <v>1675</v>
       </c>
       <c r="B825" s="5" t="s">
-        <v>183</v>
+        <v>27</v>
       </c>
       <c r="C825" s="6" t="s">
         <v>1676</v>
@@ -21505,7 +21520,7 @@
         <v>1679</v>
       </c>
       <c r="B827" s="5" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C827" s="6" t="s">
         <v>1680</v>
@@ -21531,7 +21546,7 @@
       <c r="G828" s="2"/>
     </row>
     <row r="829" ht="22.5" customHeight="1">
-      <c r="A829" s="4" t="s">
+      <c r="A829" s="8" t="s">
         <v>1683</v>
       </c>
       <c r="B829" s="5" t="s">
@@ -21552,7 +21567,7 @@
       <c r="B830" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C830" s="6" t="s">
+      <c r="C830" s="9" t="s">
         <v>1686</v>
       </c>
       <c r="D830" s="2"/>
@@ -21565,7 +21580,7 @@
         <v>1687</v>
       </c>
       <c r="B831" s="5" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="C831" s="9" t="s">
         <v>1688</v>
@@ -21580,7 +21595,7 @@
         <v>1689</v>
       </c>
       <c r="B832" s="5" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="C832" s="9" t="s">
         <v>1690</v>
@@ -21606,13 +21621,13 @@
       <c r="G833" s="2"/>
     </row>
     <row r="834" ht="22.5" customHeight="1">
-      <c r="A834" s="8" t="s">
+      <c r="A834" s="4" t="s">
         <v>1693</v>
       </c>
       <c r="B834" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C834" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C834" s="6" t="s">
         <v>1694</v>
       </c>
       <c r="D834" s="2"/>
@@ -21625,7 +21640,7 @@
         <v>1695</v>
       </c>
       <c r="B835" s="5" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="C835" s="6" t="s">
         <v>1696</v>
@@ -21636,13 +21651,13 @@
       <c r="G835" s="2"/>
     </row>
     <row r="836" ht="22.5" customHeight="1">
-      <c r="A836" s="4" t="s">
+      <c r="A836" s="8" t="s">
         <v>1697</v>
       </c>
       <c r="B836" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C836" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C836" s="9" t="s">
         <v>1698</v>
       </c>
       <c r="D836" s="2"/>
@@ -21685,7 +21700,7 @@
         <v>1703</v>
       </c>
       <c r="B839" s="5" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C839" s="9" t="s">
         <v>1704</v>
@@ -21700,7 +21715,7 @@
         <v>1705</v>
       </c>
       <c r="B840" s="5" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C840" s="9" t="s">
         <v>1706</v>
@@ -21715,7 +21730,7 @@
         <v>1707</v>
       </c>
       <c r="B841" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C841" s="9" t="s">
         <v>1708</v>
@@ -21726,13 +21741,13 @@
       <c r="G841" s="2"/>
     </row>
     <row r="842" ht="22.5" customHeight="1">
-      <c r="A842" s="8" t="s">
+      <c r="A842" s="4" t="s">
         <v>1709</v>
       </c>
       <c r="B842" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C842" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C842" s="13" t="s">
         <v>1710</v>
       </c>
       <c r="D842" s="2"/>
@@ -21741,13 +21756,13 @@
       <c r="G842" s="2"/>
     </row>
     <row r="843" ht="22.5" customHeight="1">
-      <c r="A843" s="4" t="s">
+      <c r="A843" s="8" t="s">
         <v>1711</v>
       </c>
       <c r="B843" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C843" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C843" s="9" t="s">
         <v>1712</v>
       </c>
       <c r="D843" s="2"/>
@@ -21756,7 +21771,7 @@
       <c r="G843" s="2"/>
     </row>
     <row r="844" ht="22.5" customHeight="1">
-      <c r="A844" s="8" t="s">
+      <c r="A844" s="11" t="s">
         <v>1713</v>
       </c>
       <c r="B844" s="5" t="s">
@@ -21771,7 +21786,7 @@
       <c r="G844" s="2"/>
     </row>
     <row r="845" ht="22.5" customHeight="1">
-      <c r="A845" s="11" t="s">
+      <c r="A845" s="8" t="s">
         <v>1715</v>
       </c>
       <c r="B845" s="5" t="s">
@@ -21786,7 +21801,7 @@
       <c r="G845" s="2"/>
     </row>
     <row r="846" ht="22.5" customHeight="1">
-      <c r="A846" s="8" t="s">
+      <c r="A846" s="11" t="s">
         <v>1717</v>
       </c>
       <c r="B846" s="5" t="s">
@@ -21820,7 +21835,7 @@
         <v>1721</v>
       </c>
       <c r="B848" s="5" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="C848" s="9" t="s">
         <v>1722</v>
@@ -21831,11 +21846,11 @@
       <c r="G848" s="2"/>
     </row>
     <row r="849" ht="22.5" customHeight="1">
-      <c r="A849" s="11" t="s">
+      <c r="A849" s="8" t="s">
         <v>1723</v>
       </c>
       <c r="B849" s="5" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C849" s="9" t="s">
         <v>1724</v>
@@ -21846,7 +21861,7 @@
       <c r="G849" s="2"/>
     </row>
     <row r="850" ht="22.5" customHeight="1">
-      <c r="A850" s="8" t="s">
+      <c r="A850" s="11" t="s">
         <v>1725</v>
       </c>
       <c r="B850" s="5" t="s">
@@ -21861,7 +21876,7 @@
       <c r="G850" s="2"/>
     </row>
     <row r="851" ht="22.5" customHeight="1">
-      <c r="A851" s="11" t="s">
+      <c r="A851" s="8" t="s">
         <v>1727</v>
       </c>
       <c r="B851" s="5" t="s">
@@ -21880,7 +21895,7 @@
         <v>1729</v>
       </c>
       <c r="B852" s="5" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="C852" s="9" t="s">
         <v>1730</v>
@@ -21891,11 +21906,11 @@
       <c r="G852" s="2"/>
     </row>
     <row r="853" ht="22.5" customHeight="1">
-      <c r="A853" s="8" t="s">
+      <c r="A853" s="11" t="s">
         <v>1731</v>
       </c>
       <c r="B853" s="5" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C853" s="9" t="s">
         <v>1732</v>
@@ -21906,11 +21921,11 @@
       <c r="G853" s="2"/>
     </row>
     <row r="854" ht="22.5" customHeight="1">
-      <c r="A854" s="11" t="s">
+      <c r="A854" s="8" t="s">
         <v>1733</v>
       </c>
       <c r="B854" s="5" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="C854" s="9" t="s">
         <v>1734</v>
@@ -21925,7 +21940,7 @@
         <v>1735</v>
       </c>
       <c r="B855" s="5" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C855" s="9" t="s">
         <v>1736</v>
@@ -21936,7 +21951,7 @@
       <c r="G855" s="2"/>
     </row>
     <row r="856" ht="22.5" customHeight="1">
-      <c r="A856" s="8" t="s">
+      <c r="A856" s="11" t="s">
         <v>1737</v>
       </c>
       <c r="B856" s="5" t="s">
@@ -21951,11 +21966,11 @@
       <c r="G856" s="2"/>
     </row>
     <row r="857" ht="22.5" customHeight="1">
-      <c r="A857" s="11" t="s">
+      <c r="A857" s="8" t="s">
         <v>1739</v>
       </c>
       <c r="B857" s="5" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C857" s="9" t="s">
         <v>1740</v>
@@ -21981,13 +21996,13 @@
       <c r="G858" s="2"/>
     </row>
     <row r="859" ht="22.5" customHeight="1">
-      <c r="A859" s="8" t="s">
+      <c r="A859" s="4" t="s">
         <v>1743</v>
       </c>
       <c r="B859" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C859" s="9" t="s">
+      <c r="C859" s="6" t="s">
         <v>1744</v>
       </c>
       <c r="D859" s="2"/>
@@ -21996,13 +22011,13 @@
       <c r="G859" s="2"/>
     </row>
     <row r="860" ht="22.5" customHeight="1">
-      <c r="A860" s="4" t="s">
+      <c r="A860" s="11" t="s">
         <v>1745</v>
       </c>
       <c r="B860" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C860" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C860" s="9" t="s">
         <v>1746</v>
       </c>
       <c r="D860" s="2"/>
@@ -22011,13 +22026,13 @@
       <c r="G860" s="2"/>
     </row>
     <row r="861" ht="22.5" customHeight="1">
-      <c r="A861" s="11" t="s">
+      <c r="A861" s="4" t="s">
         <v>1747</v>
       </c>
       <c r="B861" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C861" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C861" s="6" t="s">
         <v>1748</v>
       </c>
       <c r="D861" s="2"/>
@@ -22026,13 +22041,13 @@
       <c r="G861" s="2"/>
     </row>
     <row r="862" ht="22.5" customHeight="1">
-      <c r="A862" s="4" t="s">
+      <c r="A862" s="8" t="s">
         <v>1749</v>
       </c>
       <c r="B862" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C862" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C862" s="9" t="s">
         <v>1750</v>
       </c>
       <c r="D862" s="2"/>
@@ -22071,13 +22086,13 @@
       <c r="G864" s="2"/>
     </row>
     <row r="865" ht="22.5" customHeight="1">
-      <c r="A865" s="8" t="s">
+      <c r="A865" s="4" t="s">
         <v>1755</v>
       </c>
       <c r="B865" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C865" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C865" s="6" t="s">
         <v>1756</v>
       </c>
       <c r="D865" s="2"/>
@@ -22101,13 +22116,13 @@
       <c r="G866" s="2"/>
     </row>
     <row r="867" ht="22.5" customHeight="1">
-      <c r="A867" s="4" t="s">
+      <c r="A867" s="11" t="s">
         <v>1759</v>
       </c>
       <c r="B867" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C867" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C867" s="12" t="s">
         <v>1760</v>
       </c>
       <c r="D867" s="2"/>
@@ -22120,9 +22135,9 @@
         <v>1761</v>
       </c>
       <c r="B868" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C868" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C868" s="9" t="s">
         <v>1762</v>
       </c>
       <c r="D868" s="2"/>
@@ -22135,7 +22150,7 @@
         <v>1763</v>
       </c>
       <c r="B869" s="5" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="C869" s="9" t="s">
         <v>1764</v>
@@ -22146,11 +22161,11 @@
       <c r="G869" s="2"/>
     </row>
     <row r="870" ht="22.5" customHeight="1">
-      <c r="A870" s="11" t="s">
+      <c r="A870" s="8" t="s">
         <v>1765</v>
       </c>
       <c r="B870" s="5" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="C870" s="9" t="s">
         <v>1766</v>
@@ -22195,7 +22210,7 @@
         <v>1771</v>
       </c>
       <c r="B873" s="5" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C873" s="9" t="s">
         <v>1772</v>
@@ -22206,13 +22221,13 @@
       <c r="G873" s="2"/>
     </row>
     <row r="874" ht="22.5" customHeight="1">
-      <c r="A874" s="8" t="s">
+      <c r="A874" s="4" t="s">
         <v>1773</v>
       </c>
       <c r="B874" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C874" s="9" t="s">
+      <c r="C874" s="6" t="s">
         <v>1774</v>
       </c>
       <c r="D874" s="2"/>
@@ -22225,7 +22240,7 @@
         <v>1775</v>
       </c>
       <c r="B875" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C875" s="6" t="s">
         <v>1776</v>
@@ -22236,13 +22251,13 @@
       <c r="G875" s="2"/>
     </row>
     <row r="876" ht="22.5" customHeight="1">
-      <c r="A876" s="4" t="s">
+      <c r="A876" s="11" t="s">
         <v>1777</v>
       </c>
       <c r="B876" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C876" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C876" s="9" t="s">
         <v>1778</v>
       </c>
       <c r="D876" s="2"/>
@@ -22251,13 +22266,13 @@
       <c r="G876" s="2"/>
     </row>
     <row r="877" ht="22.5" customHeight="1">
-      <c r="A877" s="11" t="s">
+      <c r="A877" s="4" t="s">
         <v>1779</v>
       </c>
       <c r="B877" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C877" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C877" s="6" t="s">
         <v>1780</v>
       </c>
       <c r="D877" s="2"/>
@@ -22266,13 +22281,13 @@
       <c r="G877" s="2"/>
     </row>
     <row r="878" ht="22.5" customHeight="1">
-      <c r="A878" s="4" t="s">
+      <c r="A878" s="8" t="s">
         <v>1781</v>
       </c>
       <c r="B878" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C878" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C878" s="9" t="s">
         <v>1782</v>
       </c>
       <c r="D878" s="2"/>
@@ -22326,11 +22341,11 @@
       <c r="G881" s="2"/>
     </row>
     <row r="882" ht="22.5" customHeight="1">
-      <c r="A882" s="8" t="s">
+      <c r="A882" s="11" t="s">
         <v>1789</v>
       </c>
       <c r="B882" s="5" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="C882" s="9" t="s">
         <v>1790</v>
@@ -22341,13 +22356,13 @@
       <c r="G882" s="2"/>
     </row>
     <row r="883" ht="22.5" customHeight="1">
-      <c r="A883" s="11" t="s">
+      <c r="A883" s="8" t="s">
         <v>1791</v>
       </c>
       <c r="B883" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C883" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C883" s="6" t="s">
         <v>1792</v>
       </c>
       <c r="D883" s="2"/>
@@ -22362,7 +22377,7 @@
       <c r="B884" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C884" s="6" t="s">
+      <c r="C884" s="9" t="s">
         <v>1794</v>
       </c>
       <c r="D884" s="2"/>
@@ -22371,14 +22386,14 @@
       <c r="G884" s="2"/>
     </row>
     <row r="885" ht="22.5" customHeight="1">
-      <c r="A885" s="8" t="s">
+      <c r="A885" s="11" t="s">
+        <v>591</v>
+      </c>
+      <c r="B885" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C885" s="9" t="s">
         <v>1795</v>
-      </c>
-      <c r="B885" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C885" s="9" t="s">
-        <v>1796</v>
       </c>
       <c r="D885" s="2"/>
       <c r="E885" s="2"/>
@@ -22387,10 +22402,10 @@
     </row>
     <row r="886" ht="22.5" customHeight="1">
       <c r="A886" s="11" t="s">
-        <v>591</v>
+        <v>1796</v>
       </c>
       <c r="B886" s="5" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C886" s="9" t="s">
         <v>1797</v>
@@ -22405,7 +22420,7 @@
         <v>1798</v>
       </c>
       <c r="B887" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C887" s="9" t="s">
         <v>1799</v>
@@ -22416,11 +22431,11 @@
       <c r="G887" s="2"/>
     </row>
     <row r="888" ht="22.5" customHeight="1">
-      <c r="A888" s="11" t="s">
+      <c r="A888" s="8" t="s">
         <v>1800</v>
       </c>
       <c r="B888" s="5" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C888" s="9" t="s">
         <v>1801</v>
@@ -22461,11 +22476,11 @@
       <c r="G890" s="2"/>
     </row>
     <row r="891" ht="22.5" customHeight="1">
-      <c r="A891" s="8" t="s">
+      <c r="A891" s="11" t="s">
         <v>1806</v>
       </c>
       <c r="B891" s="5" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="C891" s="9" t="s">
         <v>1807</v>
@@ -22476,13 +22491,13 @@
       <c r="G891" s="2"/>
     </row>
     <row r="892" ht="22.5" customHeight="1">
-      <c r="A892" s="11" t="s">
+      <c r="A892" s="4" t="s">
         <v>1808</v>
       </c>
       <c r="B892" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C892" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C892" s="6" t="s">
         <v>1809</v>
       </c>
       <c r="D892" s="2"/>
@@ -22491,13 +22506,13 @@
       <c r="G892" s="2"/>
     </row>
     <row r="893" ht="22.5" customHeight="1">
-      <c r="A893" s="4" t="s">
+      <c r="A893" s="11" t="s">
         <v>1810</v>
       </c>
       <c r="B893" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C893" s="6" t="s">
+      <c r="C893" s="9" t="s">
         <v>1811</v>
       </c>
       <c r="D893" s="2"/>
@@ -22510,7 +22525,7 @@
         <v>1812</v>
       </c>
       <c r="B894" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C894" s="9" t="s">
         <v>1813</v>
@@ -22525,7 +22540,7 @@
         <v>1814</v>
       </c>
       <c r="B895" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C895" s="9" t="s">
         <v>1815</v>
@@ -22536,11 +22551,11 @@
       <c r="G895" s="2"/>
     </row>
     <row r="896" ht="22.5" customHeight="1">
-      <c r="A896" s="11" t="s">
+      <c r="A896" s="8" t="s">
         <v>1816</v>
       </c>
       <c r="B896" s="5" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="C896" s="9" t="s">
         <v>1817</v>
@@ -22551,11 +22566,11 @@
       <c r="G896" s="2"/>
     </row>
     <row r="897" ht="22.5" customHeight="1">
-      <c r="A897" s="8" t="s">
+      <c r="A897" s="11" t="s">
         <v>1818</v>
       </c>
       <c r="B897" s="5" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C897" s="9" t="s">
         <v>1819</v>
@@ -22570,7 +22585,7 @@
         <v>1820</v>
       </c>
       <c r="B898" s="5" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C898" s="9" t="s">
         <v>1821</v>
@@ -22581,13 +22596,13 @@
       <c r="G898" s="2"/>
     </row>
     <row r="899" ht="22.5" customHeight="1">
-      <c r="A899" s="11" t="s">
+      <c r="A899" s="4" t="s">
         <v>1822</v>
       </c>
       <c r="B899" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C899" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C899" s="6" t="s">
         <v>1823</v>
       </c>
       <c r="D899" s="2"/>
@@ -22596,13 +22611,13 @@
       <c r="G899" s="2"/>
     </row>
     <row r="900" ht="22.5" customHeight="1">
-      <c r="A900" s="4" t="s">
+      <c r="A900" s="8" t="s">
         <v>1824</v>
       </c>
       <c r="B900" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C900" s="6" t="s">
+      <c r="C900" s="9" t="s">
         <v>1825</v>
       </c>
       <c r="D900" s="2"/>
@@ -22615,7 +22630,7 @@
         <v>1826</v>
       </c>
       <c r="B901" s="5" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C901" s="9" t="s">
         <v>1827</v>
@@ -22630,7 +22645,7 @@
         <v>1828</v>
       </c>
       <c r="B902" s="5" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="C902" s="9" t="s">
         <v>1829</v>
@@ -22641,7 +22656,7 @@
       <c r="G902" s="2"/>
     </row>
     <row r="903" ht="22.5" customHeight="1">
-      <c r="A903" s="8" t="s">
+      <c r="A903" s="11" t="s">
         <v>1830</v>
       </c>
       <c r="B903" s="5" t="s">
@@ -22660,7 +22675,7 @@
         <v>1832</v>
       </c>
       <c r="B904" s="5" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="C904" s="9" t="s">
         <v>1833</v>
@@ -22671,11 +22686,11 @@
       <c r="G904" s="2"/>
     </row>
     <row r="905" ht="22.5" customHeight="1">
-      <c r="A905" s="11" t="s">
+      <c r="A905" s="8" t="s">
         <v>1834</v>
       </c>
       <c r="B905" s="5" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="C905" s="9" t="s">
         <v>1835</v>
@@ -22690,7 +22705,7 @@
         <v>1836</v>
       </c>
       <c r="B906" s="5" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C906" s="9" t="s">
         <v>1837</v>
@@ -22705,7 +22720,7 @@
         <v>1838</v>
       </c>
       <c r="B907" s="5" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="C907" s="9" t="s">
         <v>1839</v>
@@ -22720,7 +22735,7 @@
         <v>1840</v>
       </c>
       <c r="B908" s="5" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="C908" s="9" t="s">
         <v>1841</v>
@@ -22737,7 +22752,7 @@
       <c r="B909" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C909" s="9" t="s">
+      <c r="C909" s="6" t="s">
         <v>1843</v>
       </c>
       <c r="D909" s="2"/>
@@ -22750,9 +22765,9 @@
         <v>1844</v>
       </c>
       <c r="B910" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C910" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C910" s="9" t="s">
         <v>1845</v>
       </c>
       <c r="D910" s="2"/>
@@ -22761,7 +22776,7 @@
       <c r="G910" s="2"/>
     </row>
     <row r="911" ht="22.5" customHeight="1">
-      <c r="A911" s="8" t="s">
+      <c r="A911" s="11" t="s">
         <v>1846</v>
       </c>
       <c r="B911" s="5" t="s">
@@ -22780,7 +22795,7 @@
         <v>1848</v>
       </c>
       <c r="B912" s="5" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C912" s="9" t="s">
         <v>1849</v>
@@ -22791,13 +22806,13 @@
       <c r="G912" s="2"/>
     </row>
     <row r="913" ht="22.5" customHeight="1">
-      <c r="A913" s="11" t="s">
+      <c r="A913" s="8" t="s">
         <v>1850</v>
       </c>
       <c r="B913" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C913" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C913" s="6" t="s">
         <v>1851</v>
       </c>
       <c r="D913" s="2"/>
@@ -26317,7 +26332,7 @@
         <v>2275</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="I3" s="16" t="s">
         <v>2279</v>
@@ -26726,7 +26741,7 @@
         <v>2282</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="E24" s="16" t="s">
         <v>2321</v>
@@ -26793,7 +26808,7 @@
         <v>2275</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>638</v>
@@ -26808,7 +26823,7 @@
         <v>2282</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="E29" s="16" t="s">
         <v>2323</v>
@@ -27848,7 +27863,7 @@
         <v>2332</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="L3" s="16"/>
     </row>
@@ -28037,7 +28052,7 @@
         <v>2332</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="19" t="s">
@@ -28109,7 +28124,7 @@
         <v>2370</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="19" t="s">
@@ -28149,7 +28164,7 @@
         <v>2332</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="L16" s="16"/>
     </row>
@@ -28450,7 +28465,7 @@
         <v>2332</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="C35" s="28"/>
       <c r="D35" s="2"/>
@@ -28462,7 +28477,7 @@
         <v>2333</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="C36" s="28"/>
       <c r="D36" s="2"/>
@@ -28491,7 +28506,7 @@
         <v>2398</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="C38" s="28"/>
       <c r="D38" s="2"/>
@@ -29271,7 +29286,6 @@
       <c r="A42" s="18" t="s">
         <v>2531</v>
       </c>
-      <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -29281,7 +29295,6 @@
       <c r="A43" s="16" t="s">
         <v>2532</v>
       </c>
-      <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -29294,58 +29307,51 @@
       <c r="B44" s="18" t="s">
         <v>2534</v>
       </c>
-      <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
-      <c r="A45" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B45" s="16" t="s">
+      <c r="A45" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>2535</v>
       </c>
-      <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>2536</v>
       </c>
-      <c r="B46" s="16" t="s">
-        <v>2537</v>
-      </c>
-      <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
-      <c r="A47" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="B47" s="16" t="s">
-        <v>2538</v>
-      </c>
-      <c r="D47" s="2"/>
+      <c r="A47" s="7" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>2537</v>
+      </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
-      <c r="A48" s="16" t="s">
-        <v>1439</v>
-      </c>
-      <c r="B48" s="16" t="s">
-        <v>2539</v>
-      </c>
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -29353,12 +29359,9 @@
       <c r="H48" s="2"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
-      <c r="A49" s="16" t="s">
-        <v>1453</v>
-      </c>
-      <c r="B49" s="16" t="s">
-        <v>2540</v>
-      </c>
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
@@ -29366,12 +29369,9 @@
       <c r="H49" s="2"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
-      <c r="A50" s="16" t="s">
-        <v>1928</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>2541</v>
-      </c>
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
@@ -29379,11 +29379,8 @@
       <c r="H50" s="2"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
-      <c r="A51" s="16" t="s">
-        <v>564</v>
-      </c>
-      <c r="B51" s="16" t="s">
-        <v>2542</v>
+      <c r="A51" s="18" t="s">
+        <v>2538</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
@@ -29392,9 +29389,9 @@
       <c r="H51" s="2"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
+      <c r="A52" s="16" t="s">
+        <v>2539</v>
+      </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
@@ -29402,9 +29399,12 @@
       <c r="H52" s="2"/>
     </row>
     <row r="53" ht="18.75" customHeight="1">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
+      <c r="A53" s="18" t="s">
+        <v>2533</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>2534</v>
+      </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
@@ -29412,9 +29412,12 @@
       <c r="H53" s="2"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
+      <c r="A54" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>2540</v>
+      </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
@@ -29422,9 +29425,12 @@
       <c r="H54" s="2"/>
     </row>
     <row r="55" ht="18.75" customHeight="1">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
+      <c r="A55" s="16" t="s">
+        <v>2541</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>2542</v>
+      </c>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
@@ -29432,9 +29438,12 @@
       <c r="H55" s="2"/>
     </row>
     <row r="56" ht="18.75" customHeight="1">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
+      <c r="A56" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>2543</v>
+      </c>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
@@ -29442,9 +29451,12 @@
       <c r="H56" s="2"/>
     </row>
     <row r="57" ht="18.75" customHeight="1">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
+      <c r="A57" s="16" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>2544</v>
+      </c>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
@@ -29452,9 +29464,12 @@
       <c r="H57" s="2"/>
     </row>
     <row r="58" ht="18.75" customHeight="1">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
+      <c r="A58" s="16" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>2545</v>
+      </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
@@ -29462,9 +29477,12 @@
       <c r="H58" s="2"/>
     </row>
     <row r="59" ht="18.75" customHeight="1">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
+      <c r="A59" s="16" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>2546</v>
+      </c>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
@@ -29472,9 +29490,12 @@
       <c r="H59" s="2"/>
     </row>
     <row r="60" ht="18.75" customHeight="1">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
+      <c r="A60" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>2547</v>
+      </c>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
@@ -29482,9 +29503,6 @@
       <c r="H60" s="2"/>
     </row>
     <row r="61" ht="18.75" customHeight="1">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
@@ -29492,9 +29510,6 @@
       <c r="H61" s="2"/>
     </row>
     <row r="62" ht="18.75" customHeight="1">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
@@ -29502,9 +29517,6 @@
       <c r="H62" s="2"/>
     </row>
     <row r="63" ht="18.75" customHeight="1">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
@@ -29512,9 +29524,6 @@
       <c r="H63" s="2"/>
     </row>
     <row r="64" ht="18.75" customHeight="1">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
@@ -29522,9 +29531,6 @@
       <c r="H64" s="2"/>
     </row>
     <row r="65" ht="18.75" customHeight="1">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
@@ -29532,9 +29538,6 @@
       <c r="H65" s="2"/>
     </row>
     <row r="66" ht="18.75" customHeight="1">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
@@ -29882,18 +29885,24 @@
       <c r="H100" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
+  <mergeCells count="66">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B46:D46"/>
     <mergeCell ref="C40:F40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="B44:D44"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="C17:F17"/>
@@ -29960,18 +29969,18 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="7" t="s">
-        <v>2543</v>
+        <v>2548</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>2544</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>2545</v>
+        <v>2550</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>2546</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
@@ -29984,10 +29993,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>2547</v>
+        <v>2552</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>2548</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
@@ -30008,15 +30017,15 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>2549</v>
+        <v>2554</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>2550</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>2551</v>
+        <v>2556</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>2171</v>
@@ -30024,58 +30033,58 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>2552</v>
+        <v>2557</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>2553</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>2554</v>
+        <v>2559</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>2555</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>2556</v>
+        <v>2561</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>2557</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>2558</v>
+        <v>2563</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>2559</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>2560</v>
+        <v>2565</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>2561</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>2562</v>
+        <v>2567</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>2563</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>2564</v>
+        <v>2569</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>2565</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="16" ht="18.75" customHeight="1">
@@ -30095,19 +30104,19 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>2566</v>
+        <v>2571</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>2567</v>
+        <v>2572</v>
       </c>
       <c r="G18" s="2"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>2568</v>
+        <v>2573</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>2569</v>
+        <v>2574</v>
       </c>
       <c r="G19" s="2"/>
     </row>
@@ -30128,19 +30137,19 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="10" t="s">
-        <v>2570</v>
+        <v>2575</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>2571</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1"/>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="10" t="s">
-        <v>2572</v>
+        <v>2577</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>2573</v>
+        <v>2578</v>
       </c>
       <c r="G24" s="37"/>
     </row>
